--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -798,43 +798,43 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="O3">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P3">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="Q3">
         <v>2.96</v>
       </c>
       <c r="R3">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S3">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="V3">
         <v>1.22</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z3">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AA3">
         <v>2.66</v>
@@ -855,7 +855,7 @@
         <v>2.2</v>
       </c>
       <c r="AG3">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
         <v>1.88</v>
@@ -2277,13 +2277,13 @@
         <v>2.73</v>
       </c>
       <c r="R12">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="S12">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T12">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="U12">
         <v>3.8</v>
@@ -2301,10 +2301,10 @@
         <v>1.5</v>
       </c>
       <c r="Z12">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="AA12">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AB12">
         <v>1.44</v>
@@ -2316,10 +2316,10 @@
         <v>1.12</v>
       </c>
       <c r="AE12">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF12">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AG12">
         <v>1.57</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
         <v>1.65</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O17">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="P17">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>1.56</v>
@@ -3095,46 +3095,46 @@
         <v>3.1</v>
       </c>
       <c r="S17">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="U17">
         <v>1.73</v>
       </c>
       <c r="V17">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="W17">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z17">
-        <v>6.65</v>
+        <v>5.25</v>
       </c>
       <c r="AA17">
         <v>1.25</v>
       </c>
       <c r="AB17">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="AC17">
         <v>1.7</v>
       </c>
       <c r="AD17">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AE17">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF17">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="AG17">
         <v>2.07</v>
@@ -3436,7 +3436,7 @@
         <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.15</v>
@@ -3445,13 +3445,13 @@
         <v>4.2</v>
       </c>
       <c r="AA19">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB19">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AC19">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD19">
         <v>1.42</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P20">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q20">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB20">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC20">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AD20">
+        <v>1.42</v>
+      </c>
+      <c r="AE20">
+        <v>1.13</v>
+      </c>
+      <c r="AF20">
+        <v>1.45</v>
+      </c>
+      <c r="AG20">
+        <v>2.28</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.22</v>
+      </c>
+      <c r="AK20">
         <v>1.44</v>
-      </c>
-      <c r="AE20">
-        <v>1.14</v>
-      </c>
-      <c r="AF20">
-        <v>1.46</v>
-      </c>
-      <c r="AG20">
-        <v>2.25</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.21</v>
-      </c>
-      <c r="AK20">
-        <v>1.28</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="O21">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q21">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="V21">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA21">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AC21">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AD21">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG21">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>3.4</v>
       </c>
       <c r="S26">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T26">
         <v>4.5</v>
@@ -4589,10 +4589,10 @@
         <v>1.18</v>
       </c>
       <c r="AB26">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AC26">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AD26">
         <v>2.3</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK26">
         <v>4.5</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="O27">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="Q27">
         <v>3.65</v>
@@ -5863,19 +5863,19 @@
         <v>5</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S34">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
         <v>2.9</v>
       </c>
       <c r="U34">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
         <v>1.06</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
         <v>1.13</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N60">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G62">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O4">
         <v>3.5</v>
       </c>
       <c r="P4">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q4">
         <v>2.35</v>
@@ -979,7 +979,7 @@
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="U4">
         <v>2.63</v>
@@ -988,22 +988,22 @@
         <v>1.41</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="AA4">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AB4">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC4">
         <v>3.15</v>
@@ -1012,7 +1012,7 @@
         <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
         <v>1.75</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
         <v>1.88</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1942,10 +1942,10 @@
         <v>2.8</v>
       </c>
       <c r="O10">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P10">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.16</v>
+        <v>4.28</v>
       </c>
       <c r="O13">
-        <v>3.99</v>
+        <v>3.59</v>
       </c>
       <c r="P13">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="Q13">
         <v>4.2</v>
@@ -4387,7 +4387,7 @@
         <v>1.94</v>
       </c>
       <c r="O25">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="P25">
         <v>4.1</v>
@@ -4426,7 +4426,7 @@
         <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC25">
         <v>4.2</v>
@@ -4441,7 +4441,7 @@
         <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="O26">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="P26">
         <v>11</v>
       </c>
       <c r="Q26">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="R26">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="S26">
         <v>1.13</v>
@@ -4568,7 +4568,7 @@
         <v>4.5</v>
       </c>
       <c r="U26">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V26">
         <v>2</v>
@@ -4583,16 +4583,16 @@
         <v>1.01</v>
       </c>
       <c r="Z26">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AA26">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AB26">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AC26">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AD26">
         <v>2.3</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q27">
-        <v>3.65</v>
+        <v>3.18</v>
       </c>
       <c r="R27">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
+        <v>2.98</v>
+      </c>
+      <c r="U27">
+        <v>2.54</v>
+      </c>
+      <c r="V27">
+        <v>1.44</v>
+      </c>
+      <c r="W27">
+        <v>1.11</v>
+      </c>
+      <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.2</v>
+      </c>
+      <c r="Z27">
+        <v>3.68</v>
+      </c>
+      <c r="AA27">
+        <v>1.75</v>
+      </c>
+      <c r="AB27">
+        <v>2.02</v>
+      </c>
+      <c r="AC27">
         <v>2.7</v>
       </c>
-      <c r="U27">
-        <v>3</v>
-      </c>
-      <c r="V27">
-        <v>1.29</v>
-      </c>
-      <c r="W27">
-        <v>1.01</v>
-      </c>
-      <c r="X27">
-        <v>1.08</v>
-      </c>
-      <c r="Y27">
+      <c r="AD27">
         <v>1.36</v>
       </c>
-      <c r="Z27">
-        <v>2.7</v>
-      </c>
-      <c r="AA27">
-        <v>2.2</v>
-      </c>
-      <c r="AB27">
-        <v>1.62</v>
-      </c>
-      <c r="AC27">
-        <v>4</v>
-      </c>
-      <c r="AD27">
-        <v>1.22</v>
-      </c>
       <c r="AE27">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG27">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5214,19 +5214,19 @@
         <v>0</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X30">
         <v>0</v>
@@ -5253,10 +5253,10 @@
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5377,19 +5377,19 @@
         <v>0</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
         <v>0</v>
@@ -5416,10 +5416,10 @@
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,34 +5851,34 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.55</v>
+        <v>5.11</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="P34">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Q34">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="R34">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="S34">
         <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U34">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
         <v>1.05</v>
@@ -5887,19 +5887,19 @@
         <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA34">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB34">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC34">
         <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE34">
         <v>1.11</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,40 +6014,40 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="O35">
-        <v>3.55</v>
+        <v>4.35</v>
       </c>
       <c r="P35">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="Q35">
         <v>2.48</v>
       </c>
       <c r="R35">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="U35">
         <v>2.7</v>
       </c>
       <c r="V35">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z35">
         <v>3.65</v>
@@ -6059,13 +6059,13 @@
         <v>1.91</v>
       </c>
       <c r="AC35">
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="AD35">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
         <v>1.71</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P36">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -6192,10 +6192,10 @@
         <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T36">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="U36">
         <v>2.6</v>
@@ -6213,7 +6213,7 @@
         <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.95</v>
+        <v>3.54</v>
       </c>
       <c r="AA36">
         <v>1.76</v>
@@ -6228,10 +6228,10 @@
         <v>1.37</v>
       </c>
       <c r="AE36">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AG36">
         <v>2.16</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="O37">
         <v>3.6</v>
@@ -6361,7 +6361,7 @@
         <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="V37">
         <v>1.46</v>
@@ -6385,7 +6385,7 @@
         <v>2.08</v>
       </c>
       <c r="AC37">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="AD37">
         <v>1.38</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,68 +6499,68 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
+        <v>1.53</v>
+      </c>
+      <c r="O38">
+        <v>4.6</v>
+      </c>
+      <c r="P38">
+        <v>5.5</v>
+      </c>
+      <c r="Q38">
+        <v>1.93</v>
+      </c>
+      <c r="R38">
+        <v>2.41</v>
+      </c>
+      <c r="S38">
+        <v>1.25</v>
+      </c>
+      <c r="T38">
         <v>3.5</v>
       </c>
-      <c r="O38">
-        <v>3.7</v>
-      </c>
-      <c r="P38">
-        <v>1.95</v>
-      </c>
-      <c r="Q38">
-        <v>4.05</v>
-      </c>
-      <c r="R38">
-        <v>2.3</v>
-      </c>
-      <c r="S38">
-        <v>1.33</v>
-      </c>
-      <c r="T38">
-        <v>3.27</v>
-      </c>
       <c r="U38">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="V38">
+        <v>1.62</v>
+      </c>
+      <c r="W38">
+        <v>1.13</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
+        <v>1.14</v>
+      </c>
+      <c r="Z38">
+        <v>5</v>
+      </c>
+      <c r="AA38">
         <v>1.5</v>
       </c>
-      <c r="W38">
-        <v>1.08</v>
-      </c>
-      <c r="X38">
-        <v>1.04</v>
-      </c>
-      <c r="Y38">
-        <v>1.2</v>
-      </c>
-      <c r="Z38">
-        <v>3.74</v>
-      </c>
-      <c r="AA38">
-        <v>1.74</v>
-      </c>
       <c r="AB38">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AC38">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="AD38">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE38">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF38">
         <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,84 +6662,84 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
-        <v>1.53</v>
+        <v>3.5</v>
       </c>
       <c r="O39">
-        <v>4.6</v>
+        <v>3.52</v>
       </c>
       <c r="P39">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q39">
-        <v>2.02</v>
+        <v>3.6</v>
       </c>
       <c r="R39">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
+        <v>1.34</v>
+      </c>
+      <c r="T39">
+        <v>3.25</v>
+      </c>
+      <c r="U39">
+        <v>2.4</v>
+      </c>
+      <c r="V39">
+        <v>1.5</v>
+      </c>
+      <c r="W39">
+        <v>1.07</v>
+      </c>
+      <c r="X39">
+        <v>1.04</v>
+      </c>
+      <c r="Y39">
+        <v>1.2</v>
+      </c>
+      <c r="Z39">
+        <v>3.62</v>
+      </c>
+      <c r="AA39">
+        <v>1.76</v>
+      </c>
+      <c r="AB39">
+        <v>2.05</v>
+      </c>
+      <c r="AC39">
+        <v>2.8</v>
+      </c>
+      <c r="AD39">
+        <v>1.4</v>
+      </c>
+      <c r="AE39">
+        <v>1.15</v>
+      </c>
+      <c r="AF39">
+        <v>1.6</v>
+      </c>
+      <c r="AG39">
+        <v>2.13</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.25</v>
       </c>
-      <c r="T39">
-        <v>3.5</v>
-      </c>
-      <c r="U39">
-        <v>2.15</v>
-      </c>
-      <c r="V39">
-        <v>1.61</v>
-      </c>
-      <c r="W39">
-        <v>1.13</v>
-      </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.14</v>
-      </c>
-      <c r="Z39">
-        <v>5</v>
-      </c>
-      <c r="AA39">
-        <v>1.5</v>
-      </c>
-      <c r="AB39">
-        <v>2.5</v>
-      </c>
-      <c r="AC39">
-        <v>2.3</v>
-      </c>
-      <c r="AD39">
-        <v>1.57</v>
-      </c>
-      <c r="AE39">
-        <v>1.25</v>
-      </c>
-      <c r="AF39">
-        <v>1.62</v>
-      </c>
-      <c r="AG39">
-        <v>2.25</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.2</v>
-      </c>
       <c r="AK39">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="O48">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="P48">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q48">
         <v>6.5</v>
@@ -8160,7 +8160,7 @@
         <v>1.79</v>
       </c>
       <c r="W48">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8181,7 +8181,7 @@
         <v>1.95</v>
       </c>
       <c r="AD48">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AE48">
         <v>1.33</v>
@@ -8190,7 +8190,7 @@
         <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8631,25 +8631,25 @@
         <v>3.75</v>
       </c>
       <c r="Q51">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="R51">
         <v>2.05</v>
       </c>
       <c r="S51">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U51">
         <v>2.81</v>
       </c>
       <c r="V51">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8664,7 +8664,7 @@
         <v>2.02</v>
       </c>
       <c r="AB51">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC51">
         <v>3.2</v>
@@ -8679,7 +8679,7 @@
         <v>1.85</v>
       </c>
       <c r="AG51">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8800,34 +8800,34 @@
         <v>2.5</v>
       </c>
       <c r="S52">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T52">
         <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W52">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
         <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB52">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC52">
         <v>2.62</v>
@@ -8842,7 +8842,7 @@
         <v>2.15</v>
       </c>
       <c r="AG52">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z54">
         <v>4.2</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10611,25 +10611,25 @@
         <v>1</v>
       </c>
       <c r="Y63">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z63">
         <v>3.84</v>
       </c>
       <c r="AA63">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB63">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC63">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD63">
         <v>1.36</v>
       </c>
       <c r="AE63">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF63">
         <v>1.65</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="O14">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P14">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="Q14">
         <v>1.97</v>
@@ -2606,28 +2606,28 @@
         <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="V14">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
         <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA14">
         <v>1.63</v>
@@ -2642,13 +2642,13 @@
         <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
         <v>1.72</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>3.25</v>
       </c>
       <c r="Q15">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
         <v>2.5</v>
@@ -2781,16 +2781,16 @@
         <v>1.64</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="AA15">
         <v>1.44</v>
@@ -2926,10 +2926,10 @@
         <v>2.47</v>
       </c>
       <c r="Q16">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="R16">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="S16">
         <v>1.28</v>
@@ -2938,10 +2938,10 @@
         <v>3.28</v>
       </c>
       <c r="U16">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="V16">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="W16">
         <v>1.09</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="O29">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="P29">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="Q29">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="U29">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W29">
         <v>1.12</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG29">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="P30">
-        <v>2.01</v>
+        <v>1.34</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5214,19 +5214,19 @@
         <v>0</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U30">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V30">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W30">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>0</v>
@@ -5253,10 +5253,10 @@
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG30">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5377,19 +5377,19 @@
         <v>0</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X31">
         <v>0</v>
@@ -5416,10 +5416,10 @@
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P33">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q33">
-        <v>3.38</v>
+        <v>3.04</v>
       </c>
       <c r="R33">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="U33">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="V33">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z33">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="AA33">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AB33">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="AC33">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="AD33">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF33">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG33">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="O35">
-        <v>4.35</v>
+        <v>3.55</v>
       </c>
       <c r="P35">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="Q35">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="R35">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T35">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="U35">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V35">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="W35">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="AA35">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AB35">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC35">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AD35">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE35">
         <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG35">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="O36">
-        <v>3.55</v>
+        <v>4.35</v>
       </c>
       <c r="P36">
+        <v>5</v>
+      </c>
+      <c r="Q36">
+        <v>2.48</v>
+      </c>
+      <c r="R36">
+        <v>2.38</v>
+      </c>
+      <c r="S36">
+        <v>1.25</v>
+      </c>
+      <c r="T36">
+        <v>3.5</v>
+      </c>
+      <c r="U36">
+        <v>2.7</v>
+      </c>
+      <c r="V36">
+        <v>1.54</v>
+      </c>
+      <c r="W36">
+        <v>1.09</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>1.19</v>
+      </c>
+      <c r="Z36">
         <v>3.65</v>
       </c>
-      <c r="Q36">
-        <v>2.6</v>
-      </c>
-      <c r="R36">
-        <v>2.25</v>
-      </c>
-      <c r="S36">
-        <v>1.34</v>
-      </c>
-      <c r="T36">
-        <v>3.15</v>
-      </c>
-      <c r="U36">
-        <v>2.6</v>
-      </c>
-      <c r="V36">
+      <c r="AA36">
+        <v>1.82</v>
+      </c>
+      <c r="AB36">
+        <v>1.91</v>
+      </c>
+      <c r="AC36">
+        <v>2.45</v>
+      </c>
+      <c r="AD36">
         <v>1.44</v>
-      </c>
-      <c r="W36">
-        <v>1.07</v>
-      </c>
-      <c r="X36">
-        <v>1.02</v>
-      </c>
-      <c r="Y36">
-        <v>1.22</v>
-      </c>
-      <c r="Z36">
-        <v>3.54</v>
-      </c>
-      <c r="AA36">
-        <v>1.76</v>
-      </c>
-      <c r="AB36">
-        <v>2</v>
-      </c>
-      <c r="AC36">
-        <v>2.9</v>
-      </c>
-      <c r="AD36">
-        <v>1.37</v>
       </c>
       <c r="AE36">
         <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG36">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK36">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7976,25 +7976,25 @@
         <v>4.3</v>
       </c>
       <c r="P47">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="Q47">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="R47">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="S47">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T47">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="U47">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="V47">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="W47">
         <v>1.29</v>
@@ -8009,22 +8009,22 @@
         <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AB47">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="AC47">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AD47">
         <v>2.06</v>
       </c>
       <c r="AE47">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AF47">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AG47">
         <v>3.08</v>
@@ -8043,7 +8043,7 @@
         <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="O15">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P15">
-        <v>3.25</v>
+        <v>2.47</v>
       </c>
       <c r="Q15">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S15">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="U15">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V15">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X15">
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="AA15">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AC15">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="AD15">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE15">
+        <v>1.18</v>
+      </c>
+      <c r="AF15">
+        <v>1.42</v>
+      </c>
+      <c r="AG15">
+        <v>2.5</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.22</v>
       </c>
-      <c r="AF15">
-        <v>1.41</v>
-      </c>
-      <c r="AG15">
-        <v>2.55</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.21</v>
-      </c>
       <c r="AK15">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="O16">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P16">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="Q16">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="U16">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V16">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W16">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z16">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="AA16">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB16">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AC16">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="AD16">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG16">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.61</v>
+        <v>3.25</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P28">
-        <v>4.4</v>
+        <v>2.01</v>
       </c>
       <c r="Q28">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="P29">
-        <v>2.01</v>
+        <v>1.34</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5051,19 +5051,19 @@
         <v>0</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V29">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
         <v>0</v>
@@ -5090,10 +5090,10 @@
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG29">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5214,19 +5214,19 @@
         <v>0</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X30">
         <v>0</v>
@@ -5253,10 +5253,10 @@
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.7</v>
+        <v>1.61</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q32">
-        <v>3.38</v>
+        <v>2.2</v>
       </c>
       <c r="R32">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="S32">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U32">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
+        <v>1.21</v>
+      </c>
+      <c r="Z32">
+        <v>3.58</v>
+      </c>
+      <c r="AA32">
+        <v>1.78</v>
+      </c>
+      <c r="AB32">
+        <v>1.93</v>
+      </c>
+      <c r="AC32">
+        <v>2.92</v>
+      </c>
+      <c r="AD32">
+        <v>1.31</v>
+      </c>
+      <c r="AE32">
+        <v>1.08</v>
+      </c>
+      <c r="AF32">
+        <v>1.75</v>
+      </c>
+      <c r="AG32">
+        <v>1.95</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.18</v>
       </c>
-      <c r="Z32">
-        <v>3.88</v>
-      </c>
-      <c r="AA32">
-        <v>1.71</v>
-      </c>
-      <c r="AB32">
-        <v>2.02</v>
-      </c>
-      <c r="AC32">
-        <v>2.74</v>
-      </c>
-      <c r="AD32">
-        <v>1.35</v>
-      </c>
-      <c r="AE32">
-        <v>1.09</v>
-      </c>
-      <c r="AF32">
-        <v>1.57</v>
-      </c>
-      <c r="AG32">
-        <v>2.23</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.23</v>
-      </c>
       <c r="AK32">
-        <v>1.36</v>
+        <v>2.07</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,84 +6499,84 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38">
-        <v>1.53</v>
+        <v>3.5</v>
       </c>
       <c r="O38">
-        <v>4.6</v>
+        <v>3.52</v>
       </c>
       <c r="P38">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q38">
-        <v>1.93</v>
+        <v>3.6</v>
       </c>
       <c r="R38">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
+        <v>1.34</v>
+      </c>
+      <c r="T38">
+        <v>3.25</v>
+      </c>
+      <c r="U38">
+        <v>2.4</v>
+      </c>
+      <c r="V38">
+        <v>1.5</v>
+      </c>
+      <c r="W38">
+        <v>1.07</v>
+      </c>
+      <c r="X38">
+        <v>1.04</v>
+      </c>
+      <c r="Y38">
+        <v>1.2</v>
+      </c>
+      <c r="Z38">
+        <v>3.62</v>
+      </c>
+      <c r="AA38">
+        <v>1.76</v>
+      </c>
+      <c r="AB38">
+        <v>2.05</v>
+      </c>
+      <c r="AC38">
+        <v>2.8</v>
+      </c>
+      <c r="AD38">
+        <v>1.4</v>
+      </c>
+      <c r="AE38">
+        <v>1.15</v>
+      </c>
+      <c r="AF38">
+        <v>1.6</v>
+      </c>
+      <c r="AG38">
+        <v>2.13</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.25</v>
       </c>
-      <c r="T38">
-        <v>3.5</v>
-      </c>
-      <c r="U38">
-        <v>2.15</v>
-      </c>
-      <c r="V38">
-        <v>1.62</v>
-      </c>
-      <c r="W38">
-        <v>1.13</v>
-      </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>1.14</v>
-      </c>
-      <c r="Z38">
-        <v>5</v>
-      </c>
-      <c r="AA38">
-        <v>1.5</v>
-      </c>
-      <c r="AB38">
-        <v>2.5</v>
-      </c>
-      <c r="AC38">
-        <v>2.31</v>
-      </c>
-      <c r="AD38">
-        <v>1.57</v>
-      </c>
-      <c r="AE38">
-        <v>1.25</v>
-      </c>
-      <c r="AF38">
-        <v>1.62</v>
-      </c>
-      <c r="AG38">
-        <v>2.25</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.2</v>
-      </c>
       <c r="AK38">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,84 +6662,84 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
+        <v>1.53</v>
+      </c>
+      <c r="O39">
+        <v>4.6</v>
+      </c>
+      <c r="P39">
+        <v>5.5</v>
+      </c>
+      <c r="Q39">
+        <v>1.93</v>
+      </c>
+      <c r="R39">
+        <v>2.41</v>
+      </c>
+      <c r="S39">
+        <v>1.25</v>
+      </c>
+      <c r="T39">
         <v>3.5</v>
       </c>
-      <c r="O39">
-        <v>3.52</v>
-      </c>
-      <c r="P39">
-        <v>2.05</v>
-      </c>
-      <c r="Q39">
-        <v>3.6</v>
-      </c>
-      <c r="R39">
-        <v>2.3</v>
-      </c>
-      <c r="S39">
-        <v>1.34</v>
-      </c>
-      <c r="T39">
-        <v>3.25</v>
-      </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="V39">
+        <v>1.62</v>
+      </c>
+      <c r="W39">
+        <v>1.13</v>
+      </c>
+      <c r="X39">
+        <v>1.02</v>
+      </c>
+      <c r="Y39">
+        <v>1.14</v>
+      </c>
+      <c r="Z39">
+        <v>5</v>
+      </c>
+      <c r="AA39">
         <v>1.5</v>
       </c>
-      <c r="W39">
-        <v>1.07</v>
-      </c>
-      <c r="X39">
-        <v>1.04</v>
-      </c>
-      <c r="Y39">
+      <c r="AB39">
+        <v>2.5</v>
+      </c>
+      <c r="AC39">
+        <v>2.31</v>
+      </c>
+      <c r="AD39">
+        <v>1.57</v>
+      </c>
+      <c r="AE39">
+        <v>1.25</v>
+      </c>
+      <c r="AF39">
+        <v>1.62</v>
+      </c>
+      <c r="AG39">
+        <v>2.25</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.2</v>
       </c>
-      <c r="Z39">
-        <v>3.62</v>
-      </c>
-      <c r="AA39">
-        <v>1.76</v>
-      </c>
-      <c r="AB39">
-        <v>2.05</v>
-      </c>
-      <c r="AC39">
-        <v>2.8</v>
-      </c>
-      <c r="AD39">
-        <v>1.4</v>
-      </c>
-      <c r="AE39">
-        <v>1.15</v>
-      </c>
-      <c r="AF39">
-        <v>1.6</v>
-      </c>
-      <c r="AG39">
-        <v>2.13</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.25</v>
-      </c>
       <c r="AK39">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="O53">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="P53">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="Q53">
         <v>2.28</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O3">
         <v>2.85</v>
@@ -807,43 +807,43 @@
         <v>3.9</v>
       </c>
       <c r="Q3">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="R3">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S3">
         <v>1.48</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X3">
         <v>1.07</v>
       </c>
       <c r="Y3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z3">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AA3">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AB3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AC3">
-        <v>5.16</v>
+        <v>5.11</v>
       </c>
       <c r="AD3">
         <v>1.13</v>
@@ -852,7 +852,7 @@
         <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG3">
         <v>1.58</v>
@@ -871,7 +871,7 @@
         <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,10 +964,10 @@
         <v>1.75</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P4">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q4">
         <v>2.35</v>
@@ -979,7 +979,7 @@
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="U4">
         <v>2.63</v>
@@ -988,7 +988,7 @@
         <v>1.41</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -997,13 +997,13 @@
         <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AC4">
         <v>3.15</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="P7">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="O8">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.04</v>
+        <v>4.1</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2268,13 +2268,13 @@
         <v>1.95</v>
       </c>
       <c r="O12">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="P12">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q12">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="R12">
         <v>1.94</v>
@@ -2292,7 +2292,7 @@
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
         <v>1.07</v>
@@ -2316,7 +2316,7 @@
         <v>1.12</v>
       </c>
       <c r="AE12">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF12">
         <v>2.14</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.28</v>
+        <v>3.6</v>
       </c>
       <c r="O13">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q13">
         <v>4.2</v>
@@ -2467,10 +2467,10 @@
         <v>4.3</v>
       </c>
       <c r="AA13">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB13">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC13">
         <v>2.5</v>
@@ -3083,10 +3083,10 @@
         <v>1.27</v>
       </c>
       <c r="O17">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="P17">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q17">
         <v>1.56</v>
@@ -3095,10 +3095,10 @@
         <v>3.1</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T17">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="U17">
         <v>1.73</v>
@@ -3107,22 +3107,22 @@
         <v>1.86</v>
       </c>
       <c r="W17">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z17">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA17">
         <v>1.25</v>
       </c>
       <c r="AB17">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="AC17">
         <v>1.7</v>
@@ -3134,7 +3134,7 @@
         <v>1.4</v>
       </c>
       <c r="AF17">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG17">
         <v>2.07</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AK17">
         <v>3.3</v>
@@ -3316,7 +3316,7 @@
         <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3427,13 +3427,13 @@
         <v>3.18</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
         <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
         <v>1.02</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O20">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R20">
         <v>2.33</v>
@@ -3590,10 +3590,10 @@
         <v>3.25</v>
       </c>
       <c r="U20">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V20">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W20">
         <v>1.13</v>
@@ -3642,7 +3642,7 @@
         <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O25">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P25">
         <v>4.1</v>
@@ -4408,7 +4408,7 @@
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W25">
         <v>1.03</v>
@@ -4417,10 +4417,10 @@
         <v>1.09</v>
       </c>
       <c r="Y25">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AA25">
         <v>2.25</v>
@@ -4441,7 +4441,7 @@
         <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>1.15</v>
       </c>
       <c r="O26">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P26">
         <v>11</v>
@@ -4568,7 +4568,7 @@
         <v>4.5</v>
       </c>
       <c r="U26">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V26">
         <v>2</v>
@@ -4583,16 +4583,16 @@
         <v>1.01</v>
       </c>
       <c r="Z26">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="AA26">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AB26">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AC26">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AD26">
         <v>2.3</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK26">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4716,46 +4716,46 @@
         <v>3.25</v>
       </c>
       <c r="P27">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q27">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R27">
         <v>2.14</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T27">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="U27">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z27">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AA27">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB27">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC27">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD27">
         <v>1.36</v>
@@ -4764,10 +4764,10 @@
         <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG27">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O28">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S28">
         <v>1.29</v>
@@ -4894,40 +4894,40 @@
         <v>3.4</v>
       </c>
       <c r="U28">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
         <v>1.53</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG28">
         <v>2.25</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5042,58 +5042,58 @@
         <v>4.7</v>
       </c>
       <c r="P29">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>6.78</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U29">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W29">
         <v>1.11</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG29">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q31">
         <v>3.38</v>
       </c>
       <c r="R31">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="S31">
         <v>1.32</v>
       </c>
       <c r="T31">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
         <v>2.42</v>
@@ -5389,22 +5389,22 @@
         <v>1.47</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X31">
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="AA31">
         <v>1.71</v>
       </c>
       <c r="AB31">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AC31">
         <v>2.74</v>
@@ -5416,7 +5416,7 @@
         <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
         <v>2.23</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
         <v>1.36</v>
@@ -5525,34 +5525,34 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P32">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="Q32">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R32">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T32">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
         <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
         <v>1.04</v>
@@ -5564,10 +5564,10 @@
         <v>3.58</v>
       </c>
       <c r="AA32">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AB32">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC32">
         <v>2.92</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="O33">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="P33">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q33">
         <v>3.04</v>
@@ -5703,49 +5703,49 @@
         <v>2.38</v>
       </c>
       <c r="S33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V33">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z33">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="AA33">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB33">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AC33">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AD33">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE33">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF33">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG33">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,19 +5854,19 @@
         <v>5.11</v>
       </c>
       <c r="O34">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="P34">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q34">
         <v>5.3</v>
       </c>
       <c r="R34">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
         <v>2.91</v>
@@ -5878,7 +5878,7 @@
         <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
         <v>1.05</v>
@@ -5902,7 +5902,7 @@
         <v>1.3</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
         <v>1.8</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="O35">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="P35">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="Q35">
         <v>2.6</v>
@@ -6032,7 +6032,7 @@
         <v>1.34</v>
       </c>
       <c r="T35">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="U35">
         <v>2.6</v>
@@ -6044,7 +6044,7 @@
         <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.22</v>
@@ -6059,16 +6059,16 @@
         <v>2</v>
       </c>
       <c r="AC35">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AD35">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AE35">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
         <v>2.16</v>
@@ -6189,7 +6189,7 @@
         <v>2.48</v>
       </c>
       <c r="R36">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S36">
         <v>1.25</v>
@@ -6204,13 +6204,13 @@
         <v>1.54</v>
       </c>
       <c r="W36">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
         <v>3.65</v>
@@ -6222,10 +6222,10 @@
         <v>1.91</v>
       </c>
       <c r="AC36">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AD36">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE36">
         <v>1.14</v>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P37">
         <v>3.9</v>
       </c>
       <c r="Q37">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="R37">
         <v>2.25</v>
@@ -6361,7 +6361,7 @@
         <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="V37">
         <v>1.46</v>
@@ -6379,19 +6379,19 @@
         <v>4</v>
       </c>
       <c r="AA37">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB37">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC37">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="AD37">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE37">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
         <v>1.62</v>
@@ -6506,7 +6506,7 @@
         <v>3.5</v>
       </c>
       <c r="O38">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
         <v>2.05</v>
@@ -6530,7 +6530,7 @@
         <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
         <v>1.04</v>
@@ -6542,7 +6542,7 @@
         <v>3.62</v>
       </c>
       <c r="AA38">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB38">
         <v>2.05</v>
@@ -6560,7 +6560,7 @@
         <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6690,10 +6690,10 @@
         <v>2.15</v>
       </c>
       <c r="V39">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W39">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7970,25 +7970,25 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="O47">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="P47">
         <v>4.05</v>
       </c>
       <c r="Q47">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="R47">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="S47">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T47">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U47">
         <v>1.71</v>
@@ -8003,19 +8003,19 @@
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Z47">
         <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AB47">
-        <v>3.47</v>
+        <v>3.79</v>
       </c>
       <c r="AC47">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AD47">
         <v>2.06</v>
@@ -8024,10 +8024,10 @@
         <v>1.48</v>
       </c>
       <c r="AF47">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AG47">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="O48">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="P48">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q48">
         <v>6.5</v>
@@ -8154,7 +8154,7 @@
         <v>4.8</v>
       </c>
       <c r="U48">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V48">
         <v>1.79</v>
@@ -8166,7 +8166,7 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z48">
         <v>6.25</v>
@@ -8190,7 +8190,7 @@
         <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8625,22 +8625,22 @@
         <v>1.85</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P51">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
       </c>
       <c r="R51">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U51">
         <v>2.81</v>
@@ -8649,13 +8649,13 @@
         <v>1.36</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
         <v>3.14</v>
@@ -8667,7 +8667,7 @@
         <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD51">
         <v>1.29</v>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,10 +8794,10 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R52">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S52">
         <v>1.28</v>
@@ -8821,13 +8821,13 @@
         <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA52">
         <v>1.7</v>
       </c>
       <c r="AB52">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC52">
         <v>2.62</v>
@@ -8836,13 +8836,13 @@
         <v>1.38</v>
       </c>
       <c r="AE52">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AG52">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>3.8</v>
       </c>
       <c r="Q63">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="R63">
         <v>2.37</v>
@@ -10596,16 +10596,16 @@
         <v>1.29</v>
       </c>
       <c r="T63">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="U63">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="V63">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W63">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
         <v>1</v>
@@ -10614,13 +10614,13 @@
         <v>1.22</v>
       </c>
       <c r="Z63">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AA63">
         <v>1.75</v>
       </c>
       <c r="AB63">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC63">
         <v>2.9</v>
@@ -10629,7 +10629,7 @@
         <v>1.36</v>
       </c>
       <c r="AE63">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF63">
         <v>1.65</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="O14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P14">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q14">
         <v>1.97</v>
@@ -2612,7 +2612,7 @@
         <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V14">
         <v>1.5</v>
@@ -2624,10 +2624,10 @@
         <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA14">
         <v>1.63</v>
@@ -2642,7 +2642,7 @@
         <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF14">
         <v>1.72</v>
@@ -2664,7 +2664,7 @@
         <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>3.55</v>
       </c>
       <c r="P15">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -2769,10 +2769,10 @@
         <v>2.4</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="U15">
         <v>2.14</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="O16">
         <v>3.8</v>
       </c>
       <c r="P16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q16">
         <v>2.3</v>
@@ -2950,10 +2950,10 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z16">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA16">
         <v>1.44</v>
@@ -2962,7 +2962,7 @@
         <v>2.55</v>
       </c>
       <c r="AC16">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AD16">
         <v>1.6</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.27</v>
+        <v>2.6</v>
       </c>
       <c r="O17">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="P17">
-        <v>9.199999999999999</v>
+        <v>2.43</v>
       </c>
       <c r="Q17">
-        <v>1.56</v>
+        <v>3.08</v>
       </c>
       <c r="R17">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="S17">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="U17">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="V17">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z17">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA17">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB17">
-        <v>3.3</v>
+        <v>2.19</v>
       </c>
       <c r="AC17">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD17">
-        <v>1.96</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AG17">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>3.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="O18">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="Q18">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="R18">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T18">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U18">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA18">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB18">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AC18">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AD18">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE18">
         <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AG18">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,52 +3406,52 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="O19">
         <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q19">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S19">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U19">
         <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W19">
         <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z19">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA19">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB19">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AC19">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AD19">
         <v>1.42</v>
@@ -3460,10 +3460,10 @@
         <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG19">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,65 +3569,65 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Q20">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="R20">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U20">
+        <v>2.23</v>
+      </c>
+      <c r="V20">
+        <v>1.5</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>1.15</v>
+      </c>
+      <c r="Z20">
+        <v>4.2</v>
+      </c>
+      <c r="AA20">
+        <v>1.57</v>
+      </c>
+      <c r="AB20">
+        <v>2.17</v>
+      </c>
+      <c r="AC20">
+        <v>2.48</v>
+      </c>
+      <c r="AD20">
+        <v>1.44</v>
+      </c>
+      <c r="AE20">
+        <v>1.14</v>
+      </c>
+      <c r="AF20">
+        <v>1.46</v>
+      </c>
+      <c r="AG20">
         <v>2.25</v>
       </c>
-      <c r="V20">
-        <v>1.49</v>
-      </c>
-      <c r="W20">
-        <v>1.13</v>
-      </c>
-      <c r="X20">
-        <v>1.01</v>
-      </c>
-      <c r="Y20">
-        <v>1.16</v>
-      </c>
-      <c r="Z20">
-        <v>4.1</v>
-      </c>
-      <c r="AA20">
-        <v>1.6</v>
-      </c>
-      <c r="AB20">
-        <v>2.12</v>
-      </c>
-      <c r="AC20">
-        <v>2.55</v>
-      </c>
-      <c r="AD20">
-        <v>1.42</v>
-      </c>
-      <c r="AE20">
-        <v>1.13</v>
-      </c>
-      <c r="AF20">
-        <v>1.45</v>
-      </c>
-      <c r="AG20">
-        <v>2.28</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
+        <v>1.27</v>
+      </c>
+      <c r="O21">
+        <v>5.4</v>
+      </c>
+      <c r="P21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q21">
+        <v>1.56</v>
+      </c>
+      <c r="R21">
         <v>3.1</v>
       </c>
-      <c r="O21">
-        <v>3.7</v>
-      </c>
-      <c r="P21">
-        <v>2.05</v>
-      </c>
-      <c r="Q21">
+      <c r="S21">
+        <v>1.21</v>
+      </c>
+      <c r="T21">
+        <v>3.58</v>
+      </c>
+      <c r="U21">
+        <v>1.73</v>
+      </c>
+      <c r="V21">
+        <v>1.86</v>
+      </c>
+      <c r="W21">
+        <v>1.16</v>
+      </c>
+      <c r="X21">
+        <v>1.01</v>
+      </c>
+      <c r="Y21">
+        <v>1.08</v>
+      </c>
+      <c r="Z21">
+        <v>5.5</v>
+      </c>
+      <c r="AA21">
+        <v>1.25</v>
+      </c>
+      <c r="AB21">
         <v>3.3</v>
       </c>
-      <c r="R21">
-        <v>2.35</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>2.23</v>
-      </c>
-      <c r="V21">
-        <v>1.5</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>1.15</v>
-      </c>
-      <c r="Z21">
-        <v>4.2</v>
-      </c>
-      <c r="AA21">
-        <v>1.57</v>
-      </c>
-      <c r="AB21">
-        <v>2.17</v>
-      </c>
       <c r="AC21">
-        <v>2.48</v>
+        <v>1.7</v>
       </c>
       <c r="AD21">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AF21">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AG21">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AK21">
-        <v>1.28</v>
+        <v>3.3</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>7</v>
+        <v>2.71</v>
       </c>
       <c r="O29">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="P29">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="Q29">
-        <v>6.78</v>
+        <v>3.38</v>
       </c>
       <c r="R29">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T29">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U29">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="V29">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
         <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z29">
-        <v>3.99</v>
+        <v>3.92</v>
       </c>
       <c r="AA29">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AB29">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AC29">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AD29">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG29">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="P31">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q31">
-        <v>3.38</v>
+        <v>3.04</v>
       </c>
       <c r="R31">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="V31">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z31">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="AA31">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="AC31">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="AD31">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AE31">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG31">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
+        <v>7</v>
+      </c>
+      <c r="O32">
+        <v>4.7</v>
+      </c>
+      <c r="P32">
+        <v>1.39</v>
+      </c>
+      <c r="Q32">
+        <v>6.78</v>
+      </c>
+      <c r="R32">
+        <v>2.4</v>
+      </c>
+      <c r="S32">
+        <v>1.29</v>
+      </c>
+      <c r="T32">
+        <v>3.25</v>
+      </c>
+      <c r="U32">
+        <v>2.56</v>
+      </c>
+      <c r="V32">
+        <v>1.48</v>
+      </c>
+      <c r="W32">
+        <v>1.11</v>
+      </c>
+      <c r="X32">
+        <v>1.03</v>
+      </c>
+      <c r="Y32">
+        <v>1.22</v>
+      </c>
+      <c r="Z32">
+        <v>3.99</v>
+      </c>
+      <c r="AA32">
         <v>1.68</v>
       </c>
-      <c r="O32">
-        <v>3.85</v>
-      </c>
-      <c r="P32">
-        <v>4.45</v>
-      </c>
-      <c r="Q32">
-        <v>2.15</v>
-      </c>
-      <c r="R32">
-        <v>2.34</v>
-      </c>
-      <c r="S32">
-        <v>1.34</v>
-      </c>
-      <c r="T32">
-        <v>3.2</v>
-      </c>
-      <c r="U32">
-        <v>2.5</v>
-      </c>
-      <c r="V32">
-        <v>1.43</v>
-      </c>
-      <c r="W32">
-        <v>1.1</v>
-      </c>
-      <c r="X32">
-        <v>1.04</v>
-      </c>
-      <c r="Y32">
-        <v>1.21</v>
-      </c>
-      <c r="Z32">
-        <v>3.58</v>
-      </c>
-      <c r="AA32">
-        <v>1.81</v>
-      </c>
       <c r="AB32">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AC32">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AD32">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE32">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG32">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK32">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.65</v>
+        <v>3.35</v>
       </c>
       <c r="O33">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="Q33">
-        <v>3.04</v>
+        <v>3.88</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U33">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -5721,31 +5721,31 @@
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>4.15</v>
+        <v>4.28</v>
       </c>
       <c r="AA33">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB33">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AC33">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="AD33">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE33">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AG33">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
+        <v>1.22</v>
+      </c>
+      <c r="AK33">
         <v>1.25</v>
-      </c>
-      <c r="AK33">
-        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8957,34 +8957,34 @@
         <v>4.3</v>
       </c>
       <c r="Q53">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R53">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S53">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="U53">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="V53">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
         <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA53">
         <v>1.95</v>
@@ -8999,13 +8999,13 @@
         <v>1.3</v>
       </c>
       <c r="AE53">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG53">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK53">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O54">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P54">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q54">
         <v>2.5</v>
@@ -9129,7 +9129,7 @@
         <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U54">
         <v>2.38</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK54">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AL54">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -964,7 +964,7 @@
         <v>1.75</v>
       </c>
       <c r="O4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P4">
         <v>4.2</v>
@@ -979,7 +979,7 @@
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U4">
         <v>2.63</v>
@@ -1006,7 +1006,7 @@
         <v>1.96</v>
       </c>
       <c r="AC4">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AD4">
         <v>1.3</v>
@@ -1133,37 +1133,37 @@
         <v>1.26</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
         <v>1.15</v>
       </c>
       <c r="Z5">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB5">
         <v>2.4</v>
@@ -1178,10 +1178,10 @@
         <v>1.22</v>
       </c>
       <c r="AF5">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AG5">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -3089,16 +3089,16 @@
         <v>2.43</v>
       </c>
       <c r="Q17">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="R17">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="S17">
         <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U17">
         <v>2.3</v>
@@ -3107,7 +3107,7 @@
         <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3119,10 +3119,10 @@
         <v>4</v>
       </c>
       <c r="AA17">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB17">
-        <v>2.19</v>
+        <v>2.42</v>
       </c>
       <c r="AC17">
         <v>2.6</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AK17">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3258,10 +3258,10 @@
         <v>2.3</v>
       </c>
       <c r="S18">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T18">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
         <v>2.25</v>
@@ -3270,10 +3270,10 @@
         <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
         <v>1.15</v>
@@ -3282,13 +3282,13 @@
         <v>4.2</v>
       </c>
       <c r="AA18">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AB18">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AC18">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AD18">
         <v>1.42</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3424,16 +3424,16 @@
         <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
         <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3457,7 +3457,7 @@
         <v>1.42</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF19">
         <v>1.45</v>
@@ -3584,10 +3584,10 @@
         <v>2.35</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U20">
         <v>2.23</v>
@@ -3596,10 +3596,10 @@
         <v>1.5</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.15</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O21">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="P21">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>1.56</v>
@@ -3768,7 +3768,7 @@
         <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>1.25</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK21">
         <v>3.3</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="O22">
         <v>3.4</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O25">
         <v>3.25</v>
       </c>
       <c r="P25">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -4408,7 +4408,7 @@
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W25">
         <v>1.03</v>
@@ -4550,16 +4550,16 @@
         <v>1.15</v>
       </c>
       <c r="O26">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="P26">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R26">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="S26">
         <v>1.13</v>
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
       </c>
       <c r="R27">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="S27">
         <v>1.34</v>
       </c>
       <c r="T27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
         <v>2.55</v>
@@ -4740,7 +4740,7 @@
         <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
         <v>1.21</v>
@@ -4749,13 +4749,13 @@
         <v>3.58</v>
       </c>
       <c r="AA27">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB27">
         <v>2.05</v>
       </c>
       <c r="AC27">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD27">
         <v>1.36</v>
@@ -4764,10 +4764,10 @@
         <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.71</v>
+        <v>3.35</v>
       </c>
       <c r="O29">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="Q29">
-        <v>3.38</v>
+        <v>3.88</v>
       </c>
       <c r="R29">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="S29">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U29">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V29">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>3.92</v>
+        <v>4.28</v>
       </c>
       <c r="AA29">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AB29">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AC29">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
       <c r="AD29">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF29">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AG29">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
+        <v>1.22</v>
+      </c>
+      <c r="AK29">
         <v>1.25</v>
-      </c>
-      <c r="AK29">
-        <v>1.36</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.68</v>
+        <v>2.71</v>
       </c>
       <c r="O30">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="P30">
-        <v>4.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q30">
-        <v>2.15</v>
+        <v>3.38</v>
       </c>
       <c r="R30">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="S30">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T30">
         <v>3.2</v>
       </c>
       <c r="U30">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="V30">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z30">
-        <v>3.58</v>
+        <v>3.92</v>
       </c>
       <c r="AA30">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AB30">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AC30">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AD30">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.35</v>
+        <v>1.68</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P33">
-        <v>1.94</v>
+        <v>4.45</v>
       </c>
       <c r="Q33">
-        <v>3.88</v>
+        <v>2.15</v>
       </c>
       <c r="R33">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T33">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U33">
         <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z33">
-        <v>4.28</v>
+        <v>3.58</v>
       </c>
       <c r="AA33">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB33">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AC33">
-        <v>2.61</v>
+        <v>2.92</v>
       </c>
       <c r="AD33">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AE33">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="O35">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="Q35">
         <v>2.6</v>
@@ -6032,7 +6032,7 @@
         <v>1.34</v>
       </c>
       <c r="T35">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
         <v>2.6</v>
@@ -6059,10 +6059,10 @@
         <v>2</v>
       </c>
       <c r="AC35">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AD35">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE35">
         <v>1.08</v>
@@ -6180,19 +6180,19 @@
         <v>1.61</v>
       </c>
       <c r="O36">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="P36">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q36">
         <v>2.48</v>
       </c>
       <c r="R36">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
         <v>3.5</v>
@@ -6201,16 +6201,16 @@
         <v>2.7</v>
       </c>
       <c r="V36">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
         <v>3.65</v>
@@ -6222,10 +6222,10 @@
         <v>1.91</v>
       </c>
       <c r="AC36">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="AD36">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE36">
         <v>1.14</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O48">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="P48">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Q48">
         <v>6.5</v>
@@ -8154,7 +8154,7 @@
         <v>4.8</v>
       </c>
       <c r="U48">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V48">
         <v>1.79</v>
@@ -8166,7 +8166,7 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z48">
         <v>6.25</v>
@@ -8190,7 +8190,7 @@
         <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -964,10 +964,10 @@
         <v>1.75</v>
       </c>
       <c r="O4">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="P4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q4">
         <v>2.35</v>
@@ -976,10 +976,10 @@
         <v>2.25</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="U4">
         <v>2.63</v>
@@ -988,7 +988,7 @@
         <v>1.41</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -997,7 +997,7 @@
         <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="AA4">
         <v>1.8</v>
@@ -1012,7 +1012,7 @@
         <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
         <v>1.75</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <v>3</v>
+      </c>
+      <c r="Q6">
+        <v>2.9</v>
+      </c>
+      <c r="R6">
+        <v>1.95</v>
+      </c>
+      <c r="S6">
+        <v>1.44</v>
+      </c>
+      <c r="T6">
+        <v>2.46</v>
+      </c>
+      <c r="U6">
         <v>3.12</v>
       </c>
-      <c r="P6">
-        <v>2.88</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.22</v>
+        <v>1.8</v>
       </c>
       <c r="O7">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P8">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>2.45</v>
+        <v>4.46</v>
       </c>
       <c r="R8">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T8">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="U8">
         <v>3.2</v>
       </c>
       <c r="V8">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>1.38</v>
+      </c>
+      <c r="Z8">
+        <v>2.62</v>
+      </c>
+      <c r="AA8">
+        <v>2.23</v>
+      </c>
+      <c r="AB8">
+        <v>1.57</v>
+      </c>
+      <c r="AC8">
+        <v>4</v>
+      </c>
+      <c r="AD8">
+        <v>1.17</v>
+      </c>
+      <c r="AE8">
         <v>1.02</v>
       </c>
-      <c r="Y8">
-        <v>1.36</v>
-      </c>
-      <c r="Z8">
-        <v>2.7</v>
-      </c>
-      <c r="AA8">
-        <v>2.21</v>
-      </c>
-      <c r="AB8">
-        <v>1.58</v>
-      </c>
-      <c r="AC8">
-        <v>4.15</v>
-      </c>
-      <c r="AD8">
-        <v>1.16</v>
-      </c>
-      <c r="AE8">
-        <v>1.01</v>
-      </c>
       <c r="AF8">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK8">
-        <v>1.84</v>
+        <v>1.22</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="O9">
         <v>3.1</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="Q9">
-        <v>4.46</v>
+        <v>3</v>
       </c>
       <c r="R9">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="S9">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="U9">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="V9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z9">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AA9">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="AB9">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AC9">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="AD9">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2428,61 +2428,61 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P13">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q13">
         <v>4.2</v>
       </c>
       <c r="R13">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U13">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="V13">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="W13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
         <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z13">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA13">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AB13">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AC13">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AD13">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AF13">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
         <v>2.3</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AK13">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,10 +2594,10 @@
         <v>1.44</v>
       </c>
       <c r="O14">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P14">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q14">
         <v>1.97</v>
@@ -2609,7 +2609,7 @@
         <v>1.28</v>
       </c>
       <c r="T14">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U14">
         <v>2.4</v>
@@ -2627,7 +2627,7 @@
         <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA14">
         <v>1.63</v>
@@ -2642,7 +2642,7 @@
         <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
         <v>1.72</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O16">
         <v>3.8</v>
       </c>
       <c r="P16">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q16">
         <v>2.3</v>
@@ -2944,7 +2944,7 @@
         <v>1.64</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>1.03</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
+        <v>1.28</v>
+      </c>
+      <c r="O20">
+        <v>5.6</v>
+      </c>
+      <c r="P20">
+        <v>8</v>
+      </c>
+      <c r="Q20">
+        <v>1.56</v>
+      </c>
+      <c r="R20">
         <v>3.1</v>
       </c>
-      <c r="O20">
-        <v>3.7</v>
-      </c>
-      <c r="P20">
-        <v>2.05</v>
-      </c>
-      <c r="Q20">
-        <v>3.3</v>
-      </c>
-      <c r="R20">
-        <v>2.35</v>
-      </c>
       <c r="S20">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T20">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="U20">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AB20">
-        <v>2.17</v>
+        <v>3.3</v>
       </c>
       <c r="AC20">
-        <v>2.48</v>
+        <v>1.7</v>
       </c>
       <c r="AD20">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="AE20">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AF20">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AG20">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AK20">
-        <v>1.28</v>
+        <v>3.3</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.28</v>
+        <v>3.1</v>
       </c>
       <c r="O21">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
-        <v>8</v>
+        <v>2.05</v>
       </c>
       <c r="Q21">
-        <v>1.56</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="S21">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="T21">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="U21">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="V21">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AA21">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>3.3</v>
+        <v>2.17</v>
       </c>
       <c r="AC21">
-        <v>1.7</v>
+        <v>2.48</v>
       </c>
       <c r="AD21">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="AE21">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AG21">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>3.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4553,10 +4553,10 @@
         <v>8.6</v>
       </c>
       <c r="P26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q26">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R26">
         <v>3.3</v>
@@ -4586,13 +4586,13 @@
         <v>8.5</v>
       </c>
       <c r="AA26">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AB26">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AC26">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AD26">
         <v>2.3</v>
@@ -4722,19 +4722,19 @@
         <v>3.2</v>
       </c>
       <c r="R27">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
         <v>3.3</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V27">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
         <v>1.07</v>
@@ -4749,16 +4749,16 @@
         <v>3.58</v>
       </c>
       <c r="AA27">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB27">
         <v>2.05</v>
       </c>
       <c r="AC27">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD27">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE27">
         <v>1.11</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
         <v>1.44</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P29">
         <v>1.94</v>
@@ -5057,34 +5057,34 @@
         <v>3.4</v>
       </c>
       <c r="U29">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
         <v>1.53</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z29">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="AA29">
         <v>1.64</v>
       </c>
       <c r="AB29">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AC29">
         <v>2.61</v>
       </c>
       <c r="AD29">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE29">
         <v>1.18</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="AK29">
         <v>1.25</v>
@@ -5211,22 +5211,22 @@
         <v>3.38</v>
       </c>
       <c r="R30">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U30">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.03</v>
@@ -5238,16 +5238,16 @@
         <v>3.92</v>
       </c>
       <c r="AA30">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB30">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC30">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD30">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE30">
         <v>1.09</v>
@@ -5256,7 +5256,7 @@
         <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AK30">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="O31">
         <v>3.65</v>
       </c>
       <c r="P31">
-        <v>2.32</v>
+        <v>3.95</v>
       </c>
       <c r="Q31">
-        <v>3.04</v>
+        <v>2.22</v>
       </c>
       <c r="R31">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T31">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U31">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z31">
-        <v>4.15</v>
+        <v>3.58</v>
       </c>
       <c r="AA31">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AB31">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="AC31">
-        <v>2.49</v>
+        <v>2.92</v>
       </c>
       <c r="AD31">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AE31">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF31">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AG31">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK31">
-        <v>1.44</v>
+        <v>2.07</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>2.47</v>
       </c>
       <c r="O32">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="P32">
-        <v>1.39</v>
+        <v>2.49</v>
       </c>
       <c r="Q32">
-        <v>6.78</v>
+        <v>2.9</v>
       </c>
       <c r="R32">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U32">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="V32">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W32">
         <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
+        <v>1.16</v>
+      </c>
+      <c r="Z32">
+        <v>4.15</v>
+      </c>
+      <c r="AA32">
+        <v>1.6</v>
+      </c>
+      <c r="AB32">
+        <v>2.19</v>
+      </c>
+      <c r="AC32">
+        <v>2.49</v>
+      </c>
+      <c r="AD32">
+        <v>1.42</v>
+      </c>
+      <c r="AE32">
+        <v>1.17</v>
+      </c>
+      <c r="AF32">
+        <v>1.53</v>
+      </c>
+      <c r="AG32">
+        <v>2.5</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.22</v>
       </c>
-      <c r="Z32">
-        <v>3.99</v>
-      </c>
-      <c r="AA32">
-        <v>1.68</v>
-      </c>
-      <c r="AB32">
-        <v>2.06</v>
-      </c>
-      <c r="AC32">
-        <v>2.66</v>
-      </c>
-      <c r="AD32">
-        <v>1.37</v>
-      </c>
-      <c r="AE32">
-        <v>1.15</v>
-      </c>
-      <c r="AF32">
-        <v>1.91</v>
-      </c>
-      <c r="AG32">
-        <v>1.78</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.12</v>
-      </c>
       <c r="AK32">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
+        <v>7</v>
+      </c>
+      <c r="O33">
+        <v>4.6</v>
+      </c>
+      <c r="P33">
+        <v>1.39</v>
+      </c>
+      <c r="Q33">
+        <v>6.78</v>
+      </c>
+      <c r="R33">
+        <v>2.4</v>
+      </c>
+      <c r="S33">
+        <v>1.29</v>
+      </c>
+      <c r="T33">
+        <v>3.25</v>
+      </c>
+      <c r="U33">
+        <v>2.56</v>
+      </c>
+      <c r="V33">
+        <v>1.5</v>
+      </c>
+      <c r="W33">
+        <v>1.13</v>
+      </c>
+      <c r="X33">
+        <v>1.03</v>
+      </c>
+      <c r="Y33">
+        <v>1.22</v>
+      </c>
+      <c r="Z33">
+        <v>3.99</v>
+      </c>
+      <c r="AA33">
         <v>1.68</v>
       </c>
-      <c r="O33">
-        <v>3.85</v>
-      </c>
-      <c r="P33">
-        <v>4.45</v>
-      </c>
-      <c r="Q33">
-        <v>2.15</v>
-      </c>
-      <c r="R33">
-        <v>2.34</v>
-      </c>
-      <c r="S33">
-        <v>1.34</v>
-      </c>
-      <c r="T33">
-        <v>3.2</v>
-      </c>
-      <c r="U33">
-        <v>2.5</v>
-      </c>
-      <c r="V33">
-        <v>1.43</v>
-      </c>
-      <c r="W33">
-        <v>1.1</v>
-      </c>
-      <c r="X33">
-        <v>1.04</v>
-      </c>
-      <c r="Y33">
-        <v>1.21</v>
-      </c>
-      <c r="Z33">
-        <v>3.58</v>
-      </c>
-      <c r="AA33">
-        <v>1.81</v>
-      </c>
       <c r="AB33">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AC33">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AD33">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG33">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="AK33">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="Q35">
         <v>2.6</v>
@@ -6029,7 +6029,7 @@
         <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
         <v>3.2</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="O36">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P36">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="Q36">
         <v>2.48</v>
       </c>
       <c r="R36">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
         <v>1.29</v>
@@ -6201,7 +6201,7 @@
         <v>2.7</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
         <v>1.11</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="O41">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P41">
-        <v>2.34</v>
+        <v>3.1</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="O42">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="P42">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P43">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="O44">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P44">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="O45">
         <v>3.45</v>
       </c>
       <c r="P45">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="O46">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P46">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,25 +7970,25 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="O47">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="P47">
-        <v>4.05</v>
+        <v>4.21</v>
       </c>
       <c r="Q47">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="R47">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="S47">
         <v>1.12</v>
       </c>
       <c r="T47">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="U47">
         <v>1.71</v>
@@ -8009,10 +8009,10 @@
         <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AB47">
-        <v>3.79</v>
+        <v>3.87</v>
       </c>
       <c r="AC47">
         <v>1.5</v>
@@ -8957,55 +8957,55 @@
         <v>4.3</v>
       </c>
       <c r="Q53">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R53">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="T53">
-        <v>3.15</v>
+        <v>3.74</v>
       </c>
       <c r="U53">
-        <v>2.47</v>
+        <v>2.08</v>
       </c>
       <c r="V53">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X53">
         <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z53">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA53">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="AB53">
-        <v>1.85</v>
+        <v>2.49</v>
       </c>
       <c r="AC53">
         <v>3.2</v>
       </c>
       <c r="AD53">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE53">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AF53">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AG53">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK53">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AL53">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="O2">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P2">
+        <v>3.9</v>
+      </c>
+      <c r="Q2">
+        <v>2.63</v>
+      </c>
+      <c r="R2">
+        <v>1.96</v>
+      </c>
+      <c r="S2">
+        <v>1.48</v>
+      </c>
+      <c r="T2">
+        <v>2.18</v>
+      </c>
+      <c r="U2">
+        <v>3.8</v>
+      </c>
+      <c r="V2">
+        <v>1.22</v>
+      </c>
+      <c r="W2">
+        <v>1.01</v>
+      </c>
+      <c r="X2">
+        <v>1.07</v>
+      </c>
+      <c r="Y2">
+        <v>1.5</v>
+      </c>
+      <c r="Z2">
+        <v>2.41</v>
+      </c>
+      <c r="AA2">
+        <v>2.63</v>
+      </c>
+      <c r="AB2">
+        <v>1.47</v>
+      </c>
+      <c r="AC2">
+        <v>5.11</v>
+      </c>
+      <c r="AD2">
+        <v>1.11</v>
+      </c>
+      <c r="AE2">
+        <v>1.01</v>
+      </c>
+      <c r="AF2">
         <v>2.1</v>
       </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="O3">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P3">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q3">
-        <v>2.63</v>
+        <v>4.8</v>
       </c>
       <c r="R3">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="S3">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U3">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="V3">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y3">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z3">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AA3">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="AB3">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AC3">
-        <v>5.11</v>
+        <v>6</v>
       </c>
       <c r="AD3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE3">
         <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG3">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="AK3">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1296,25 +1296,25 @@
         <v>3</v>
       </c>
       <c r="Q6">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R6">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S6">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T6">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="U6">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V6">
         <v>1.28</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
         <v>1.04</v>
@@ -1332,7 +1332,7 @@
         <v>1.6</v>
       </c>
       <c r="AC6">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AD6">
         <v>1.18</v>
@@ -1456,7 +1456,7 @@
         <v>3.2</v>
       </c>
       <c r="P7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q7">
         <v>2.45</v>
@@ -1489,10 +1489,10 @@
         <v>2.7</v>
       </c>
       <c r="AA7">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AB7">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC7">
         <v>4.15</v>
@@ -1504,10 +1504,10 @@
         <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG7">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK7">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
         <v>2</v>
@@ -1667,7 +1667,7 @@
         <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG8">
         <v>1.75</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="AK8">
         <v>1.22</v>
@@ -1785,7 +1785,7 @@
         <v>2.9</v>
       </c>
       <c r="Q9">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R9">
         <v>1.97</v>
@@ -1815,7 +1815,7 @@
         <v>2.92</v>
       </c>
       <c r="AA9">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB9">
         <v>1.67</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
+        <v>1.22</v>
+      </c>
+      <c r="O11">
+        <v>5.25</v>
+      </c>
+      <c r="P11">
+        <v>10</v>
+      </c>
+      <c r="Q11">
+        <v>1.67</v>
+      </c>
+      <c r="R11">
+        <v>2.46</v>
+      </c>
+      <c r="S11">
         <v>1.28</v>
       </c>
-      <c r="O11">
-        <v>4.8</v>
-      </c>
-      <c r="P11">
-        <v>8</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O12">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P12">
         <v>4.6</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="O13">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P13">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q13">
         <v>4.2</v>
@@ -2443,7 +2443,7 @@
         <v>2.62</v>
       </c>
       <c r="S13">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T13">
         <v>3.8</v>
@@ -2452,7 +2452,7 @@
         <v>2.18</v>
       </c>
       <c r="V13">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W13">
         <v>1.14</v>
@@ -2461,25 +2461,25 @@
         <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AA13">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB13">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC13">
         <v>2.19</v>
       </c>
       <c r="AD13">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE13">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF13">
         <v>1.44</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>2</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2609,7 +2609,7 @@
         <v>1.28</v>
       </c>
       <c r="T14">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
         <v>2.4</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O15">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
         <v>2.4</v>
@@ -2920,7 +2920,7 @@
         <v>2</v>
       </c>
       <c r="O16">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
         <v>3.4</v>
@@ -3083,16 +3083,16 @@
         <v>2.6</v>
       </c>
       <c r="O17">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="Q17">
-        <v>3.19</v>
+        <v>2.99</v>
       </c>
       <c r="R17">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="S17">
         <v>1.25</v>
@@ -3110,7 +3110,7 @@
         <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
         <v>1.16</v>
@@ -3122,7 +3122,7 @@
         <v>1.44</v>
       </c>
       <c r="AB17">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AC17">
         <v>2.6</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
         <v>1.44</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O18">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q18">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S18">
         <v>1.26</v>
@@ -3270,7 +3270,7 @@
         <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3288,7 +3288,7 @@
         <v>2.29</v>
       </c>
       <c r="AC18">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AD18">
         <v>1.42</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
         <v>2.37</v>
@@ -3421,22 +3421,22 @@
         <v>2.33</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W19">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.16</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
         <v>1.37</v>
@@ -3584,10 +3584,10 @@
         <v>3.1</v>
       </c>
       <c r="S20">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="T20">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="U20">
         <v>1.73</v>
@@ -3596,7 +3596,7 @@
         <v>1.86</v>
       </c>
       <c r="W20">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3605,7 +3605,7 @@
         <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA20">
         <v>1.25</v>
@@ -3623,7 +3623,7 @@
         <v>1.4</v>
       </c>
       <c r="AF20">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG20">
         <v>2.07</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O21">
         <v>3.7</v>
       </c>
       <c r="P21">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q21">
         <v>3.3</v>
@@ -3898,7 +3898,7 @@
         <v>2.04</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="P22">
         <v>3.6</v>
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="O25">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="P25">
         <v>4.25</v>
@@ -4441,7 +4441,7 @@
         <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="O26">
         <v>8.6</v>
       </c>
       <c r="P26">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q26">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="R26">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="S26">
         <v>1.13</v>
@@ -4568,7 +4568,7 @@
         <v>4.5</v>
       </c>
       <c r="U26">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V26">
         <v>2</v>
@@ -4577,7 +4577,7 @@
         <v>1.29</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.01</v>
@@ -4592,7 +4592,7 @@
         <v>4.2</v>
       </c>
       <c r="AC26">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AD26">
         <v>2.3</v>
@@ -4601,10 +4601,10 @@
         <v>1.55</v>
       </c>
       <c r="AF26">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.87</v>
+        <v>2.71</v>
       </c>
       <c r="O28">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P28">
-        <v>3.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q28">
-        <v>2.27</v>
+        <v>3.38</v>
       </c>
       <c r="R28">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
         <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U28">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z28">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="AA28">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB28">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="AD28">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE28">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="AK28">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="O29">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P29">
-        <v>1.94</v>
+        <v>3.95</v>
       </c>
       <c r="Q29">
-        <v>3.88</v>
+        <v>2.22</v>
       </c>
       <c r="R29">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T29">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V29">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
+        <v>1.1</v>
+      </c>
+      <c r="X29">
+        <v>1.04</v>
+      </c>
+      <c r="Y29">
+        <v>1.21</v>
+      </c>
+      <c r="Z29">
+        <v>3.58</v>
+      </c>
+      <c r="AA29">
+        <v>1.81</v>
+      </c>
+      <c r="AB29">
+        <v>1.98</v>
+      </c>
+      <c r="AC29">
+        <v>2.92</v>
+      </c>
+      <c r="AD29">
+        <v>1.31</v>
+      </c>
+      <c r="AE29">
         <v>1.12</v>
       </c>
-      <c r="X29">
-        <v>1.02</v>
-      </c>
-      <c r="Y29">
-        <v>1.17</v>
-      </c>
-      <c r="Z29">
-        <v>4</v>
-      </c>
-      <c r="AA29">
-        <v>1.64</v>
-      </c>
-      <c r="AB29">
-        <v>2.18</v>
-      </c>
-      <c r="AC29">
-        <v>2.61</v>
-      </c>
-      <c r="AD29">
-        <v>1.46</v>
-      </c>
-      <c r="AE29">
+      <c r="AF29">
+        <v>1.75</v>
+      </c>
+      <c r="AG29">
+        <v>1.95</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.18</v>
       </c>
-      <c r="AF29">
-        <v>1.56</v>
-      </c>
-      <c r="AG29">
-        <v>2.25</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.72</v>
-      </c>
       <c r="AK29">
-        <v>1.25</v>
+        <v>2.07</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.71</v>
+        <v>2.47</v>
       </c>
       <c r="O30">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="P30">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="Q30">
-        <v>3.38</v>
+        <v>2.9</v>
       </c>
       <c r="R30">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U30">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W30">
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z30">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="AA30">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AC30">
-        <v>2.78</v>
+        <v>2.49</v>
       </c>
       <c r="AD30">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
+        <v>7</v>
+      </c>
+      <c r="O31">
+        <v>4.6</v>
+      </c>
+      <c r="P31">
+        <v>1.39</v>
+      </c>
+      <c r="Q31">
+        <v>6.78</v>
+      </c>
+      <c r="R31">
+        <v>2.4</v>
+      </c>
+      <c r="S31">
+        <v>1.29</v>
+      </c>
+      <c r="T31">
+        <v>3.25</v>
+      </c>
+      <c r="U31">
+        <v>2.56</v>
+      </c>
+      <c r="V31">
+        <v>1.5</v>
+      </c>
+      <c r="W31">
+        <v>1.13</v>
+      </c>
+      <c r="X31">
+        <v>1.03</v>
+      </c>
+      <c r="Y31">
+        <v>1.22</v>
+      </c>
+      <c r="Z31">
+        <v>3.99</v>
+      </c>
+      <c r="AA31">
         <v>1.68</v>
       </c>
-      <c r="O31">
-        <v>3.65</v>
-      </c>
-      <c r="P31">
-        <v>3.95</v>
-      </c>
-      <c r="Q31">
-        <v>2.22</v>
-      </c>
-      <c r="R31">
-        <v>2.34</v>
-      </c>
-      <c r="S31">
-        <v>1.34</v>
-      </c>
-      <c r="T31">
-        <v>3.1</v>
-      </c>
-      <c r="U31">
-        <v>2.5</v>
-      </c>
-      <c r="V31">
-        <v>1.44</v>
-      </c>
-      <c r="W31">
-        <v>1.1</v>
-      </c>
-      <c r="X31">
-        <v>1.04</v>
-      </c>
-      <c r="Y31">
-        <v>1.21</v>
-      </c>
-      <c r="Z31">
-        <v>3.58</v>
-      </c>
-      <c r="AA31">
-        <v>1.81</v>
-      </c>
       <c r="AB31">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AC31">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AD31">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE31">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG31">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.18</v>
+        <v>2.88</v>
       </c>
       <c r="AK31">
-        <v>2.07</v>
+        <v>1.03</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,37 +5525,37 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.47</v>
+        <v>1.87</v>
       </c>
       <c r="O32">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P32">
-        <v>2.49</v>
+        <v>3.55</v>
       </c>
       <c r="Q32">
-        <v>2.9</v>
+        <v>2.27</v>
       </c>
       <c r="R32">
         <v>2.32</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="V32">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.16</v>
@@ -5564,25 +5564,25 @@
         <v>4.15</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB32">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AC32">
-        <v>2.49</v>
+        <v>2.72</v>
       </c>
       <c r="AD32">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE32">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF32">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG32">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK32">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="O33">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="P33">
-        <v>1.39</v>
+        <v>1.94</v>
       </c>
       <c r="Q33">
-        <v>6.78</v>
+        <v>3.88</v>
       </c>
       <c r="R33">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S33">
         <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U33">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="V33">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W33">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z33">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="AA33">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB33">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AC33">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="AD33">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AE33">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AG33">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>2.88</v>
+        <v>1.72</v>
       </c>
       <c r="AK33">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>5.11</v>
+        <v>4.6</v>
       </c>
       <c r="O34">
         <v>3.9</v>
@@ -5860,7 +5860,7 @@
         <v>1.54</v>
       </c>
       <c r="Q34">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="R34">
         <v>2.25</v>
@@ -5875,7 +5875,7 @@
         <v>2.75</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W34">
         <v>1.04</v>
@@ -5924,7 +5924,7 @@
         <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6382,7 +6382,7 @@
         <v>1.71</v>
       </c>
       <c r="AB37">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC37">
         <v>2.61</v>
@@ -6506,7 +6506,7 @@
         <v>3.5</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P38">
         <v>2.05</v>
@@ -6539,10 +6539,10 @@
         <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA38">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB38">
         <v>2.05</v>
@@ -6557,10 +6557,10 @@
         <v>1.15</v>
       </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>1.53</v>
       </c>
       <c r="O39">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P39">
         <v>5.5</v>
@@ -6690,10 +6690,10 @@
         <v>2.15</v>
       </c>
       <c r="V39">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W39">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6720,7 +6720,7 @@
         <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
         <v>2.25</v>
@@ -7538,7 +7538,7 @@
         <v>1.96</v>
       </c>
       <c r="AG44">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7653,10 +7653,10 @@
         <v>4</v>
       </c>
       <c r="Q45">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R45">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S45">
         <v>1.36</v>
@@ -7665,7 +7665,7 @@
         <v>2.75</v>
       </c>
       <c r="U45">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="V45">
         <v>1.38</v>
@@ -7689,10 +7689,10 @@
         <v>1.76</v>
       </c>
       <c r="AC45">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD45">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE45">
         <v>1.06</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
         <v>1.82</v>
@@ -7810,13 +7810,13 @@
         <v>2.85</v>
       </c>
       <c r="O46">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P46">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q46">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="R46">
         <v>2.02</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>9.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O48">
-        <v>5.55</v>
+        <v>6.2</v>
       </c>
       <c r="P48">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Q48">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R48">
         <v>2.8</v>
@@ -8154,7 +8154,7 @@
         <v>4.8</v>
       </c>
       <c r="U48">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V48">
         <v>1.79</v>
@@ -8166,7 +8166,7 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z48">
         <v>6.25</v>
@@ -8190,7 +8190,7 @@
         <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8305,55 +8305,55 @@
         <v>2.8</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>1.71</v>
+      </c>
+      <c r="R51">
+        <v>2.55</v>
+      </c>
+      <c r="S51">
+        <v>1.3</v>
+      </c>
+      <c r="T51">
+        <v>3.4</v>
+      </c>
+      <c r="U51">
+        <v>2.34</v>
+      </c>
+      <c r="V51">
+        <v>1.5</v>
+      </c>
+      <c r="W51">
+        <v>1.1</v>
+      </c>
+      <c r="X51">
+        <v>1.02</v>
+      </c>
+      <c r="Y51">
+        <v>1.22</v>
+      </c>
+      <c r="Z51">
+        <v>4.1</v>
+      </c>
+      <c r="AA51">
+        <v>1.7</v>
+      </c>
+      <c r="AB51">
+        <v>2.04</v>
+      </c>
+      <c r="AC51">
+        <v>2.62</v>
+      </c>
+      <c r="AD51">
+        <v>1.38</v>
+      </c>
+      <c r="AE51">
+        <v>1.13</v>
+      </c>
+      <c r="AF51">
+        <v>2.16</v>
+      </c>
+      <c r="AG51">
+        <v>1.62</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.04</v>
+      </c>
+      <c r="AK51">
         <v>3.6</v>
-      </c>
-      <c r="Q51">
-        <v>2.5</v>
-      </c>
-      <c r="R51">
-        <v>2.04</v>
-      </c>
-      <c r="S51">
-        <v>1.4</v>
-      </c>
-      <c r="T51">
-        <v>2.9</v>
-      </c>
-      <c r="U51">
-        <v>2.81</v>
-      </c>
-      <c r="V51">
-        <v>1.36</v>
-      </c>
-      <c r="W51">
-        <v>1.06</v>
-      </c>
-      <c r="X51">
-        <v>1.01</v>
-      </c>
-      <c r="Y51">
-        <v>1.3</v>
-      </c>
-      <c r="Z51">
-        <v>3.14</v>
-      </c>
-      <c r="AA51">
-        <v>2.02</v>
-      </c>
-      <c r="AB51">
-        <v>1.83</v>
-      </c>
-      <c r="AC51">
-        <v>3.48</v>
-      </c>
-      <c r="AD51">
-        <v>1.29</v>
-      </c>
-      <c r="AE51">
-        <v>1.08</v>
-      </c>
-      <c r="AF51">
-        <v>1.85</v>
-      </c>
-      <c r="AG51">
-        <v>1.91</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.25</v>
-      </c>
-      <c r="AK51">
-        <v>1.8</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q52">
-        <v>1.71</v>
+        <v>2.37</v>
       </c>
       <c r="R52">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="S52">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="U52">
-        <v>2.34</v>
+        <v>2.81</v>
       </c>
       <c r="V52">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z52">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA52">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AB52">
-        <v>2.09</v>
+        <v>1.76</v>
       </c>
       <c r="AC52">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AD52">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE52">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="AG52">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>3.52</v>
+        <v>1.8</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,10 +8957,10 @@
         <v>4.3</v>
       </c>
       <c r="Q53">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R53">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="S53">
         <v>1.19</v>
@@ -8969,10 +8969,10 @@
         <v>3.74</v>
       </c>
       <c r="U53">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V53">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="W53">
         <v>1.15</v>
@@ -8984,7 +8984,7 @@
         <v>1.14</v>
       </c>
       <c r="Z53">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA53">
         <v>1.42</v>
@@ -8993,7 +8993,7 @@
         <v>2.49</v>
       </c>
       <c r="AC53">
-        <v>3.2</v>
+        <v>2.17</v>
       </c>
       <c r="AD53">
         <v>1.67</v>
@@ -9129,16 +9129,16 @@
         <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U54">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="V54">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W54">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X54">
         <v>1.01</v>
@@ -9184,7 +9184,7 @@
         <v>1.21</v>
       </c>
       <c r="AK54">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10581,28 +10581,28 @@
         <v>1.8</v>
       </c>
       <c r="O63">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="P63">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="Q63">
         <v>2.37</v>
       </c>
       <c r="R63">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="S63">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T63">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U63">
         <v>2.53</v>
       </c>
       <c r="V63">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W63">
         <v>1.08</v>
@@ -10611,7 +10611,7 @@
         <v>1</v>
       </c>
       <c r="Y63">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z63">
         <v>3.82</v>
@@ -10620,22 +10620,22 @@
         <v>1.75</v>
       </c>
       <c r="AB63">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AC63">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AD63">
         <v>1.36</v>
       </c>
       <c r="AE63">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF63">
         <v>1.65</v>
       </c>
       <c r="AG63">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P2">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q2">
-        <v>2.63</v>
+        <v>4.8</v>
       </c>
       <c r="R2">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="S2">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="T2">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U2">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="V2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W2">
         <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y2">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z2">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AA2">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="AB2">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AC2">
-        <v>5.11</v>
+        <v>6</v>
       </c>
       <c r="AD2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG2">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="AK2">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="O3">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P3">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q3">
-        <v>4.8</v>
+        <v>2.63</v>
       </c>
       <c r="R3">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="S3">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="T3">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
         <v>1.01</v>
       </c>
       <c r="X3">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="Z3">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AA3">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="AB3">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AC3">
-        <v>6</v>
+        <v>5.11</v>
       </c>
       <c r="AD3">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG3">
+        <v>1.58</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.28</v>
+      </c>
+      <c r="AK3">
         <v>1.65</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.61</v>
-      </c>
-      <c r="AK3">
-        <v>1.17</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -979,13 +979,13 @@
         <v>1.34</v>
       </c>
       <c r="T4">
-        <v>2.82</v>
+        <v>3.16</v>
       </c>
       <c r="U4">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="V4">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
         <v>1.07</v>
@@ -1006,7 +1006,7 @@
         <v>1.96</v>
       </c>
       <c r="AC4">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AD4">
         <v>1.3</v>
@@ -1015,10 +1015,10 @@
         <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK4">
         <v>1.88</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>8.15</v>
+        <v>7.75</v>
       </c>
       <c r="O5">
-        <v>4.85</v>
+        <v>4.7</v>
       </c>
       <c r="P5">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Q5">
-        <v>6.9</v>
+        <v>7.36</v>
       </c>
       <c r="R5">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="S5">
         <v>1.22</v>
       </c>
       <c r="T5">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="U5">
         <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W5">
         <v>1.13</v>
@@ -1157,31 +1157,31 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z5">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB5">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC5">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AD5">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE5">
         <v>1.22</v>
       </c>
       <c r="AF5">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         <v>2.8</v>
       </c>
       <c r="O10">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
         <v>2.46</v>
@@ -2594,10 +2594,10 @@
         <v>1.44</v>
       </c>
       <c r="O14">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="P14">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="Q14">
         <v>1.97</v>
@@ -2615,7 +2615,7 @@
         <v>2.4</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W14">
         <v>1.11</v>
@@ -2627,7 +2627,7 @@
         <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA14">
         <v>1.63</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK14">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,19 +2763,19 @@
         <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>2.8</v>
+        <v>3.13</v>
       </c>
       <c r="R15">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="V15">
         <v>1.61</v>
@@ -2790,10 +2790,10 @@
         <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AA15">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB15">
         <v>2.25</v>
@@ -2932,10 +2932,10 @@
         <v>2.5</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T16">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U16">
         <v>2.2</v>
@@ -2950,10 +2950,10 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA16">
         <v>1.44</v>
@@ -3080,37 +3080,37 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P17">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q17">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="R17">
         <v>2.42</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="W17">
         <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.16</v>
@@ -3134,10 +3134,10 @@
         <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AG17">
-        <v>2.23</v>
+        <v>2.66</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
         <v>1.44</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q18">
         <v>3.15</v>
       </c>
       <c r="R18">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
         <v>1.26</v>
@@ -3264,10 +3264,10 @@
         <v>3.2</v>
       </c>
       <c r="U18">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W18">
         <v>1.15</v>
@@ -3279,7 +3279,7 @@
         <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA18">
         <v>1.55</v>
@@ -3288,19 +3288,19 @@
         <v>2.29</v>
       </c>
       <c r="AC18">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AD18">
         <v>1.42</v>
       </c>
       <c r="AE18">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF18">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,22 +3409,22 @@
         <v>2.35</v>
       </c>
       <c r="O19">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q19">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="R19">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S19">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T19">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="U19">
         <v>2.1</v>
@@ -3436,7 +3436,7 @@
         <v>1.17</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
         <v>1.16</v>
@@ -3457,13 +3457,13 @@
         <v>1.42</v>
       </c>
       <c r="AE19">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AF19">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AG19">
-        <v>2.28</v>
+        <v>2.95</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="O20">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="P20">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="Q20">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R20">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="S20">
         <v>1.15</v>
@@ -3590,37 +3590,37 @@
         <v>3</v>
       </c>
       <c r="U20">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="V20">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z20">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AA20">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB20">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AC20">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD20">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="AE20">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AF20">
         <v>1.69</v>
@@ -3732,22 +3732,22 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="O21">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="R21">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
         <v>3.55</v>
@@ -3756,31 +3756,31 @@
         <v>2.23</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB21">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AC21">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AD21">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE21">
         <v>1.14</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.21</v>
+        <v>1.68</v>
       </c>
       <c r="AK21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="O22">
         <v>3.33</v>
       </c>
       <c r="P22">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q22">
         <v>2.45</v>
@@ -3910,16 +3910,16 @@
         <v>2.25</v>
       </c>
       <c r="S22">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="U22">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
         <v>1.09</v>
@@ -3928,10 +3928,10 @@
         <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AA22">
         <v>1.91</v>
@@ -3940,10 +3940,10 @@
         <v>1.86</v>
       </c>
       <c r="AC22">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="AD22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE22">
         <v>1.1</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK22">
         <v>1.86</v>
@@ -4067,34 +4067,34 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
         <v>1.33</v>
       </c>
       <c r="T23">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V23">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
         <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA23">
         <v>1.8</v>
@@ -4103,19 +4103,19 @@
         <v>1.9</v>
       </c>
       <c r="AC23">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD23">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG23">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK23">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>3.13</v>
       </c>
       <c r="P25">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -4408,7 +4408,7 @@
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
         <v>1.03</v>
@@ -4441,7 +4441,7 @@
         <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O27">
         <v>3.45</v>
@@ -4722,31 +4722,31 @@
         <v>3.2</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="S27">
         <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U27">
         <v>2.45</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W27">
         <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
         <v>1.21</v>
       </c>
       <c r="Z27">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA27">
         <v>1.77</v>
@@ -4755,19 +4755,19 @@
         <v>2.05</v>
       </c>
       <c r="AC27">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AD27">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
         <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,25 +4873,25 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.71</v>
+        <v>1.68</v>
       </c>
       <c r="O28">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="P28">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="Q28">
-        <v>3.38</v>
+        <v>2.22</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U28">
         <v>2.5</v>
@@ -4900,37 +4900,37 @@
         <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z28">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="AA28">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AB28">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC28">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AD28">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG28">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>1.37</v>
+        <v>2.07</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,65 +5036,65 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.68</v>
+        <v>2.47</v>
       </c>
       <c r="O29">
         <v>3.65</v>
       </c>
       <c r="P29">
-        <v>3.95</v>
+        <v>2.49</v>
       </c>
       <c r="Q29">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="R29">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="S29">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U29">
+        <v>2.53</v>
+      </c>
+      <c r="V29">
+        <v>1.49</v>
+      </c>
+      <c r="W29">
+        <v>1.11</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>1.16</v>
+      </c>
+      <c r="Z29">
+        <v>4.15</v>
+      </c>
+      <c r="AA29">
+        <v>1.6</v>
+      </c>
+      <c r="AB29">
+        <v>2.19</v>
+      </c>
+      <c r="AC29">
+        <v>2.49</v>
+      </c>
+      <c r="AD29">
+        <v>1.42</v>
+      </c>
+      <c r="AE29">
+        <v>1.17</v>
+      </c>
+      <c r="AF29">
+        <v>1.53</v>
+      </c>
+      <c r="AG29">
         <v>2.5</v>
       </c>
-      <c r="V29">
-        <v>1.44</v>
-      </c>
-      <c r="W29">
-        <v>1.1</v>
-      </c>
-      <c r="X29">
-        <v>1.04</v>
-      </c>
-      <c r="Y29">
-        <v>1.21</v>
-      </c>
-      <c r="Z29">
-        <v>3.58</v>
-      </c>
-      <c r="AA29">
-        <v>1.81</v>
-      </c>
-      <c r="AB29">
-        <v>1.98</v>
-      </c>
-      <c r="AC29">
-        <v>2.92</v>
-      </c>
-      <c r="AD29">
-        <v>1.31</v>
-      </c>
-      <c r="AE29">
-        <v>1.12</v>
-      </c>
-      <c r="AF29">
-        <v>1.75</v>
-      </c>
-      <c r="AG29">
-        <v>1.95</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="O30">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P30">
-        <v>2.49</v>
+        <v>1.94</v>
       </c>
       <c r="Q30">
-        <v>2.9</v>
+        <v>3.88</v>
       </c>
       <c r="R30">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="S30">
+        <v>1.29</v>
+      </c>
+      <c r="T30">
+        <v>3.4</v>
+      </c>
+      <c r="U30">
+        <v>2.4</v>
+      </c>
+      <c r="V30">
+        <v>1.53</v>
+      </c>
+      <c r="W30">
+        <v>1.12</v>
+      </c>
+      <c r="X30">
+        <v>1.02</v>
+      </c>
+      <c r="Y30">
+        <v>1.17</v>
+      </c>
+      <c r="Z30">
+        <v>4</v>
+      </c>
+      <c r="AA30">
+        <v>1.64</v>
+      </c>
+      <c r="AB30">
+        <v>2.18</v>
+      </c>
+      <c r="AC30">
+        <v>2.61</v>
+      </c>
+      <c r="AD30">
+        <v>1.46</v>
+      </c>
+      <c r="AE30">
+        <v>1.18</v>
+      </c>
+      <c r="AF30">
+        <v>1.56</v>
+      </c>
+      <c r="AG30">
+        <v>2.25</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.72</v>
+      </c>
+      <c r="AK30">
         <v>1.25</v>
-      </c>
-      <c r="T30">
-        <v>3.5</v>
-      </c>
-      <c r="U30">
-        <v>2.53</v>
-      </c>
-      <c r="V30">
-        <v>1.49</v>
-      </c>
-      <c r="W30">
-        <v>1.11</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.16</v>
-      </c>
-      <c r="Z30">
-        <v>4.15</v>
-      </c>
-      <c r="AA30">
-        <v>1.6</v>
-      </c>
-      <c r="AB30">
-        <v>2.19</v>
-      </c>
-      <c r="AC30">
-        <v>2.49</v>
-      </c>
-      <c r="AD30">
-        <v>1.42</v>
-      </c>
-      <c r="AE30">
-        <v>1.17</v>
-      </c>
-      <c r="AF30">
-        <v>1.53</v>
-      </c>
-      <c r="AG30">
-        <v>2.5</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.22</v>
-      </c>
-      <c r="AK30">
-        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>7</v>
+        <v>2.71</v>
       </c>
       <c r="O31">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="Q31">
-        <v>6.78</v>
+        <v>3.38</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
         <v>3.25</v>
       </c>
       <c r="U31">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>3.99</v>
+        <v>3.92</v>
       </c>
       <c r="AA31">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB31">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC31">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AD31">
+        <v>1.34</v>
+      </c>
+      <c r="AE31">
+        <v>1.09</v>
+      </c>
+      <c r="AF31">
+        <v>1.62</v>
+      </c>
+      <c r="AG31">
+        <v>2.21</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.49</v>
+      </c>
+      <c r="AK31">
         <v>1.37</v>
-      </c>
-      <c r="AE31">
-        <v>1.11</v>
-      </c>
-      <c r="AF31">
-        <v>1.85</v>
-      </c>
-      <c r="AG31">
-        <v>1.85</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>2.88</v>
-      </c>
-      <c r="AK31">
-        <v>1.03</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="P33">
-        <v>1.94</v>
+        <v>1.39</v>
       </c>
       <c r="Q33">
-        <v>3.88</v>
+        <v>6.78</v>
       </c>
       <c r="R33">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S33">
         <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U33">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="V33">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="AA33">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB33">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AC33">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="AD33">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AE33">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AG33">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.72</v>
+        <v>2.88</v>
       </c>
       <c r="AK33">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="O44">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q44">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="R44">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S44">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="U44">
-        <v>3.34</v>
+        <v>2.68</v>
       </c>
       <c r="V44">
+        <v>1.38</v>
+      </c>
+      <c r="W44">
+        <v>1.07</v>
+      </c>
+      <c r="X44">
+        <v>1.02</v>
+      </c>
+      <c r="Y44">
+        <v>1.28</v>
+      </c>
+      <c r="Z44">
+        <v>3.08</v>
+      </c>
+      <c r="AA44">
+        <v>2</v>
+      </c>
+      <c r="AB44">
+        <v>1.76</v>
+      </c>
+      <c r="AC44">
+        <v>3.2</v>
+      </c>
+      <c r="AD44">
+        <v>1.26</v>
+      </c>
+      <c r="AE44">
+        <v>1.06</v>
+      </c>
+      <c r="AF44">
+        <v>1.81</v>
+      </c>
+      <c r="AG44">
+        <v>1.86</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
         <v>1.25</v>
       </c>
-      <c r="W44">
-        <v>1.02</v>
-      </c>
-      <c r="X44">
-        <v>1.03</v>
-      </c>
-      <c r="Y44">
-        <v>1.4</v>
-      </c>
-      <c r="Z44">
-        <v>2.56</v>
-      </c>
-      <c r="AA44">
-        <v>2.34</v>
-      </c>
-      <c r="AB44">
-        <v>1.52</v>
-      </c>
-      <c r="AC44">
-        <v>4.5</v>
-      </c>
-      <c r="AD44">
-        <v>1.13</v>
-      </c>
-      <c r="AE44">
-        <v>1.01</v>
-      </c>
-      <c r="AF44">
-        <v>1.96</v>
-      </c>
-      <c r="AG44">
-        <v>1.73</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.29</v>
-      </c>
       <c r="AK44">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="O45">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P45">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="Q45">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="R45">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S45">
+        <v>1.37</v>
+      </c>
+      <c r="T45">
+        <v>2.71</v>
+      </c>
+      <c r="U45">
+        <v>2.75</v>
+      </c>
+      <c r="V45">
         <v>1.36</v>
       </c>
-      <c r="T45">
-        <v>2.75</v>
-      </c>
-      <c r="U45">
-        <v>2.68</v>
-      </c>
-      <c r="V45">
-        <v>1.38</v>
-      </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AA45">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB45">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC45">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD45">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE45">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AG45">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>1.82</v>
+        <v>1.34</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="O46">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P46">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Q46">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="R46">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="S46">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="T46">
-        <v>2.71</v>
+        <v>2.36</v>
       </c>
       <c r="U46">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="V46">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W46">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z46">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="AA46">
-        <v>2.01</v>
+        <v>2.34</v>
       </c>
       <c r="AB46">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AC46">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="AD46">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AE46">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF46">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AG46">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="O47">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>4.21</v>
+        <v>3.28</v>
       </c>
       <c r="Q47">
         <v>2.05</v>
@@ -7991,10 +7991,10 @@
         <v>4.85</v>
       </c>
       <c r="U47">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="V47">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="W47">
         <v>1.29</v>
@@ -8018,7 +8018,7 @@
         <v>1.5</v>
       </c>
       <c r="AD47">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="AE47">
         <v>1.48</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="O48">
         <v>6.2</v>
       </c>
       <c r="P48">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Q48">
         <v>7</v>
@@ -8148,19 +8148,19 @@
         <v>2.8</v>
       </c>
       <c r="S48">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T48">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U48">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="V48">
         <v>1.79</v>
       </c>
       <c r="W48">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8169,7 +8169,7 @@
         <v>1.06</v>
       </c>
       <c r="Z48">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="AA48">
         <v>1.36</v>
@@ -8181,16 +8181,16 @@
         <v>1.95</v>
       </c>
       <c r="AD48">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AE48">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF48">
         <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8311,10 +8311,10 @@
         <v>2.2</v>
       </c>
       <c r="S49">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
         <v>2.59</v>
@@ -8954,13 +8954,13 @@
         <v>3.32</v>
       </c>
       <c r="P53">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q53">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="R53">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="S53">
         <v>1.19</v>
@@ -8969,10 +8969,10 @@
         <v>3.74</v>
       </c>
       <c r="U53">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V53">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="W53">
         <v>1.15</v>
@@ -8987,10 +8987,10 @@
         <v>5.1</v>
       </c>
       <c r="AA53">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB53">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AC53">
         <v>2.17</v>
@@ -9005,7 +9005,7 @@
         <v>1.44</v>
       </c>
       <c r="AG53">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>3.3</v>
       </c>
       <c r="Q54">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R54">
         <v>2.3</v>
@@ -9129,7 +9129,7 @@
         <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U54">
         <v>2.23</v>
@@ -9184,7 +9184,7 @@
         <v>1.21</v>
       </c>
       <c r="AK54">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AL54">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.71</v>
+        <v>1.87</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P31">
-        <v>2.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q31">
-        <v>3.38</v>
+        <v>2.27</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S31">
         <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X31">
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z31">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="AA31">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB31">
+        <v>2.17</v>
+      </c>
+      <c r="AC31">
+        <v>2.72</v>
+      </c>
+      <c r="AD31">
+        <v>1.38</v>
+      </c>
+      <c r="AE31">
+        <v>1.16</v>
+      </c>
+      <c r="AF31">
+        <v>1.61</v>
+      </c>
+      <c r="AG31">
+        <v>2.16</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.18</v>
+      </c>
+      <c r="AK31">
         <v>2</v>
-      </c>
-      <c r="AC31">
-        <v>2.78</v>
-      </c>
-      <c r="AD31">
-        <v>1.34</v>
-      </c>
-      <c r="AE31">
-        <v>1.09</v>
-      </c>
-      <c r="AF31">
-        <v>1.62</v>
-      </c>
-      <c r="AG31">
-        <v>2.21</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.49</v>
-      </c>
-      <c r="AK31">
-        <v>1.37</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.87</v>
+        <v>2.71</v>
       </c>
       <c r="O32">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
-        <v>3.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q32">
-        <v>2.27</v>
+        <v>3.38</v>
       </c>
       <c r="R32">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
         <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z32">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="AA32">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB32">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AC32">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="AD32">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE32">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG32">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="AK32">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -8631,7 +8631,7 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R51">
         <v>2.55</v>
@@ -8643,7 +8643,7 @@
         <v>3.4</v>
       </c>
       <c r="U51">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V51">
         <v>1.5</v>
@@ -8655,25 +8655,25 @@
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA51">
         <v>1.7</v>
       </c>
       <c r="AB51">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AC51">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD51">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
         <v>2.16</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AK51">
         <v>3.6</v>
@@ -8788,7 +8788,7 @@
         <v>1.85</v>
       </c>
       <c r="O52">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P52">
         <v>4</v>
@@ -8797,7 +8797,7 @@
         <v>2.37</v>
       </c>
       <c r="R52">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S52">
         <v>1.36</v>
@@ -8815,34 +8815,34 @@
         <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z52">
         <v>3.14</v>
       </c>
       <c r="AA52">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AB52">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC52">
         <v>3.2</v>
       </c>
       <c r="AD52">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE52">
         <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG52">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8951,10 +8951,10 @@
         <v>1.62</v>
       </c>
       <c r="O53">
-        <v>3.32</v>
+        <v>3.95</v>
       </c>
       <c r="P53">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="Q53">
         <v>2.1</v>
@@ -8966,13 +8966,13 @@
         <v>1.19</v>
       </c>
       <c r="T53">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="U53">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V53">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W53">
         <v>1.15</v>
@@ -8984,28 +8984,28 @@
         <v>1.14</v>
       </c>
       <c r="Z53">
-        <v>5.1</v>
+        <v>5.35</v>
       </c>
       <c r="AA53">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB53">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AC53">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AD53">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE53">
         <v>1.24</v>
       </c>
       <c r="AF53">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG53">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK53">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="O63">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P63">
         <v>3.23</v>
@@ -10590,7 +10590,7 @@
         <v>2.37</v>
       </c>
       <c r="R63">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="S63">
         <v>1.35</v>
@@ -10599,13 +10599,13 @@
         <v>2.9</v>
       </c>
       <c r="U63">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="V63">
         <v>1.46</v>
       </c>
       <c r="W63">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
         <v>1</v>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK63">
         <v>1.91</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -635,34 +635,34 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O2">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P2">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R2">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="S2">
         <v>1.57</v>
       </c>
       <c r="T2">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U2">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
         <v>1.1</v>
@@ -674,10 +674,10 @@
         <v>2.38</v>
       </c>
       <c r="AA2">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="AB2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC2">
         <v>6</v>
@@ -686,13 +686,13 @@
         <v>1.12</v>
       </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG2">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AK2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O3">
         <v>2.85</v>
@@ -831,19 +831,19 @@
         <v>1.07</v>
       </c>
       <c r="Y3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z3">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AA3">
         <v>2.63</v>
       </c>
       <c r="AB3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AC3">
-        <v>5.11</v>
+        <v>5.4</v>
       </c>
       <c r="AD3">
         <v>1.11</v>
@@ -855,7 +855,7 @@
         <v>2.1</v>
       </c>
       <c r="AG3">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>10</v>
       </c>
       <c r="Q11">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="R11">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S11">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="AA11">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB11">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AD11">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG11">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK11">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O12">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P12">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q12">
         <v>2.63</v>
@@ -2289,7 +2289,7 @@
         <v>3.8</v>
       </c>
       <c r="V12">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W12">
         <v>1.05</v>
@@ -2298,28 +2298,28 @@
         <v>1.07</v>
       </c>
       <c r="Y12">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z12">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="AA12">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AB12">
         <v>1.44</v>
       </c>
       <c r="AC12">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AD12">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE12">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF12">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AG12">
         <v>1.57</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="O29">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P29">
-        <v>2.49</v>
+        <v>1.94</v>
       </c>
       <c r="Q29">
-        <v>2.9</v>
+        <v>3.88</v>
       </c>
       <c r="R29">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="S29">
+        <v>1.29</v>
+      </c>
+      <c r="T29">
+        <v>3.4</v>
+      </c>
+      <c r="U29">
+        <v>2.4</v>
+      </c>
+      <c r="V29">
+        <v>1.53</v>
+      </c>
+      <c r="W29">
+        <v>1.12</v>
+      </c>
+      <c r="X29">
+        <v>1.02</v>
+      </c>
+      <c r="Y29">
+        <v>1.17</v>
+      </c>
+      <c r="Z29">
+        <v>4</v>
+      </c>
+      <c r="AA29">
+        <v>1.64</v>
+      </c>
+      <c r="AB29">
+        <v>2.18</v>
+      </c>
+      <c r="AC29">
+        <v>2.61</v>
+      </c>
+      <c r="AD29">
+        <v>1.46</v>
+      </c>
+      <c r="AE29">
+        <v>1.18</v>
+      </c>
+      <c r="AF29">
+        <v>1.56</v>
+      </c>
+      <c r="AG29">
+        <v>2.25</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.72</v>
+      </c>
+      <c r="AK29">
         <v>1.25</v>
-      </c>
-      <c r="T29">
-        <v>3.5</v>
-      </c>
-      <c r="U29">
-        <v>2.53</v>
-      </c>
-      <c r="V29">
-        <v>1.49</v>
-      </c>
-      <c r="W29">
-        <v>1.11</v>
-      </c>
-      <c r="X29">
-        <v>1.01</v>
-      </c>
-      <c r="Y29">
-        <v>1.16</v>
-      </c>
-      <c r="Z29">
-        <v>4.15</v>
-      </c>
-      <c r="AA29">
-        <v>1.6</v>
-      </c>
-      <c r="AB29">
-        <v>2.19</v>
-      </c>
-      <c r="AC29">
-        <v>2.49</v>
-      </c>
-      <c r="AD29">
-        <v>1.42</v>
-      </c>
-      <c r="AE29">
-        <v>1.17</v>
-      </c>
-      <c r="AF29">
-        <v>1.53</v>
-      </c>
-      <c r="AG29">
-        <v>2.5</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.22</v>
-      </c>
-      <c r="AK29">
-        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.4</v>
+        <v>1.87</v>
       </c>
       <c r="O30">
+        <v>3.75</v>
+      </c>
+      <c r="P30">
         <v>3.55</v>
       </c>
-      <c r="P30">
-        <v>1.94</v>
-      </c>
       <c r="Q30">
-        <v>3.88</v>
+        <v>2.27</v>
       </c>
       <c r="R30">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
         <v>2.4</v>
       </c>
       <c r="V30">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W30">
         <v>1.12</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z30">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AA30">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB30">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AC30">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="AD30">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AE30">
+        <v>1.16</v>
+      </c>
+      <c r="AF30">
+        <v>1.61</v>
+      </c>
+      <c r="AG30">
+        <v>2.16</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.18</v>
       </c>
-      <c r="AF30">
-        <v>1.56</v>
-      </c>
-      <c r="AG30">
-        <v>2.25</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.72</v>
-      </c>
       <c r="AK30">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.87</v>
+        <v>2.71</v>
       </c>
       <c r="O31">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>3.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q31">
-        <v>2.27</v>
+        <v>3.38</v>
       </c>
       <c r="R31">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S31">
         <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="AA31">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB31">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AC31">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="AD31">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE31">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="AK31">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.71</v>
+        <v>7</v>
       </c>
       <c r="O32">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="P32">
-        <v>2.2</v>
+        <v>1.39</v>
       </c>
       <c r="Q32">
-        <v>3.38</v>
+        <v>6.78</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
         <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X32">
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.92</v>
+        <v>3.99</v>
       </c>
       <c r="AA32">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC32">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AD32">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG32">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.49</v>
+        <v>2.88</v>
       </c>
       <c r="AK32">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>2.47</v>
       </c>
       <c r="O33">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="P33">
-        <v>1.39</v>
+        <v>2.49</v>
       </c>
       <c r="Q33">
-        <v>6.78</v>
+        <v>2.9</v>
       </c>
       <c r="R33">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="V33">
+        <v>1.49</v>
+      </c>
+      <c r="W33">
+        <v>1.11</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.16</v>
+      </c>
+      <c r="Z33">
+        <v>4.15</v>
+      </c>
+      <c r="AA33">
+        <v>1.6</v>
+      </c>
+      <c r="AB33">
+        <v>2.19</v>
+      </c>
+      <c r="AC33">
+        <v>2.49</v>
+      </c>
+      <c r="AD33">
+        <v>1.42</v>
+      </c>
+      <c r="AE33">
+        <v>1.17</v>
+      </c>
+      <c r="AF33">
+        <v>1.53</v>
+      </c>
+      <c r="AG33">
+        <v>2.5</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>1.22</v>
+      </c>
+      <c r="AK33">
         <v>1.5</v>
-      </c>
-      <c r="W33">
-        <v>1.13</v>
-      </c>
-      <c r="X33">
-        <v>1.03</v>
-      </c>
-      <c r="Y33">
-        <v>1.22</v>
-      </c>
-      <c r="Z33">
-        <v>3.99</v>
-      </c>
-      <c r="AA33">
-        <v>1.68</v>
-      </c>
-      <c r="AB33">
-        <v>2.06</v>
-      </c>
-      <c r="AC33">
-        <v>2.66</v>
-      </c>
-      <c r="AD33">
-        <v>1.37</v>
-      </c>
-      <c r="AE33">
-        <v>1.11</v>
-      </c>
-      <c r="AF33">
-        <v>1.85</v>
-      </c>
-      <c r="AG33">
-        <v>1.85</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>2.88</v>
-      </c>
-      <c r="AK33">
-        <v>1.03</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -8951,10 +8951,10 @@
         <v>1.62</v>
       </c>
       <c r="O53">
-        <v>3.95</v>
+        <v>3.32</v>
       </c>
       <c r="P53">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="Q53">
         <v>2.1</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -964,7 +964,7 @@
         <v>1.75</v>
       </c>
       <c r="O4">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
         <v>4</v>
@@ -976,13 +976,13 @@
         <v>2.25</v>
       </c>
       <c r="S4">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="V4">
         <v>1.44</v>
@@ -991,7 +991,7 @@
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
         <v>1.22</v>
@@ -1000,13 +1000,13 @@
         <v>3.81</v>
       </c>
       <c r="AA4">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB4">
         <v>1.96</v>
       </c>
       <c r="AC4">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AD4">
         <v>1.3</v>
@@ -1018,7 +1018,7 @@
         <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
         <v>1.88</v>
@@ -1133,7 +1133,7 @@
         <v>1.29</v>
       </c>
       <c r="Q5">
-        <v>7.36</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>2.52</v>
@@ -1160,7 +1160,7 @@
         <v>1.12</v>
       </c>
       <c r="Z5">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA5">
         <v>1.46</v>
@@ -1178,10 +1178,10 @@
         <v>1.22</v>
       </c>
       <c r="AF5">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG5">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O6">
         <v>3</v>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -1302,10 +1302,10 @@
         <v>2</v>
       </c>
       <c r="S6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U6">
         <v>3.2</v>
@@ -1329,22 +1329,22 @@
         <v>2.17</v>
       </c>
       <c r="AB6">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC6">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="AD6">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
         <v>1.87</v>
       </c>
       <c r="AG6">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>1.8</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q7">
         <v>2.45</v>
@@ -1480,13 +1480,13 @@
         <v>1</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z7">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA7">
         <v>2.23</v>
@@ -1495,13 +1495,13 @@
         <v>1.57</v>
       </c>
       <c r="AC7">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AD7">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE7">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
         <v>2</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
         <v>1.82</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
         <v>3.1</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="Q8">
-        <v>4.46</v>
+        <v>3.04</v>
       </c>
       <c r="R8">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="S8">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T8">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="U8">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W8">
         <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z8">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="AA8">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AB8">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AC8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD8">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AK8">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="O9">
         <v>3.1</v>
       </c>
       <c r="P9">
-        <v>2.9</v>
+        <v>2.06</v>
       </c>
       <c r="Q9">
-        <v>3.04</v>
+        <v>4.46</v>
       </c>
       <c r="R9">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T9">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="U9">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
+        <v>1.02</v>
+      </c>
+      <c r="X9">
+        <v>1.04</v>
+      </c>
+      <c r="Y9">
+        <v>1.38</v>
+      </c>
+      <c r="Z9">
+        <v>2.62</v>
+      </c>
+      <c r="AA9">
+        <v>2.23</v>
+      </c>
+      <c r="AB9">
+        <v>1.57</v>
+      </c>
+      <c r="AC9">
+        <v>4.33</v>
+      </c>
+      <c r="AD9">
+        <v>1.17</v>
+      </c>
+      <c r="AE9">
         <v>1.06</v>
       </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
-        <v>1.31</v>
-      </c>
-      <c r="Z9">
-        <v>2.92</v>
-      </c>
-      <c r="AA9">
-        <v>2.15</v>
-      </c>
-      <c r="AB9">
-        <v>1.67</v>
-      </c>
-      <c r="AC9">
-        <v>3.72</v>
-      </c>
-      <c r="AD9">
-        <v>1.2</v>
-      </c>
-      <c r="AE9">
-        <v>1.03</v>
-      </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG9">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         <v>2.8</v>
       </c>
       <c r="O10">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
         <v>2.46</v>
@@ -2437,7 +2437,7 @@
         <v>1.8</v>
       </c>
       <c r="Q13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="R13">
         <v>2.62</v>
@@ -2452,13 +2452,13 @@
         <v>2.18</v>
       </c>
       <c r="V13">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W13">
         <v>1.14</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.14</v>
@@ -2470,22 +2470,22 @@
         <v>1.47</v>
       </c>
       <c r="AB13">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC13">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD13">
         <v>1.65</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
         <v>1.25</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="O14">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P14">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>1.97</v>
@@ -2606,49 +2606,49 @@
         <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U14">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V14">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA14">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB14">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AC14">
         <v>2.63</v>
       </c>
       <c r="AD14">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF14">
         <v>1.72</v>
       </c>
       <c r="AG14">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK14">
         <v>2.63</v>
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
         <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>3.13</v>
+        <v>2.8</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
         <v>1.28</v>
       </c>
       <c r="T15">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U15">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="V15">
         <v>1.61</v>
       </c>
       <c r="W15">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1.03</v>
@@ -2799,7 +2799,7 @@
         <v>2.25</v>
       </c>
       <c r="AC15">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AD15">
         <v>1.5</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O16">
         <v>3.6</v>
       </c>
       <c r="P16">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q16">
         <v>2.3</v>
@@ -2935,7 +2935,7 @@
         <v>1.24</v>
       </c>
       <c r="T16">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U16">
         <v>2.2</v>
@@ -2944,16 +2944,16 @@
         <v>1.64</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA16">
         <v>1.44</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="O17">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q17">
         <v>2.95</v>
@@ -3098,7 +3098,7 @@
         <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U17">
         <v>2.1</v>
@@ -3110,7 +3110,7 @@
         <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
         <v>1.16</v>
@@ -3119,7 +3119,7 @@
         <v>4</v>
       </c>
       <c r="AA17">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AB17">
         <v>2.43</v>
@@ -3134,10 +3134,10 @@
         <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AG17">
-        <v>2.66</v>
+        <v>2.23</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK17">
         <v>1.44</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P18">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q18">
         <v>3.15</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S18">
         <v>1.26</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AK18">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,31 +3406,31 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P19">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q19">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="R19">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S19">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T19">
         <v>4.2</v>
       </c>
       <c r="U19">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="V19">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W19">
         <v>1.17</v>
@@ -3460,10 +3460,10 @@
         <v>1.27</v>
       </c>
       <c r="AF19">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AG19">
-        <v>2.95</v>
+        <v>2.28</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O20">
         <v>5.3</v>
       </c>
       <c r="P20">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="Q20">
         <v>1.57</v>
@@ -3584,19 +3584,19 @@
         <v>2.8</v>
       </c>
       <c r="S20">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="U20">
         <v>1.79</v>
       </c>
       <c r="V20">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="W20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3623,7 +3623,7 @@
         <v>1.22</v>
       </c>
       <c r="AF20">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AG20">
         <v>2.07</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P21">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q21">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="R21">
         <v>2.4</v>
@@ -3759,28 +3759,28 @@
         <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA21">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AC21">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AD21">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE21">
         <v>1.14</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.68</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="O22">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q22">
         <v>2.45</v>
@@ -3910,7 +3910,7 @@
         <v>2.25</v>
       </c>
       <c r="S22">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
         <v>2.94</v>
@@ -3919,7 +3919,7 @@
         <v>2.78</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
         <v>1.09</v>
@@ -3928,19 +3928,19 @@
         <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA22">
         <v>1.91</v>
       </c>
       <c r="AB22">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC22">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="AD22">
         <v>1.29</v>
@@ -3949,10 +3949,10 @@
         <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG22">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
         <v>1.86</v>
@@ -4067,22 +4067,22 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="R23">
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T23">
-        <v>3.19</v>
+        <v>2.85</v>
       </c>
       <c r="U23">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
         <v>1.07</v>
@@ -4097,7 +4097,7 @@
         <v>3.8</v>
       </c>
       <c r="AA23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB23">
         <v>1.9</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="O25">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="P25">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -4426,16 +4426,16 @@
         <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC25">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD25">
         <v>1.22</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF25">
         <v>1.95</v>
@@ -4457,7 +4457,7 @@
         <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>1.14</v>
       </c>
       <c r="O26">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="P26">
         <v>12</v>
@@ -4559,7 +4559,7 @@
         <v>1.4</v>
       </c>
       <c r="R26">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="S26">
         <v>1.13</v>
@@ -4568,28 +4568,28 @@
         <v>4.5</v>
       </c>
       <c r="U26">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V26">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="W26">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Z26">
         <v>8.5</v>
       </c>
       <c r="AA26">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AB26">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AC26">
         <v>1.65</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK26">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O27">
         <v>3.45</v>
@@ -4722,22 +4722,22 @@
         <v>3.2</v>
       </c>
       <c r="R27">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
         <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
         <v>2.45</v>
       </c>
       <c r="V27">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
         <v>1.03</v>
@@ -4746,10 +4746,10 @@
         <v>1.21</v>
       </c>
       <c r="Z27">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA27">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB27">
         <v>2.05</v>
@@ -4761,13 +4761,13 @@
         <v>1.35</v>
       </c>
       <c r="AE27">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
         <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK27">
         <v>1.44</v>
@@ -4873,22 +4873,22 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O28">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="Q28">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="R28">
         <v>2.34</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
         <v>3.1</v>
@@ -4903,31 +4903,31 @@
         <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z28">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="AA28">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB28">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC28">
         <v>2.92</v>
       </c>
       <c r="AD28">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG28">
         <v>1.95</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK28">
         <v>2.07</v>
@@ -5039,16 +5039,16 @@
         <v>3.4</v>
       </c>
       <c r="O29">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P29">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q29">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="R29">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
         <v>1.29</v>
@@ -5063,7 +5063,7 @@
         <v>1.53</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
         <v>1.02</v>
@@ -5084,16 +5084,16 @@
         <v>2.61</v>
       </c>
       <c r="AD29">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
         <v>1.18</v>
       </c>
       <c r="AF29">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG29">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.72</v>
+        <v>1.08</v>
       </c>
       <c r="AK29">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="O30">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P30">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q30">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="R30">
         <v>2.32</v>
@@ -5220,34 +5220,34 @@
         <v>3.3</v>
       </c>
       <c r="U30">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="V30">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W30">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="AA30">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB30">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AC30">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="AD30">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE30">
         <v>1.16</v>
@@ -5272,7 +5272,7 @@
         <v>1.18</v>
       </c>
       <c r="AK30">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,49 +5362,49 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P31">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q31">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T31">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z31">
         <v>3.92</v>
       </c>
       <c r="AA31">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB31">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC31">
         <v>2.78</v>
@@ -5413,13 +5413,13 @@
         <v>1.34</v>
       </c>
       <c r="AE31">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
         <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AK31">
         <v>1.37</v>
@@ -5525,43 +5525,43 @@
         </is>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="O32">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="P32">
         <v>1.39</v>
       </c>
       <c r="Q32">
-        <v>6.78</v>
+        <v>6</v>
       </c>
       <c r="R32">
         <v>2.4</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U32">
         <v>2.56</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W32">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z32">
-        <v>3.99</v>
+        <v>3.92</v>
       </c>
       <c r="AA32">
         <v>1.68</v>
@@ -5570,10 +5570,10 @@
         <v>2.06</v>
       </c>
       <c r="AC32">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="AD32">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
         <v>1.11</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="O33">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="Q33">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R33">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
         <v>1.25</v>
@@ -5709,19 +5709,19 @@
         <v>3.5</v>
       </c>
       <c r="U33">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="V33">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
         <v>4.15</v>
@@ -5733,10 +5733,10 @@
         <v>2.19</v>
       </c>
       <c r="AC33">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AD33">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE33">
         <v>1.17</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK33">
         <v>1.5</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O34">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q34">
         <v>5.35</v>
@@ -5866,28 +5866,28 @@
         <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T34">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="U34">
         <v>2.75</v>
       </c>
       <c r="V34">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
         <v>1.04</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
         <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA34">
         <v>1.85</v>
@@ -5896,10 +5896,10 @@
         <v>1.87</v>
       </c>
       <c r="AC34">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AD34">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE34">
         <v>1.12</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="P35">
-        <v>3.12</v>
+        <v>3.95</v>
       </c>
       <c r="Q35">
         <v>2.6</v>
@@ -6035,22 +6035,22 @@
         <v>3.2</v>
       </c>
       <c r="U35">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="V35">
         <v>1.44</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AA35">
         <v>1.76</v>
@@ -6059,19 +6059,19 @@
         <v>2</v>
       </c>
       <c r="AC35">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AD35">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
         <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,61 +6177,61 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="O36">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="P36">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
         <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U36">
         <v>2.7</v>
       </c>
       <c r="V36">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z36">
         <v>3.65</v>
       </c>
       <c r="AA36">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AB36">
         <v>1.91</v>
       </c>
       <c r="AC36">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="AD36">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE36">
         <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
         <v>2.02</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
         <v>1.85</v>
@@ -6349,40 +6349,40 @@
         <v>3.9</v>
       </c>
       <c r="Q37">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="R37">
         <v>2.25</v>
       </c>
       <c r="S37">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
         <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="V37">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
         <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
         <v>1.71</v>
       </c>
       <c r="AB37">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AC37">
         <v>2.61</v>
@@ -6397,7 +6397,7 @@
         <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,34 +6503,34 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O38">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
         <v>2.05</v>
       </c>
       <c r="Q38">
-        <v>3.6</v>
+        <v>4.11</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S38">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V38">
         <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
         <v>1.04</v>
@@ -6542,7 +6542,7 @@
         <v>3.7</v>
       </c>
       <c r="AA38">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB38">
         <v>2.05</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AK38">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O39">
         <v>4.5</v>
@@ -6675,25 +6675,25 @@
         <v>5.5</v>
       </c>
       <c r="Q39">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R39">
         <v>2.41</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T39">
         <v>3.5</v>
       </c>
       <c r="U39">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V39">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W39">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6702,28 +6702,28 @@
         <v>1.14</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>5.34</v>
       </c>
       <c r="AA39">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB39">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AC39">
         <v>2.31</v>
       </c>
       <c r="AD39">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF39">
         <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O41">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>2.75</v>
       </c>
       <c r="O42">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P42">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="O43">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7487,22 +7487,22 @@
         <v>3.45</v>
       </c>
       <c r="P44">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q44">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R44">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
         <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U44">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="V44">
         <v>1.38</v>
@@ -7511,28 +7511,28 @@
         <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y44">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z44">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA44">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB44">
         <v>1.76</v>
       </c>
       <c r="AC44">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD44">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF44">
         <v>1.81</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK44">
         <v>1.82</v>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="O45">
         <v>3.1</v>
@@ -7656,7 +7656,7 @@
         <v>3.6</v>
       </c>
       <c r="R45">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S45">
         <v>1.37</v>
@@ -7674,13 +7674,13 @@
         <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y45">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z45">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AA45">
         <v>2.01</v>
@@ -7689,19 +7689,19 @@
         <v>1.7</v>
       </c>
       <c r="AC45">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AD45">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE45">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF45">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK45">
         <v>1.34</v>
@@ -7816,7 +7816,7 @@
         <v>3</v>
       </c>
       <c r="Q46">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R46">
         <v>1.91</v>
@@ -7825,7 +7825,7 @@
         <v>1.48</v>
       </c>
       <c r="T46">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="U46">
         <v>3.34</v>
@@ -7834,7 +7834,7 @@
         <v>1.25</v>
       </c>
       <c r="W46">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X46">
         <v>1.03</v>
@@ -7849,7 +7849,7 @@
         <v>2.34</v>
       </c>
       <c r="AB46">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC46">
         <v>4.5</v>
@@ -7880,7 +7880,7 @@
         <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,31 +7970,31 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="O47">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P47">
-        <v>3.28</v>
+        <v>4.05</v>
       </c>
       <c r="Q47">
         <v>2.05</v>
       </c>
       <c r="R47">
-        <v>2.98</v>
+        <v>2.67</v>
       </c>
       <c r="S47">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="T47">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="U47">
         <v>1.75</v>
       </c>
       <c r="V47">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="W47">
         <v>1.29</v>
@@ -8006,7 +8006,7 @@
         <v>1.01</v>
       </c>
       <c r="Z47">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AA47">
         <v>1.23</v>
@@ -8015,7 +8015,7 @@
         <v>3.87</v>
       </c>
       <c r="AC47">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AD47">
         <v>2.21</v>
@@ -8024,10 +8024,10 @@
         <v>1.48</v>
       </c>
       <c r="AF47">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AG47">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK47">
         <v>1.98</v>
@@ -8133,28 +8133,28 @@
         </is>
       </c>
       <c r="N48">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="O48">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="P48">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Q48">
         <v>7</v>
       </c>
       <c r="R48">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="S48">
         <v>1.2</v>
       </c>
       <c r="T48">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V48">
         <v>1.79</v>
@@ -8169,7 +8169,7 @@
         <v>1.06</v>
       </c>
       <c r="Z48">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="AA48">
         <v>1.36</v>
@@ -8181,16 +8181,16 @@
         <v>1.95</v>
       </c>
       <c r="AD48">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AE48">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF48">
         <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="R49">
         <v>2.2</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U49">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="V49">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z49">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA49">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC49">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD49">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE49">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK49">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q51">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="R51">
-        <v>2.55</v>
+        <v>2.24</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="U51">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z51">
-        <v>4.33</v>
+        <v>3.14</v>
       </c>
       <c r="AA51">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB51">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AC51">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF51">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="AG51">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.37</v>
+        <v>1.71</v>
       </c>
       <c r="R52">
+        <v>2.5</v>
+      </c>
+      <c r="S52">
+        <v>1.3</v>
+      </c>
+      <c r="T52">
+        <v>3.4</v>
+      </c>
+      <c r="U52">
+        <v>2.4</v>
+      </c>
+      <c r="V52">
+        <v>1.5</v>
+      </c>
+      <c r="W52">
+        <v>1.1</v>
+      </c>
+      <c r="X52">
+        <v>1.02</v>
+      </c>
+      <c r="Y52">
+        <v>1.22</v>
+      </c>
+      <c r="Z52">
+        <v>4.1</v>
+      </c>
+      <c r="AA52">
+        <v>1.7</v>
+      </c>
+      <c r="AB52">
         <v>2.04</v>
       </c>
-      <c r="S52">
-        <v>1.36</v>
-      </c>
-      <c r="T52">
-        <v>2.92</v>
-      </c>
-      <c r="U52">
-        <v>2.81</v>
-      </c>
-      <c r="V52">
-        <v>1.37</v>
-      </c>
-      <c r="W52">
-        <v>1.05</v>
-      </c>
-      <c r="X52">
-        <v>1.03</v>
-      </c>
-      <c r="Y52">
-        <v>1.27</v>
-      </c>
-      <c r="Z52">
-        <v>3.14</v>
-      </c>
-      <c r="AA52">
-        <v>1.92</v>
-      </c>
-      <c r="AB52">
-        <v>1.8</v>
-      </c>
       <c r="AC52">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD52">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE52">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AG52">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AK52">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9111,25 +9111,25 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="O54">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P54">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q54">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R54">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S54">
         <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U54">
         <v>2.23</v>
@@ -9184,7 +9184,7 @@
         <v>1.21</v>
       </c>
       <c r="AK54">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10590,22 +10590,22 @@
         <v>2.37</v>
       </c>
       <c r="R63">
-        <v>2.37</v>
+        <v>2.09</v>
       </c>
       <c r="S63">
         <v>1.35</v>
       </c>
       <c r="T63">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="U63">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="V63">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W63">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
         <v>1</v>
@@ -10617,13 +10617,13 @@
         <v>3.82</v>
       </c>
       <c r="AA63">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB63">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AC63">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD63">
         <v>1.36</v>
@@ -10635,7 +10635,7 @@
         <v>1.65</v>
       </c>
       <c r="AG63">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK63">
         <v>1.91</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="O2">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P2">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -689,10 +689,10 @@
         <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG2">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O3">
         <v>2.85</v>
@@ -816,19 +816,19 @@
         <v>1.48</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
         <v>1.01</v>
       </c>
       <c r="X3">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y3">
         <v>1.49</v>
@@ -837,25 +837,25 @@
         <v>2.44</v>
       </c>
       <c r="AA3">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AB3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AC3">
-        <v>5.4</v>
+        <v>4.55</v>
       </c>
       <c r="AD3">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
         <v>2.1</v>
       </c>
       <c r="AG3">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O11">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P11">
         <v>10</v>
@@ -2126,7 +2126,7 @@
         <v>2.4</v>
       </c>
       <c r="V11">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
         <v>1.12</v>
@@ -2141,7 +2141,7 @@
         <v>4.33</v>
       </c>
       <c r="AA11">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
         <v>2.15</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O12">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="P12">
         <v>3.8</v>
@@ -2280,16 +2280,16 @@
         <v>1.94</v>
       </c>
       <c r="S12">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="T12">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="U12">
         <v>3.8</v>
       </c>
       <c r="V12">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
         <v>1.05</v>
@@ -2301,10 +2301,10 @@
         <v>1.51</v>
       </c>
       <c r="Z12">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AA12">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AB12">
         <v>1.44</v>
@@ -2316,10 +2316,10 @@
         <v>1.13</v>
       </c>
       <c r="AE12">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF12">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AG12">
         <v>1.57</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="O26">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="P26">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q26">
         <v>1.4</v>
       </c>
       <c r="R26">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="S26">
         <v>1.13</v>
@@ -4568,13 +4568,13 @@
         <v>4.5</v>
       </c>
       <c r="U26">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V26">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="W26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4583,13 +4583,13 @@
         <v>1.08</v>
       </c>
       <c r="Z26">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB26">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AC26">
         <v>1.65</v>
@@ -4601,10 +4601,10 @@
         <v>1.55</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -8963,13 +8963,13 @@
         <v>2.5</v>
       </c>
       <c r="S53">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T53">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="U53">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V53">
         <v>1.67</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -964,10 +964,10 @@
         <v>1.75</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="Q4">
         <v>2.35</v>
@@ -979,7 +979,7 @@
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="U4">
         <v>2.63</v>
@@ -997,13 +997,13 @@
         <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="AA4">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC4">
         <v>3</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>7.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O5">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="P5">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="R5">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="S5">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T5">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="V5">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="W5">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Z5">
-        <v>4.75</v>
+        <v>6.15</v>
       </c>
       <c r="AA5">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AB5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC5">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AD5">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE5">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AF5">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>1.8</v>
       </c>
       <c r="Q13">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R13">
         <v>2.62</v>
@@ -2449,22 +2449,22 @@
         <v>3.8</v>
       </c>
       <c r="U13">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="V13">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AA13">
         <v>1.47</v>
@@ -2473,13 +2473,13 @@
         <v>2.63</v>
       </c>
       <c r="AC13">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AD13">
         <v>1.65</v>
       </c>
       <c r="AE13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF13">
         <v>1.47</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="O17">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P17">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="Q17">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="R17">
         <v>2.42</v>
@@ -3098,19 +3098,19 @@
         <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="U17">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="V17">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.16</v>
@@ -3122,7 +3122,7 @@
         <v>1.62</v>
       </c>
       <c r="AB17">
-        <v>2.43</v>
+        <v>2.08</v>
       </c>
       <c r="AC17">
         <v>2.6</v>
@@ -3153,7 +3153,7 @@
         <v>1.23</v>
       </c>
       <c r="AK17">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3246,10 +3246,10 @@
         <v>2.87</v>
       </c>
       <c r="O18">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Q18">
         <v>3.15</v>
@@ -3261,16 +3261,16 @@
         <v>1.26</v>
       </c>
       <c r="T18">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V18">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3282,7 +3282,7 @@
         <v>4.4</v>
       </c>
       <c r="AA18">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB18">
         <v>2.29</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="O19">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
         <v>2.43</v>
@@ -3424,16 +3424,16 @@
         <v>1.16</v>
       </c>
       <c r="T19">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U19">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="V19">
         <v>1.73</v>
       </c>
       <c r="W19">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK19">
         <v>1.37</v>
@@ -3569,55 +3569,55 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O20">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="P20">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="Q20">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R20">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S20">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T20">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U20">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="V20">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W20">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z20">
-        <v>5.5</v>
+        <v>5.84</v>
       </c>
       <c r="AA20">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB20">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AC20">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD20">
-        <v>1.59</v>
+        <v>1.96</v>
       </c>
       <c r="AE20">
         <v>1.22</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK20">
         <v>3.3</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="O21">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q21">
         <v>3.25</v>
@@ -3750,7 +3750,7 @@
         <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
         <v>2.23</v>
@@ -3774,7 +3774,7 @@
         <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC21">
         <v>2.48</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="P22">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q22">
         <v>2.45</v>
@@ -3913,13 +3913,13 @@
         <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="U22">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W22">
         <v>1.09</v>
@@ -3940,7 +3940,7 @@
         <v>1.9</v>
       </c>
       <c r="AC22">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="AD22">
         <v>1.29</v>
@@ -3949,10 +3949,10 @@
         <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG22">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK22">
         <v>1.86</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O25">
         <v>3.25</v>
       </c>
       <c r="P25">
-        <v>4.6</v>
+        <v>3.78</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -4457,7 +4457,7 @@
         <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
+        <v>2.35</v>
+      </c>
+      <c r="O27">
+        <v>3.38</v>
+      </c>
+      <c r="P27">
         <v>2.6</v>
       </c>
-      <c r="O27">
-        <v>3.45</v>
-      </c>
-      <c r="P27">
-        <v>2.51</v>
-      </c>
       <c r="Q27">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
         <v>1.29</v>
@@ -4734,7 +4734,7 @@
         <v>2.45</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W27">
         <v>1.11</v>
@@ -4743,31 +4743,31 @@
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z27">
-        <v>3.58</v>
+        <v>4.13</v>
       </c>
       <c r="AA27">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB27">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC27">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD27">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
         <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
         <v>1.44</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O35">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="Q35">
         <v>2.6</v>
@@ -6035,7 +6035,7 @@
         <v>3.2</v>
       </c>
       <c r="U35">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="V35">
         <v>1.44</v>
@@ -6068,7 +6068,7 @@
         <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG35">
         <v>2.05</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="O36">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P36">
         <v>5</v>
@@ -6201,7 +6201,7 @@
         <v>2.7</v>
       </c>
       <c r="V36">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W36">
         <v>1.12</v>
@@ -8133,34 +8133,34 @@
         </is>
       </c>
       <c r="N48">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="O48">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="P48">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Q48">
         <v>7</v>
       </c>
       <c r="R48">
-        <v>2.91</v>
+        <v>3.24</v>
       </c>
       <c r="S48">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T48">
         <v>4</v>
       </c>
       <c r="U48">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="V48">
         <v>1.79</v>
       </c>
       <c r="W48">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8181,16 +8181,16 @@
         <v>1.95</v>
       </c>
       <c r="AD48">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE48">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF48">
         <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -635,52 +635,52 @@
         </is>
       </c>
       <c r="N2">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O2">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P2">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="R2">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S2">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T2">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="U2">
         <v>3.8</v>
       </c>
       <c r="V2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W2">
         <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y2">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z2">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AA2">
         <v>2.75</v>
       </c>
       <c r="AB2">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC2">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="AD2">
         <v>1.12</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK2">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="O3">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="P3">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
       </c>
       <c r="R3">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="S3">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="T3">
         <v>2.2</v>
       </c>
       <c r="U3">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
         <v>1.49</v>
       </c>
       <c r="Z3">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AA3">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AB3">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC3">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="AD3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF3">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG3">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK3">
         <v>1.65</v>
@@ -973,7 +973,7 @@
         <v>2.35</v>
       </c>
       <c r="R4">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S4">
         <v>1.36</v>
@@ -982,7 +982,7 @@
         <v>2.95</v>
       </c>
       <c r="U4">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="V4">
         <v>1.44</v>
@@ -997,28 +997,28 @@
         <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AA4">
         <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
         <v>3</v>
       </c>
       <c r="AD4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE4">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
         <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
         <v>3.2</v>
       </c>
       <c r="Q6">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S6">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T6">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="U6">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="V6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z6">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA6">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AB6">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC6">
-        <v>4.33</v>
+        <v>3.74</v>
       </c>
       <c r="AD6">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG6">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,37 +1450,37 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="O7">
         <v>3.4</v>
       </c>
       <c r="P7">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="Q7">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
         <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="U7">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V7">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
         <v>1.4</v>
@@ -1489,25 +1489,25 @@
         <v>2.88</v>
       </c>
       <c r="AA7">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AB7">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC7">
-        <v>4.33</v>
+        <v>3.82</v>
       </c>
       <c r="AD7">
         <v>1.2</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AG7">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1619,58 +1619,58 @@
         <v>3.1</v>
       </c>
       <c r="P8">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q8">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="R8">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="S8">
         <v>1.4</v>
       </c>
       <c r="T8">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U8">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="V8">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z8">
         <v>3.1</v>
       </c>
       <c r="AA8">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB8">
         <v>1.67</v>
       </c>
       <c r="AC8">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG8">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AK8">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,34 +1776,34 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P9">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q9">
-        <v>4.46</v>
+        <v>4</v>
       </c>
       <c r="R9">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S9">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T9">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="U9">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1.04</v>
@@ -1815,22 +1815,22 @@
         <v>2.62</v>
       </c>
       <c r="AA9">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AB9">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC9">
         <v>4.33</v>
       </c>
       <c r="AD9">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE9">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG9">
         <v>1.75</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="AK9">
         <v>1.22</v>
@@ -2102,34 +2102,34 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="O11">
         <v>5.5</v>
       </c>
       <c r="P11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="R11">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="S11">
         <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U11">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2144,7 +2144,7 @@
         <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AC11">
         <v>2.88</v>
@@ -2156,10 +2156,10 @@
         <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AG11">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK11">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,22 +2268,22 @@
         <v>1.91</v>
       </c>
       <c r="O12">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="P12">
         <v>3.8</v>
       </c>
       <c r="Q12">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R12">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="S12">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="T12">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="U12">
         <v>3.8</v>
@@ -2292,7 +2292,7 @@
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
         <v>1.07</v>
@@ -2307,7 +2307,7 @@
         <v>2.63</v>
       </c>
       <c r="AB12">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC12">
         <v>5.25</v>
@@ -2316,13 +2316,13 @@
         <v>1.13</v>
       </c>
       <c r="AE12">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG12">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>1.8</v>
       </c>
       <c r="Q13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R13">
         <v>2.62</v>
       </c>
       <c r="S13">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.8</v>
+        <v>3.32</v>
       </c>
       <c r="U13">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="V13">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
         <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z13">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA13">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB13">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC13">
         <v>2.19</v>
       </c>
       <c r="AD13">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
         <v>1.47</v>
       </c>
       <c r="AG13">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,7 +2594,7 @@
         <v>1.49</v>
       </c>
       <c r="O14">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -2606,43 +2606,43 @@
         <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
         <v>2.55</v>
       </c>
       <c r="V14">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
         <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
         <v>4.3</v>
       </c>
       <c r="AA14">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB14">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC14">
         <v>2.63</v>
       </c>
       <c r="AD14">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
         <v>1.72</v>
@@ -2664,7 +2664,7 @@
         <v>1.06</v>
       </c>
       <c r="AK14">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O15">
         <v>3.5</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q15">
         <v>2.8</v>
@@ -2775,7 +2775,7 @@
         <v>3.4</v>
       </c>
       <c r="U15">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="V15">
         <v>1.61</v>
@@ -2802,7 +2802,7 @@
         <v>2.5</v>
       </c>
       <c r="AD15">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE15">
         <v>1.18</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="P16">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
         <v>2.3</v>
@@ -2932,28 +2932,28 @@
         <v>2.5</v>
       </c>
       <c r="S16">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T16">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U16">
         <v>2.2</v>
       </c>
       <c r="V16">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W16">
         <v>1.12</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AA16">
         <v>1.44</v>
@@ -2962,7 +2962,7 @@
         <v>2.55</v>
       </c>
       <c r="AC16">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD16">
         <v>1.6</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="O17">
         <v>3.45</v>
@@ -3089,55 +3089,55 @@
         <v>2.28</v>
       </c>
       <c r="Q17">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="R17">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
         <v>1.22</v>
       </c>
       <c r="T17">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z17">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AA17">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AB17">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AC17">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD17">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF17">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG17">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,25 +3252,25 @@
         <v>2.15</v>
       </c>
       <c r="Q18">
-        <v>3.15</v>
+        <v>3.56</v>
       </c>
       <c r="R18">
         <v>2.35</v>
       </c>
       <c r="S18">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U18">
         <v>2.25</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3279,28 +3279,28 @@
         <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA18">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AB18">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AC18">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD18">
         <v>1.42</v>
       </c>
       <c r="AE18">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF18">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG18">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.53</v>
       </c>
       <c r="AK18">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3412,71 +3412,71 @@
         <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="Q19">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="R19">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="S19">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="T19">
         <v>4.5</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="V19">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Z19">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AB19">
-        <v>2.12</v>
+        <v>2.87</v>
       </c>
       <c r="AC19">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="AD19">
+        <v>1.61</v>
+      </c>
+      <c r="AE19">
+        <v>1.33</v>
+      </c>
+      <c r="AF19">
+        <v>1.33</v>
+      </c>
+      <c r="AG19">
+        <v>3</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
         <v>1.42</v>
-      </c>
-      <c r="AE19">
-        <v>1.27</v>
-      </c>
-      <c r="AF19">
-        <v>1.45</v>
-      </c>
-      <c r="AG19">
-        <v>2.28</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.44</v>
       </c>
       <c r="AK19">
         <v>1.37</v>
@@ -3569,58 +3569,58 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O20">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="P20">
         <v>6.6</v>
       </c>
       <c r="Q20">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="R20">
         <v>2.75</v>
       </c>
       <c r="S20">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T20">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U20">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="V20">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="W20">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
         <v>5.84</v>
       </c>
       <c r="AA20">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="AC20">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AD20">
         <v>1.96</v>
       </c>
       <c r="AE20">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF20">
         <v>1.56</v>
@@ -3735,7 +3735,7 @@
         <v>2.98</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
         <v>2.05</v>
@@ -3747,19 +3747,19 @@
         <v>2.4</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U21">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="V21">
         <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3768,28 +3768,28 @@
         <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA21">
         <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC21">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AD21">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE21">
         <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AG21">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O22">
         <v>3.33</v>
@@ -3913,16 +3913,16 @@
         <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U22">
         <v>2.65</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -3937,7 +3937,7 @@
         <v>1.91</v>
       </c>
       <c r="AB22">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC22">
         <v>3.44</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK22">
         <v>1.86</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="O25">
         <v>3.25</v>
       </c>
       <c r="P25">
-        <v>3.78</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -4408,7 +4408,7 @@
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W25">
         <v>1.03</v>
@@ -4429,7 +4429,7 @@
         <v>1.6</v>
       </c>
       <c r="AC25">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD25">
         <v>1.22</v>
@@ -4550,19 +4550,19 @@
         <v>1.11</v>
       </c>
       <c r="O26">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P26">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q26">
         <v>1.4</v>
       </c>
       <c r="R26">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="S26">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T26">
         <v>4.5</v>
@@ -4571,10 +4571,10 @@
         <v>1.7</v>
       </c>
       <c r="V26">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="W26">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4583,16 +4583,16 @@
         <v>1.08</v>
       </c>
       <c r="Z26">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AA26">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AB26">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AC26">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AD26">
         <v>2.3</v>
@@ -4601,7 +4601,7 @@
         <v>1.55</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG26">
         <v>1.95</v>
@@ -4620,7 +4620,7 @@
         <v>1.07</v>
       </c>
       <c r="AK26">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4716,25 +4716,25 @@
         <v>3.38</v>
       </c>
       <c r="P27">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q27">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U27">
         <v>2.45</v>
       </c>
       <c r="V27">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
         <v>1.11</v>
@@ -4746,13 +4746,13 @@
         <v>1.23</v>
       </c>
       <c r="Z27">
-        <v>4.13</v>
+        <v>3.68</v>
       </c>
       <c r="AA27">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC27">
         <v>2.7</v>
@@ -4767,7 +4767,7 @@
         <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK27">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,65 +5199,65 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="O30">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P30">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q30">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="R30">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T30">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="U30">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="V30">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
         <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="AA30">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB30">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AC30">
+        <v>2.78</v>
+      </c>
+      <c r="AD30">
+        <v>1.34</v>
+      </c>
+      <c r="AE30">
+        <v>1.08</v>
+      </c>
+      <c r="AF30">
+        <v>1.62</v>
+      </c>
+      <c r="AG30">
         <v>2.2</v>
       </c>
-      <c r="AD30">
-        <v>1.43</v>
-      </c>
-      <c r="AE30">
-        <v>1.16</v>
-      </c>
-      <c r="AF30">
-        <v>1.61</v>
-      </c>
-      <c r="AG30">
-        <v>2.16</v>
-      </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK30">
-        <v>1.95</v>
+        <v>1.37</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.62</v>
+        <v>6.7</v>
       </c>
       <c r="O31">
-        <v>3.55</v>
+        <v>4.45</v>
       </c>
       <c r="P31">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="Q31">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T31">
-        <v>2.4</v>
+        <v>3.32</v>
       </c>
       <c r="U31">
-        <v>2.09</v>
+        <v>2.56</v>
       </c>
       <c r="V31">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="W31">
         <v>1.06</v>
@@ -5395,31 +5395,31 @@
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
         <v>3.92</v>
       </c>
       <c r="AA31">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB31">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AC31">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="AD31">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG31">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.23</v>
+        <v>2.88</v>
       </c>
       <c r="AK31">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>6.7</v>
+        <v>1.8</v>
       </c>
       <c r="O32">
-        <v>4.45</v>
+        <v>3.9</v>
       </c>
       <c r="P32">
-        <v>1.39</v>
+        <v>3.7</v>
       </c>
       <c r="Q32">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="R32">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S32">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.56</v>
+        <v>2.31</v>
       </c>
       <c r="V32">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z32">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA32">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AC32">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD32">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE32">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF32">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG32">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>2.88</v>
+        <v>1.18</v>
       </c>
       <c r="AK32">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
+        <v>2.25</v>
+      </c>
+      <c r="O41">
+        <v>3.35</v>
+      </c>
+      <c r="P41">
+        <v>2.75</v>
+      </c>
+      <c r="Q41">
+        <v>2.81</v>
+      </c>
+      <c r="R41">
         <v>2.2</v>
       </c>
-      <c r="O41">
-        <v>3.4</v>
-      </c>
-      <c r="P41">
-        <v>3.15</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O42">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P42">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P43">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,31 +7481,31 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O44">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q44">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R44">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S44">
         <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U44">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="V44">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W44">
         <v>1.07</v>
@@ -7514,31 +7514,31 @@
         <v>1.05</v>
       </c>
       <c r="Y44">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z44">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA44">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AB44">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC44">
         <v>3.5</v>
       </c>
       <c r="AD44">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE44">
         <v>1.08</v>
       </c>
       <c r="AF44">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK44">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="O45">
         <v>3.1</v>
       </c>
       <c r="P45">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q45">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S45">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="U45">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z45">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AB45">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC45">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD45">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE45">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="AK45">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,61 +7810,61 @@
         <v>2.2</v>
       </c>
       <c r="O46">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P46">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q46">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R46">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S46">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T46">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="U46">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V46">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W46">
         <v>1.04</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z46">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="AA46">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AB46">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AC46">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE46">
         <v>1.01</v>
       </c>
       <c r="AF46">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AG46">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK46">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,34 +7970,34 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="O47">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="P47">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="Q47">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R47">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="S47">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T47">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U47">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V47">
         <v>1.89</v>
       </c>
       <c r="W47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -8006,25 +8006,25 @@
         <v>1.01</v>
       </c>
       <c r="Z47">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA47">
         <v>1.23</v>
       </c>
       <c r="AB47">
-        <v>3.87</v>
+        <v>3.98</v>
       </c>
       <c r="AC47">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AD47">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AE47">
         <v>1.48</v>
       </c>
       <c r="AF47">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AG47">
         <v>3.34</v>
@@ -8133,34 +8133,34 @@
         </is>
       </c>
       <c r="N48">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="O48">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="P48">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q48">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R48">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="S48">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T48">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="U48">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="V48">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="W48">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8169,7 +8169,7 @@
         <v>1.06</v>
       </c>
       <c r="Z48">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="AA48">
         <v>1.36</v>
@@ -8181,16 +8181,16 @@
         <v>1.95</v>
       </c>
       <c r="AD48">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AE48">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF48">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG48">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O49">
         <v>3.4</v>
@@ -8305,22 +8305,22 @@
         <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T49">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="U49">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="V49">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W49">
         <v>1.1</v>
@@ -8329,7 +8329,7 @@
         <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
         <v>4.2</v>
@@ -8341,35 +8341,35 @@
         <v>2.07</v>
       </c>
       <c r="AC49">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD49">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
+        <v>1.58</v>
+      </c>
+      <c r="AG49">
+        <v>2.17</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.36</v>
+      </c>
+      <c r="AK49">
         <v>1.53</v>
-      </c>
-      <c r="AG49">
-        <v>2.3</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.4</v>
-      </c>
-      <c r="AK49">
-        <v>1.48</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="O54">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="P54">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q54">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="R54">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="S54">
+        <v>1.32</v>
+      </c>
+      <c r="T54">
+        <v>2.75</v>
+      </c>
+      <c r="U54">
+        <v>2.51</v>
+      </c>
+      <c r="V54">
+        <v>1.42</v>
+      </c>
+      <c r="W54">
+        <v>1.1</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54">
         <v>1.25</v>
       </c>
-      <c r="T54">
-        <v>3.4</v>
-      </c>
-      <c r="U54">
-        <v>2.23</v>
-      </c>
-      <c r="V54">
-        <v>1.55</v>
-      </c>
-      <c r="W54">
-        <v>1.12</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.16</v>
-      </c>
       <c r="Z54">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA54">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AB54">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AC54">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="AD54">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE54">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG54">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK54">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL54">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="O5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="P5">
         <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="R5">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="S5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T5">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="U5">
         <v>1.99</v>
       </c>
       <c r="V5">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W5">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,28 +1160,28 @@
         <v>1.06</v>
       </c>
       <c r="Z5">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="AA5">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB5">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AC5">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AD5">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AE5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG5">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK5">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="O14">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P14">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="Q14">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="R14">
         <v>2.5</v>
@@ -2609,46 +2609,46 @@
         <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AA14">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AB14">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AC14">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AD14">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF14">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AK14">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2760,52 +2760,52 @@
         <v>3.5</v>
       </c>
       <c r="P15">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="R15">
         <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
         <v>3.4</v>
       </c>
       <c r="U15">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V15">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="W15">
         <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
         <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB15">
         <v>2.25</v>
       </c>
       <c r="AC15">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD15">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF15">
         <v>1.42</v>
@@ -2827,7 +2827,7 @@
         <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,22 +2917,22 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="O16">
-        <v>3.41</v>
+        <v>3.75</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q16">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R16">
         <v>2.5</v>
       </c>
       <c r="S16">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
         <v>3.6</v>
@@ -2950,28 +2950,28 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AA16">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AB16">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC16">
         <v>2.29</v>
       </c>
       <c r="AD16">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE16">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF16">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AG16">
         <v>2.55</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="O17">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q17">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U17">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="V17">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AB17">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC17">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD17">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE17">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF17">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AG17">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AK17">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.87</v>
+        <v>2.44</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q18">
-        <v>3.56</v>
+        <v>2.8</v>
       </c>
       <c r="R18">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T18">
-        <v>3.12</v>
+        <v>4.5</v>
       </c>
       <c r="U18">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="V18">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="Z18">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AA18">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="AB18">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="AC18">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="AD18">
+        <v>1.61</v>
+      </c>
+      <c r="AE18">
+        <v>1.33</v>
+      </c>
+      <c r="AF18">
+        <v>1.33</v>
+      </c>
+      <c r="AG18">
+        <v>3</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.42</v>
       </c>
-      <c r="AE18">
-        <v>1.16</v>
-      </c>
-      <c r="AF18">
-        <v>1.49</v>
-      </c>
-      <c r="AG18">
-        <v>2.42</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.53</v>
-      </c>
       <c r="AK18">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.44</v>
+        <v>1.28</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>4.95</v>
       </c>
       <c r="P19">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="Q19">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="R19">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="S19">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T19">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="U19">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="V19">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W19">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>5.84</v>
       </c>
       <c r="AA19">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB19">
         <v>2.87</v>
       </c>
       <c r="AC19">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AD19">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="AE19">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF19">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AG19">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="AK19">
-        <v>1.37</v>
+        <v>3.3</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.28</v>
+        <v>2.5</v>
       </c>
       <c r="O20">
-        <v>4.95</v>
+        <v>3.45</v>
       </c>
       <c r="P20">
-        <v>6.6</v>
+        <v>2.28</v>
       </c>
       <c r="Q20">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T20">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U20">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="V20">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="W20">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3605,28 +3605,28 @@
         <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>5.84</v>
+        <v>5.1</v>
       </c>
       <c r="AA20">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB20">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AC20">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AD20">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="AE20">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AF20">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG20">
-        <v>2.07</v>
+        <v>2.63</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>3.3</v>
+        <v>1.39</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="Q23">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S23">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="U23">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z23">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="AA23">
+        <v>1.73</v>
+      </c>
+      <c r="AB23">
+        <v>2</v>
+      </c>
+      <c r="AC23">
+        <v>2.88</v>
+      </c>
+      <c r="AD23">
+        <v>1.4</v>
+      </c>
+      <c r="AE23">
+        <v>1.09</v>
+      </c>
+      <c r="AF23">
         <v>1.79</v>
       </c>
-      <c r="AB23">
-        <v>1.9</v>
-      </c>
-      <c r="AC23">
-        <v>3.1</v>
-      </c>
-      <c r="AD23">
-        <v>1.36</v>
-      </c>
-      <c r="AE23">
-        <v>1.13</v>
-      </c>
-      <c r="AF23">
-        <v>1.83</v>
-      </c>
       <c r="AG23">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4550,31 +4550,31 @@
         <v>1.11</v>
       </c>
       <c r="O26">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P26">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q26">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="R26">
         <v>3.4</v>
       </c>
       <c r="S26">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="T26">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>1.7</v>
       </c>
       <c r="V26">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="W26">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4583,10 +4583,10 @@
         <v>1.08</v>
       </c>
       <c r="Z26">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="AA26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB26">
         <v>4.2</v>
@@ -4601,7 +4601,7 @@
         <v>1.55</v>
       </c>
       <c r="AF26">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
         <v>1.95</v>
@@ -4620,7 +4620,7 @@
         <v>1.07</v>
       </c>
       <c r="AK26">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P28">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q28">
         <v>2.1</v>
@@ -4888,10 +4888,10 @@
         <v>2.34</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U28">
         <v>2.5</v>
@@ -4903,34 +4903,34 @@
         <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="AA28">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AB28">
         <v>1.93</v>
       </c>
       <c r="AC28">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD28">
         <v>1.25</v>
       </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AG28">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK28">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,61 +5036,61 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="O29">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="Q29">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V29">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z29">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA29">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AB29">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AC29">
-        <v>2.61</v>
+        <v>2.78</v>
       </c>
       <c r="AD29">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AE29">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG29">
         <v>2.21</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.62</v>
+        <v>6.75</v>
       </c>
       <c r="O30">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="P30">
-        <v>2.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q30">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="S30">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T30">
-        <v>2.4</v>
+        <v>3.24</v>
       </c>
       <c r="U30">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="V30">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
         <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z30">
-        <v>3.92</v>
+        <v>3</v>
       </c>
       <c r="AA30">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB30">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AC30">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="AD30">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG30">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.23</v>
+        <v>2.88</v>
       </c>
       <c r="AK30">
-        <v>1.37</v>
+        <v>1.06</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>6.7</v>
+        <v>1.76</v>
       </c>
       <c r="O31">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="P31">
-        <v>1.39</v>
+        <v>3.8</v>
       </c>
       <c r="Q31">
-        <v>6</v>
+        <v>2.23</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="T31">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="U31">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="V31">
         <v>1.48</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="AA31">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB31">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC31">
         <v>2.3</v>
       </c>
       <c r="AD31">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG31">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>2.88</v>
+        <v>1.16</v>
       </c>
       <c r="AK31">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="O32">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>3.7</v>
+        <v>2.46</v>
       </c>
       <c r="Q32">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="R32">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U32">
-        <v>2.31</v>
+        <v>2.01</v>
       </c>
       <c r="V32">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W32">
         <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA32">
         <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AC32">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="AD32">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE32">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF32">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AG32">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AK32">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P33">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="Q33">
-        <v>2.7</v>
+        <v>4.04</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="S33">
+        <v>1.29</v>
+      </c>
+      <c r="T33">
+        <v>3.25</v>
+      </c>
+      <c r="U33">
+        <v>2.03</v>
+      </c>
+      <c r="V33">
+        <v>1.41</v>
+      </c>
+      <c r="W33">
+        <v>1.07</v>
+      </c>
+      <c r="X33">
+        <v>1.02</v>
+      </c>
+      <c r="Y33">
+        <v>1.17</v>
+      </c>
+      <c r="Z33">
+        <v>3.98</v>
+      </c>
+      <c r="AA33">
+        <v>1.52</v>
+      </c>
+      <c r="AB33">
+        <v>2.15</v>
+      </c>
+      <c r="AC33">
+        <v>2.2</v>
+      </c>
+      <c r="AD33">
+        <v>1.33</v>
+      </c>
+      <c r="AE33">
+        <v>1.14</v>
+      </c>
+      <c r="AF33">
+        <v>1.57</v>
+      </c>
+      <c r="AG33">
+        <v>2.19</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>1.21</v>
+      </c>
+      <c r="AK33">
         <v>1.25</v>
-      </c>
-      <c r="T33">
-        <v>3.5</v>
-      </c>
-      <c r="U33">
-        <v>2</v>
-      </c>
-      <c r="V33">
-        <v>1.53</v>
-      </c>
-      <c r="W33">
-        <v>1.13</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.13</v>
-      </c>
-      <c r="Z33">
-        <v>4.15</v>
-      </c>
-      <c r="AA33">
-        <v>1.6</v>
-      </c>
-      <c r="AB33">
-        <v>2.19</v>
-      </c>
-      <c r="AC33">
-        <v>2.63</v>
-      </c>
-      <c r="AD33">
-        <v>1.46</v>
-      </c>
-      <c r="AE33">
-        <v>1.17</v>
-      </c>
-      <c r="AF33">
-        <v>1.53</v>
-      </c>
-      <c r="AG33">
-        <v>2.5</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.09</v>
-      </c>
-      <c r="AK33">
-        <v>1.5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="O34">
         <v>3.8</v>
       </c>
       <c r="P34">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q34">
         <v>5.35</v>
@@ -5869,7 +5869,7 @@
         <v>1.37</v>
       </c>
       <c r="T34">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="U34">
         <v>2.75</v>
@@ -5878,37 +5878,37 @@
         <v>1.44</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>3.8</v>
+        <v>3.61</v>
       </c>
       <c r="AA34">
         <v>1.85</v>
       </c>
       <c r="AB34">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
         <v>3.04</v>
       </c>
       <c r="AD34">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG34">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
         <v>1.09</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
+        <v>1.59</v>
+      </c>
+      <c r="O35">
+        <v>4.2</v>
+      </c>
+      <c r="P35">
+        <v>5</v>
+      </c>
+      <c r="Q35">
         <v>2.05</v>
       </c>
-      <c r="O35">
-        <v>3.5</v>
-      </c>
-      <c r="P35">
-        <v>3.5</v>
-      </c>
-      <c r="Q35">
-        <v>2.6</v>
-      </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U35">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V35">
+        <v>1.52</v>
+      </c>
+      <c r="W35">
+        <v>1.12</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
+        <v>1.2</v>
+      </c>
+      <c r="Z35">
+        <v>3.65</v>
+      </c>
+      <c r="AA35">
+        <v>1.62</v>
+      </c>
+      <c r="AB35">
+        <v>1.91</v>
+      </c>
+      <c r="AC35">
+        <v>2.45</v>
+      </c>
+      <c r="AD35">
         <v>1.44</v>
       </c>
-      <c r="W35">
-        <v>1.11</v>
-      </c>
-      <c r="X35">
-        <v>1.04</v>
-      </c>
-      <c r="Y35">
-        <v>1.25</v>
-      </c>
-      <c r="Z35">
-        <v>3.8</v>
-      </c>
-      <c r="AA35">
-        <v>1.76</v>
-      </c>
-      <c r="AB35">
-        <v>2</v>
-      </c>
-      <c r="AC35">
-        <v>3.1</v>
-      </c>
-      <c r="AD35">
-        <v>1.36</v>
-      </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG35">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="O36">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="Q36">
+        <v>2.6</v>
+      </c>
+      <c r="R36">
+        <v>2.25</v>
+      </c>
+      <c r="S36">
+        <v>1.3</v>
+      </c>
+      <c r="T36">
+        <v>3.2</v>
+      </c>
+      <c r="U36">
+        <v>2.6</v>
+      </c>
+      <c r="V36">
+        <v>1.44</v>
+      </c>
+      <c r="W36">
+        <v>1.11</v>
+      </c>
+      <c r="X36">
+        <v>1.04</v>
+      </c>
+      <c r="Y36">
+        <v>1.25</v>
+      </c>
+      <c r="Z36">
+        <v>3.8</v>
+      </c>
+      <c r="AA36">
+        <v>1.76</v>
+      </c>
+      <c r="AB36">
+        <v>2</v>
+      </c>
+      <c r="AC36">
+        <v>3.1</v>
+      </c>
+      <c r="AD36">
+        <v>1.36</v>
+      </c>
+      <c r="AE36">
+        <v>1.1</v>
+      </c>
+      <c r="AF36">
+        <v>1.68</v>
+      </c>
+      <c r="AG36">
         <v>2.05</v>
       </c>
-      <c r="R36">
-        <v>2.38</v>
-      </c>
-      <c r="S36">
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.29</v>
       </c>
-      <c r="T36">
-        <v>3.4</v>
-      </c>
-      <c r="U36">
-        <v>2.7</v>
-      </c>
-      <c r="V36">
-        <v>1.52</v>
-      </c>
-      <c r="W36">
-        <v>1.12</v>
-      </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.2</v>
-      </c>
-      <c r="Z36">
-        <v>3.65</v>
-      </c>
-      <c r="AA36">
-        <v>1.62</v>
-      </c>
-      <c r="AB36">
-        <v>1.91</v>
-      </c>
-      <c r="AC36">
-        <v>2.45</v>
-      </c>
-      <c r="AD36">
-        <v>1.44</v>
-      </c>
-      <c r="AE36">
-        <v>1.14</v>
-      </c>
-      <c r="AF36">
-        <v>1.65</v>
-      </c>
-      <c r="AG36">
-        <v>2.02</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.2</v>
-      </c>
       <c r="AK36">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6346,13 +6346,13 @@
         <v>3.65</v>
       </c>
       <c r="P37">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q37">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R37">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
         <v>1.3</v>
@@ -6361,13 +6361,13 @@
         <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V37">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
         <v>1.04</v>
@@ -6379,25 +6379,25 @@
         <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB37">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AC37">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="AD37">
         <v>1.39</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
         <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,46 +6503,46 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O38">
         <v>3.6</v>
       </c>
       <c r="P38">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Q38">
-        <v>4.11</v>
+        <v>4.26</v>
       </c>
       <c r="R38">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U38">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
         <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="AA38">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB38">
         <v>2.05</v>
@@ -6551,7 +6551,7 @@
         <v>2.8</v>
       </c>
       <c r="AD38">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE38">
         <v>1.15</v>
@@ -6560,7 +6560,7 @@
         <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,55 +6666,55 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="O39">
         <v>4.5</v>
       </c>
       <c r="P39">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q39">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R39">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
         <v>1.24</v>
       </c>
       <c r="T39">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U39">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="V39">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.14</v>
       </c>
       <c r="Z39">
-        <v>5.34</v>
+        <v>5</v>
       </c>
       <c r="AA39">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB39">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="AC39">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AD39">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE39">
         <v>1.19</v>
@@ -6723,7 +6723,7 @@
         <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="O41">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P41">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q41">
-        <v>2.81</v>
+        <v>3.58</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="T41">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="U41">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="V41">
+        <v>1.25</v>
+      </c>
+      <c r="W41">
+        <v>1.03</v>
+      </c>
+      <c r="X41">
+        <v>1.05</v>
+      </c>
+      <c r="Y41">
         <v>1.46</v>
       </c>
-      <c r="W41">
-        <v>1.08</v>
-      </c>
-      <c r="X41">
+      <c r="Z41">
+        <v>2.47</v>
+      </c>
+      <c r="AA41">
+        <v>2.37</v>
+      </c>
+      <c r="AB41">
+        <v>1.53</v>
+      </c>
+      <c r="AC41">
+        <v>4.35</v>
+      </c>
+      <c r="AD41">
+        <v>1.14</v>
+      </c>
+      <c r="AE41">
         <v>1.01</v>
       </c>
-      <c r="Y41">
-        <v>1.22</v>
-      </c>
-      <c r="Z41">
-        <v>3.9</v>
-      </c>
-      <c r="AA41">
-        <v>1.85</v>
-      </c>
-      <c r="AB41">
-        <v>1.98</v>
-      </c>
-      <c r="AC41">
-        <v>2.9</v>
-      </c>
-      <c r="AD41">
+      <c r="AF41">
+        <v>1.95</v>
+      </c>
+      <c r="AG41">
+        <v>1.73</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.36</v>
       </c>
-      <c r="AE41">
-        <v>1.1</v>
-      </c>
-      <c r="AF41">
-        <v>1.58</v>
-      </c>
-      <c r="AG41">
-        <v>2.15</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.31</v>
-      </c>
       <c r="AK41">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.7</v>
+        <v>1.82</v>
       </c>
       <c r="O42">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
+        <v>4.2</v>
+      </c>
+      <c r="Q42">
         <v>2.5</v>
       </c>
-      <c r="Q42">
-        <v>3.58</v>
-      </c>
       <c r="R42">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="S42">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="U42">
-        <v>3.12</v>
+        <v>2.65</v>
       </c>
       <c r="V42">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="W42">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
         <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="Z42">
-        <v>2.47</v>
+        <v>3.3</v>
       </c>
       <c r="AA42">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="AB42">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AC42">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD42">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AE42">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF42">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AK42">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="O43">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
-        <v>3.8</v>
+        <v>2.37</v>
       </c>
       <c r="Q43">
-        <v>2.43</v>
+        <v>3.3</v>
       </c>
       <c r="R43">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="U43">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="V43">
         <v>1.4</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z43">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA43">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB43">
         <v>1.75</v>
       </c>
       <c r="AC43">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD43">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE43">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AG43">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AK43">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="O44">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="P44">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q44">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R44">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="S44">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="T44">
-        <v>2.66</v>
+        <v>2.32</v>
       </c>
       <c r="U44">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="V44">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X44">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
+        <v>1.46</v>
+      </c>
+      <c r="Z44">
+        <v>2.47</v>
+      </c>
+      <c r="AA44">
+        <v>2.33</v>
+      </c>
+      <c r="AB44">
+        <v>1.51</v>
+      </c>
+      <c r="AC44">
+        <v>4.45</v>
+      </c>
+      <c r="AD44">
+        <v>1.14</v>
+      </c>
+      <c r="AE44">
+        <v>1.01</v>
+      </c>
+      <c r="AF44">
+        <v>2.05</v>
+      </c>
+      <c r="AG44">
+        <v>1.67</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
         <v>1.28</v>
       </c>
-      <c r="Z44">
-        <v>3.3</v>
-      </c>
-      <c r="AA44">
-        <v>1.91</v>
-      </c>
-      <c r="AB44">
-        <v>1.77</v>
-      </c>
-      <c r="AC44">
-        <v>3.5</v>
-      </c>
-      <c r="AD44">
-        <v>1.25</v>
-      </c>
-      <c r="AE44">
-        <v>1.08</v>
-      </c>
-      <c r="AF44">
-        <v>1.8</v>
-      </c>
-      <c r="AG44">
-        <v>1.9</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.23</v>
-      </c>
       <c r="AK44">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="O45">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P45">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="Q45">
-        <v>3.3</v>
+        <v>2.43</v>
       </c>
       <c r="R45">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S45">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="U45">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V45">
         <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA45">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB45">
         <v>1.75</v>
       </c>
       <c r="AC45">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD45">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE45">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF45">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG45">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AK45">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
+        <v>2.25</v>
+      </c>
+      <c r="O46">
+        <v>3.35</v>
+      </c>
+      <c r="P46">
+        <v>2.75</v>
+      </c>
+      <c r="Q46">
+        <v>2.81</v>
+      </c>
+      <c r="R46">
         <v>2.2</v>
       </c>
-      <c r="O46">
+      <c r="S46">
+        <v>1.32</v>
+      </c>
+      <c r="T46">
+        <v>2.86</v>
+      </c>
+      <c r="U46">
+        <v>2.4</v>
+      </c>
+      <c r="V46">
+        <v>1.46</v>
+      </c>
+      <c r="W46">
+        <v>1.08</v>
+      </c>
+      <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>1.22</v>
+      </c>
+      <c r="Z46">
+        <v>3.9</v>
+      </c>
+      <c r="AA46">
+        <v>1.85</v>
+      </c>
+      <c r="AB46">
+        <v>1.98</v>
+      </c>
+      <c r="AC46">
         <v>2.9</v>
       </c>
-      <c r="P46">
-        <v>3.2</v>
-      </c>
-      <c r="Q46">
-        <v>2.8</v>
-      </c>
-      <c r="R46">
-        <v>1.95</v>
-      </c>
-      <c r="S46">
-        <v>1.49</v>
-      </c>
-      <c r="T46">
-        <v>2.32</v>
-      </c>
-      <c r="U46">
-        <v>3.3</v>
-      </c>
-      <c r="V46">
-        <v>1.24</v>
-      </c>
-      <c r="W46">
-        <v>1.04</v>
-      </c>
-      <c r="X46">
-        <v>1.04</v>
-      </c>
-      <c r="Y46">
-        <v>1.46</v>
-      </c>
-      <c r="Z46">
-        <v>2.47</v>
-      </c>
-      <c r="AA46">
-        <v>2.33</v>
-      </c>
-      <c r="AB46">
-        <v>1.51</v>
-      </c>
-      <c r="AC46">
-        <v>4.45</v>
-      </c>
       <c r="AD46">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AE46">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AG46">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK46">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="O47">
-        <v>4.15</v>
+        <v>4.55</v>
       </c>
       <c r="P47">
-        <v>3.85</v>
+        <v>4.21</v>
       </c>
       <c r="Q47">
         <v>2</v>
@@ -7985,19 +7985,19 @@
         <v>3</v>
       </c>
       <c r="S47">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="U47">
         <v>1.73</v>
       </c>
       <c r="V47">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="W47">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -8006,25 +8006,25 @@
         <v>1.01</v>
       </c>
       <c r="Z47">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA47">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AB47">
         <v>3.98</v>
       </c>
       <c r="AC47">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AD47">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AE47">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AF47">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AG47">
         <v>3.34</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK47">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="O49">
         <v>3.4</v>
@@ -8311,22 +8311,22 @@
         <v>2.3</v>
       </c>
       <c r="S49">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U49">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V49">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
         <v>1.22</v>
@@ -8335,25 +8335,25 @@
         <v>4.2</v>
       </c>
       <c r="AA49">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB49">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AC49">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD49">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE49">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="O51">
         <v>3.3</v>
       </c>
       <c r="P51">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
       </c>
       <c r="R51">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="U51">
         <v>2.81</v>
@@ -8649,10 +8649,10 @@
         <v>1.36</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.27</v>
@@ -8661,7 +8661,7 @@
         <v>3.14</v>
       </c>
       <c r="AA51">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB51">
         <v>1.8</v>
@@ -8670,10 +8670,10 @@
         <v>3.2</v>
       </c>
       <c r="AD51">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE51">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
         <v>1.78</v>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q52">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R52">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S52">
         <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
         <v>1.1</v>
@@ -8821,7 +8821,7 @@
         <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA52">
         <v>1.7</v>
@@ -8830,19 +8830,19 @@
         <v>2.04</v>
       </c>
       <c r="AC52">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD52">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
         <v>2.15</v>
       </c>
       <c r="AG52">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AK52">
         <v>3.6</v>
@@ -9114,61 +9114,61 @@
         <v>2.1</v>
       </c>
       <c r="O54">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P54">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="Q54">
         <v>2.62</v>
       </c>
       <c r="R54">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="S54">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T54">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="U54">
-        <v>2.51</v>
+        <v>2.72</v>
       </c>
       <c r="V54">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W54">
         <v>1.1</v>
       </c>
       <c r="X54">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.25</v>
       </c>
       <c r="Z54">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AA54">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB54">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC54">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD54">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE54">
         <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG54">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
         <v>1.67</v>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N56">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N62">
@@ -10578,34 +10578,34 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="O63">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P63">
-        <v>3.23</v>
+        <v>3.8</v>
       </c>
       <c r="Q63">
         <v>2.37</v>
       </c>
       <c r="R63">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S63">
         <v>1.35</v>
       </c>
       <c r="T63">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U63">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="V63">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W63">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
         <v>1</v>
@@ -10617,22 +10617,22 @@
         <v>3.82</v>
       </c>
       <c r="AA63">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AB63">
         <v>1.98</v>
       </c>
       <c r="AC63">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD63">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE63">
         <v>1.1</v>
       </c>
       <c r="AF63">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG63">
         <v>2.11</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL63">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.9</v>
+        <v>1.94</v>
       </c>
       <c r="O2">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="Q2">
-        <v>4.8</v>
+        <v>2.63</v>
       </c>
       <c r="R2">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S2">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="T2">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U2">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="V2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y2">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="Z2">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AA2">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="AB2">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AC2">
-        <v>6.12</v>
+        <v>4.65</v>
       </c>
       <c r="AD2">
         <v>1.12</v>
       </c>
       <c r="AE2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF2">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AG2">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AK2">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.94</v>
+        <v>3.9</v>
       </c>
       <c r="O3">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="P3">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="Q3">
-        <v>2.63</v>
+        <v>4.8</v>
       </c>
       <c r="R3">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S3">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="U3">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y3">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="Z3">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AA3">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="AB3">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AC3">
-        <v>4.65</v>
+        <v>6.12</v>
       </c>
       <c r="AD3">
         <v>1.12</v>
       </c>
       <c r="AE3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AG3">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -957,11 +957,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O4">
         <v>3.23</v>
@@ -970,7 +970,7 @@
         <v>3.25</v>
       </c>
       <c r="Q4">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="R4">
         <v>2.19</v>
@@ -979,16 +979,16 @@
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U4">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -997,13 +997,13 @@
         <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>3.87</v>
       </c>
       <c r="AA4">
         <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC4">
         <v>3</v>
@@ -1018,7 +1018,7 @@
         <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q6">
+        <v>3.12</v>
+      </c>
+      <c r="R6">
+        <v>1.93</v>
+      </c>
+      <c r="S6">
+        <v>1.4</v>
+      </c>
+      <c r="T6">
         <v>2.8</v>
       </c>
-      <c r="R6">
-        <v>2.05</v>
-      </c>
-      <c r="S6">
-        <v>1.46</v>
-      </c>
-      <c r="T6">
-        <v>2.39</v>
-      </c>
       <c r="U6">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="V6">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AA6">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AB6">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC6">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AD6">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK6">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="Q7">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S7">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T7">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="U7">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z7">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA7">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AB7">
         <v>1.65</v>
       </c>
       <c r="AC7">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="AD7">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG7">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
+        <v>1.67</v>
+      </c>
+      <c r="O8">
+        <v>3.4</v>
+      </c>
+      <c r="P8">
+        <v>4.75</v>
+      </c>
+      <c r="Q8">
         <v>2.3</v>
       </c>
-      <c r="O8">
-        <v>3.1</v>
-      </c>
-      <c r="P8">
-        <v>2.75</v>
-      </c>
-      <c r="Q8">
-        <v>3.12</v>
-      </c>
       <c r="R8">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="U8">
         <v>2.8</v>
@@ -1640,37 +1640,37 @@
         <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z8">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA8">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AB8">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC8">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE8">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AG8">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>1.43</v>
+        <v>1.95</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.28</v>
+        <v>3.95</v>
       </c>
       <c r="O13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P13">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q13">
-        <v>4.1</v>
+        <v>4.32</v>
       </c>
       <c r="R13">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="S13">
         <v>1.22</v>
@@ -2449,13 +2449,13 @@
         <v>3.32</v>
       </c>
       <c r="U13">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V13">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
         <v>1.03</v>
@@ -2464,25 +2464,25 @@
         <v>1.11</v>
       </c>
       <c r="Z13">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA13">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB13">
         <v>2.6</v>
       </c>
       <c r="AC13">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AD13">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AE13">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF13">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
         <v>2.55</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
         <v>1.22</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="O22">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q22">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S22">
         <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="U22">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="V22">
         <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
         <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z22">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="AA22">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB22">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC22">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AD22">
         <v>1.29</v>
       </c>
       <c r="AE22">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF22">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AK22">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4387,16 +4387,16 @@
         <v>1.89</v>
       </c>
       <c r="O25">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q25">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="R25">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S25">
         <v>1.45</v>
@@ -4408,13 +4408,13 @@
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y25">
         <v>1.36</v>
@@ -4426,13 +4426,13 @@
         <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC25">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD25">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE25">
         <v>1.02</v>
@@ -4441,7 +4441,7 @@
         <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="O27">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q27">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="R27">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="U27">
         <v>2.45</v>
@@ -4743,10 +4743,10 @@
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
       <c r="AA27">
         <v>1.75</v>
@@ -4755,10 +4755,10 @@
         <v>2.05</v>
       </c>
       <c r="AC27">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AD27">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE27">
         <v>1.14</v>
@@ -4767,7 +4767,7 @@
         <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
         <v>1.43</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.65</v>
+        <v>3.4</v>
       </c>
       <c r="O28">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="P28">
-        <v>4.6</v>
+        <v>1.94</v>
       </c>
       <c r="Q28">
-        <v>2.1</v>
+        <v>4.04</v>
       </c>
       <c r="R28">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="S28">
         <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z28">
-        <v>2.8</v>
+        <v>3.98</v>
       </c>
       <c r="AA28">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AB28">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AC28">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AD28">
+        <v>1.33</v>
+      </c>
+      <c r="AE28">
+        <v>1.14</v>
+      </c>
+      <c r="AF28">
+        <v>1.57</v>
+      </c>
+      <c r="AG28">
+        <v>2.19</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.21</v>
+      </c>
+      <c r="AK28">
         <v>1.25</v>
-      </c>
-      <c r="AE28">
-        <v>1.07</v>
-      </c>
-      <c r="AF28">
-        <v>1.74</v>
-      </c>
-      <c r="AG28">
-        <v>1.96</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.12</v>
-      </c>
-      <c r="AK28">
-        <v>2.03</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.62</v>
+        <v>1.65</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="P29">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q29">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="R29">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="S29">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U29">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V29">
         <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
         <v>1.18</v>
       </c>
       <c r="Z29">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="AA29">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AB29">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC29">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AD29">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="AG29">
-        <v>2.21</v>
+        <v>1.96</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>1.36</v>
+        <v>2.03</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,34 +5199,34 @@
         </is>
       </c>
       <c r="N30">
-        <v>6.75</v>
+        <v>2.62</v>
       </c>
       <c r="O30">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>1.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R30">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="S30">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T30">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="U30">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="V30">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.03</v>
@@ -5235,28 +5235,28 @@
         <v>1.18</v>
       </c>
       <c r="Z30">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="AA30">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB30">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AC30">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="AD30">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE30">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="AG30">
-        <v>1.76</v>
+        <v>2.21</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>2.88</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.76</v>
+        <v>6.75</v>
       </c>
       <c r="O31">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="P31">
-        <v>3.8</v>
+        <v>1.34</v>
       </c>
       <c r="Q31">
-        <v>2.23</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T31">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="U31">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="V31">
         <v>1.48</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="AA31">
         <v>1.7</v>
       </c>
       <c r="AB31">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC31">
         <v>2.3</v>
       </c>
       <c r="AD31">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AE31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AG31">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.16</v>
+        <v>2.88</v>
       </c>
       <c r="AK31">
-        <v>2</v>
+        <v>1.06</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.37</v>
+        <v>1.76</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P32">
-        <v>2.46</v>
+        <v>3.8</v>
       </c>
       <c r="Q32">
-        <v>2.84</v>
+        <v>2.23</v>
       </c>
       <c r="R32">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T32">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="U32">
-        <v>2.01</v>
+        <v>2.34</v>
       </c>
       <c r="V32">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W32">
         <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
         <v>4.15</v>
       </c>
       <c r="AA32">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB32">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AD32">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AE32">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AK32">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.4</v>
+        <v>2.37</v>
       </c>
       <c r="O33">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>1.94</v>
+        <v>2.46</v>
       </c>
       <c r="Q33">
-        <v>4.04</v>
+        <v>2.84</v>
       </c>
       <c r="R33">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="S33">
         <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U33">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="V33">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
+        <v>1.13</v>
+      </c>
+      <c r="Z33">
+        <v>4.15</v>
+      </c>
+      <c r="AA33">
+        <v>1.65</v>
+      </c>
+      <c r="AB33">
+        <v>2.2</v>
+      </c>
+      <c r="AC33">
+        <v>2.64</v>
+      </c>
+      <c r="AD33">
+        <v>1.46</v>
+      </c>
+      <c r="AE33">
         <v>1.17</v>
       </c>
-      <c r="Z33">
-        <v>3.98</v>
-      </c>
-      <c r="AA33">
-        <v>1.52</v>
-      </c>
-      <c r="AB33">
-        <v>2.15</v>
-      </c>
-      <c r="AC33">
-        <v>2.2</v>
-      </c>
-      <c r="AD33">
-        <v>1.33</v>
-      </c>
-      <c r="AE33">
-        <v>1.14</v>
-      </c>
       <c r="AF33">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG33">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AK33">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="O35">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="Q35">
+        <v>2.6</v>
+      </c>
+      <c r="R35">
+        <v>2.25</v>
+      </c>
+      <c r="S35">
+        <v>1.3</v>
+      </c>
+      <c r="T35">
+        <v>3.2</v>
+      </c>
+      <c r="U35">
+        <v>2.6</v>
+      </c>
+      <c r="V35">
+        <v>1.44</v>
+      </c>
+      <c r="W35">
+        <v>1.11</v>
+      </c>
+      <c r="X35">
+        <v>1.04</v>
+      </c>
+      <c r="Y35">
+        <v>1.25</v>
+      </c>
+      <c r="Z35">
+        <v>3.8</v>
+      </c>
+      <c r="AA35">
+        <v>1.76</v>
+      </c>
+      <c r="AB35">
+        <v>2</v>
+      </c>
+      <c r="AC35">
+        <v>3.1</v>
+      </c>
+      <c r="AD35">
+        <v>1.36</v>
+      </c>
+      <c r="AE35">
+        <v>1.1</v>
+      </c>
+      <c r="AF35">
+        <v>1.68</v>
+      </c>
+      <c r="AG35">
         <v>2.05</v>
       </c>
-      <c r="R35">
-        <v>2.38</v>
-      </c>
-      <c r="S35">
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.29</v>
       </c>
-      <c r="T35">
-        <v>3.4</v>
-      </c>
-      <c r="U35">
-        <v>2.7</v>
-      </c>
-      <c r="V35">
-        <v>1.52</v>
-      </c>
-      <c r="W35">
-        <v>1.12</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.2</v>
-      </c>
-      <c r="Z35">
-        <v>3.65</v>
-      </c>
-      <c r="AA35">
-        <v>1.62</v>
-      </c>
-      <c r="AB35">
-        <v>1.91</v>
-      </c>
-      <c r="AC35">
-        <v>2.45</v>
-      </c>
-      <c r="AD35">
-        <v>1.44</v>
-      </c>
-      <c r="AE35">
-        <v>1.14</v>
-      </c>
-      <c r="AF35">
-        <v>1.65</v>
-      </c>
-      <c r="AG35">
-        <v>2.02</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.2</v>
-      </c>
       <c r="AK35">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
+        <v>1.59</v>
+      </c>
+      <c r="O36">
+        <v>4.2</v>
+      </c>
+      <c r="P36">
+        <v>5</v>
+      </c>
+      <c r="Q36">
         <v>2.05</v>
       </c>
-      <c r="O36">
-        <v>3.5</v>
-      </c>
-      <c r="P36">
-        <v>3.5</v>
-      </c>
-      <c r="Q36">
-        <v>2.6</v>
-      </c>
       <c r="R36">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U36">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V36">
+        <v>1.52</v>
+      </c>
+      <c r="W36">
+        <v>1.12</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>1.2</v>
+      </c>
+      <c r="Z36">
+        <v>3.65</v>
+      </c>
+      <c r="AA36">
+        <v>1.62</v>
+      </c>
+      <c r="AB36">
+        <v>1.91</v>
+      </c>
+      <c r="AC36">
+        <v>2.45</v>
+      </c>
+      <c r="AD36">
         <v>1.44</v>
       </c>
-      <c r="W36">
-        <v>1.11</v>
-      </c>
-      <c r="X36">
-        <v>1.04</v>
-      </c>
-      <c r="Y36">
-        <v>1.25</v>
-      </c>
-      <c r="Z36">
-        <v>3.8</v>
-      </c>
-      <c r="AA36">
-        <v>1.76</v>
-      </c>
-      <c r="AB36">
-        <v>2</v>
-      </c>
-      <c r="AC36">
-        <v>3.1</v>
-      </c>
-      <c r="AD36">
-        <v>1.36</v>
-      </c>
       <c r="AE36">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="O37">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q37">
         <v>2.25</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S37">
         <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U37">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="V37">
         <v>1.5</v>
@@ -6376,28 +6376,28 @@
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="AA37">
         <v>1.72</v>
       </c>
       <c r="AB37">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC37">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD37">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE37">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,22 +6512,22 @@
         <v>1.9</v>
       </c>
       <c r="Q38">
-        <v>4.26</v>
+        <v>3.9</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
         <v>3.02</v>
       </c>
       <c r="U38">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W38">
         <v>1.08</v>
@@ -6536,31 +6536,31 @@
         <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AA38">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AB38">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AC38">
         <v>2.8</v>
       </c>
       <c r="AD38">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE38">
         <v>1.15</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG38">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.86</v>
       </c>
       <c r="AK38">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
@@ -6675,19 +6675,19 @@
         <v>5.75</v>
       </c>
       <c r="Q39">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R39">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S39">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T39">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U39">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="V39">
         <v>1.57</v>
@@ -6696,31 +6696,31 @@
         <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
         <v>5</v>
       </c>
       <c r="AA39">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB39">
-        <v>2.58</v>
+        <v>2.41</v>
       </c>
       <c r="AC39">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AD39">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE39">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF39">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG39">
         <v>2.25</v>
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q40">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R40">
         <v>2.38</v>
       </c>
       <c r="S40">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U40">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V40">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W40">
         <v>1.17</v>
@@ -6862,31 +6862,31 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z40">
         <v>5.75</v>
       </c>
       <c r="AA40">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB40">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC40">
         <v>2.08</v>
       </c>
       <c r="AD40">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE40">
         <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG40">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AK40">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="O41">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P41">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q41">
-        <v>3.58</v>
+        <v>2.81</v>
       </c>
       <c r="R41">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="U41">
-        <v>3.12</v>
+        <v>2.4</v>
       </c>
       <c r="V41">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="W41">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>2.47</v>
+        <v>3.9</v>
       </c>
       <c r="AA41">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="AB41">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="AC41">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="AD41">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AG41">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK41">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="O42">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P42">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q42">
+        <v>3.58</v>
+      </c>
+      <c r="R42">
+        <v>1.95</v>
+      </c>
+      <c r="S42">
+        <v>1.47</v>
+      </c>
+      <c r="T42">
         <v>2.5</v>
       </c>
-      <c r="R42">
-        <v>2.04</v>
-      </c>
-      <c r="S42">
-        <v>1.36</v>
-      </c>
-      <c r="T42">
-        <v>2.66</v>
-      </c>
       <c r="U42">
-        <v>2.65</v>
+        <v>3.12</v>
       </c>
       <c r="V42">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
         <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="Z42">
-        <v>3.3</v>
+        <v>2.47</v>
       </c>
       <c r="AA42">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="AB42">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AC42">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="AD42">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE42">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF42">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG42">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK42">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,65 +7318,65 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="O43">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="Q43">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="R43">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="U43">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="V43">
         <v>1.4</v>
       </c>
       <c r="W43">
+        <v>1.07</v>
+      </c>
+      <c r="X43">
+        <v>1.05</v>
+      </c>
+      <c r="Y43">
+        <v>1.28</v>
+      </c>
+      <c r="Z43">
+        <v>3.3</v>
+      </c>
+      <c r="AA43">
+        <v>1.91</v>
+      </c>
+      <c r="AB43">
+        <v>1.77</v>
+      </c>
+      <c r="AC43">
+        <v>3.5</v>
+      </c>
+      <c r="AD43">
+        <v>1.25</v>
+      </c>
+      <c r="AE43">
         <v>1.08</v>
       </c>
-      <c r="X43">
-        <v>1.02</v>
-      </c>
-      <c r="Y43">
-        <v>1.29</v>
-      </c>
-      <c r="Z43">
-        <v>3.5</v>
-      </c>
-      <c r="AA43">
+      <c r="AF43">
+        <v>1.8</v>
+      </c>
+      <c r="AG43">
         <v>1.9</v>
       </c>
-      <c r="AB43">
-        <v>1.75</v>
-      </c>
-      <c r="AC43">
-        <v>3.4</v>
-      </c>
-      <c r="AD43">
-        <v>1.3</v>
-      </c>
-      <c r="AE43">
-        <v>1.1</v>
-      </c>
-      <c r="AF43">
-        <v>1.71</v>
-      </c>
-      <c r="AG43">
-        <v>1.98</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="AK43">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="O44">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P44">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="Q44">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="R44">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S44">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="U44">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="V44">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="W44">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="Z44">
-        <v>2.47</v>
+        <v>3.5</v>
       </c>
       <c r="AA44">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AB44">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AC44">
-        <v>4.45</v>
+        <v>3.4</v>
       </c>
       <c r="AD44">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AE44">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AG44">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AK44">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="O45">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P45">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="Q45">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="R45">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S45">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="T45">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="U45">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X45">
+        <v>1.04</v>
+      </c>
+      <c r="Y45">
+        <v>1.46</v>
+      </c>
+      <c r="Z45">
+        <v>2.47</v>
+      </c>
+      <c r="AA45">
+        <v>2.33</v>
+      </c>
+      <c r="AB45">
+        <v>1.51</v>
+      </c>
+      <c r="AC45">
+        <v>4.45</v>
+      </c>
+      <c r="AD45">
+        <v>1.14</v>
+      </c>
+      <c r="AE45">
         <v>1.01</v>
       </c>
-      <c r="Y45">
-        <v>1.3</v>
-      </c>
-      <c r="Z45">
-        <v>3.25</v>
-      </c>
-      <c r="AA45">
+      <c r="AF45">
         <v>2.05</v>
       </c>
-      <c r="AB45">
-        <v>1.75</v>
-      </c>
-      <c r="AC45">
-        <v>3.6</v>
-      </c>
-      <c r="AD45">
-        <v>1.25</v>
-      </c>
-      <c r="AE45">
-        <v>1.04</v>
-      </c>
-      <c r="AF45">
-        <v>1.83</v>
-      </c>
       <c r="AG45">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK45">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,65 +7807,65 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="O46">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P46">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q46">
-        <v>2.81</v>
+        <v>2.43</v>
       </c>
       <c r="R46">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S46">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T46">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="U46">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="V46">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z46">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="AA46">
+        <v>2.05</v>
+      </c>
+      <c r="AB46">
+        <v>1.75</v>
+      </c>
+      <c r="AC46">
+        <v>3.6</v>
+      </c>
+      <c r="AD46">
+        <v>1.25</v>
+      </c>
+      <c r="AE46">
+        <v>1.04</v>
+      </c>
+      <c r="AF46">
+        <v>1.83</v>
+      </c>
+      <c r="AG46">
         <v>1.85</v>
       </c>
-      <c r="AB46">
-        <v>1.98</v>
-      </c>
-      <c r="AC46">
-        <v>2.9</v>
-      </c>
-      <c r="AD46">
-        <v>1.36</v>
-      </c>
-      <c r="AE46">
-        <v>1.1</v>
-      </c>
-      <c r="AF46">
-        <v>1.58</v>
-      </c>
-      <c r="AG46">
-        <v>2.15</v>
-      </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AK46">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>11</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="O48">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="P48">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Q48">
         <v>7.5</v>
       </c>
       <c r="R48">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="S48">
         <v>1.2</v>
       </c>
       <c r="T48">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="U48">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="V48">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W48">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z48">
-        <v>6.45</v>
+        <v>6.6</v>
       </c>
       <c r="AA48">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB48">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AC48">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AD48">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AE48">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF48">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8465,13 +8465,13 @@
         <v>3.7</v>
       </c>
       <c r="P50">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q50">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="R50">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
         <v>1.2</v>
@@ -8480,10 +8480,10 @@
         <v>4</v>
       </c>
       <c r="U50">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V50">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W50">
         <v>1.17</v>
@@ -8510,7 +8510,7 @@
         <v>1.65</v>
       </c>
       <c r="AE50">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF50">
         <v>1.44</v>
@@ -8532,7 +8532,7 @@
         <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8951,61 +8951,61 @@
         <v>1.62</v>
       </c>
       <c r="O53">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="P53">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="Q53">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R53">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S53">
         <v>1.22</v>
       </c>
       <c r="T53">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U53">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V53">
         <v>1.67</v>
       </c>
       <c r="W53">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X53">
         <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z53">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="AA53">
         <v>1.4</v>
       </c>
       <c r="AB53">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AC53">
         <v>2.14</v>
       </c>
       <c r="AD53">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE53">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF53">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG53">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK53">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N55">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N61">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="O2">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="P2">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q2">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R2">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="S2">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T2">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U2">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="V2">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y2">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Z2">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AA2">
         <v>2.42</v>
       </c>
       <c r="AB2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC2">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="AD2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AG2">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK2">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O3">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q3">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R3">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T3">
         <v>2.12</v>
@@ -828,34 +828,34 @@
         <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Y3">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z3">
         <v>2.18</v>
       </c>
       <c r="AA3">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="AB3">
         <v>1.4</v>
       </c>
       <c r="AC3">
-        <v>6.12</v>
+        <v>6.31</v>
       </c>
       <c r="AD3">
         <v>1.12</v>
       </c>
       <c r="AE3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AG3">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AK3">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -991,16 +991,16 @@
         <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z4">
         <v>3.87</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB4">
         <v>1.9</v>
@@ -1012,10 +1012,10 @@
         <v>1.33</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
         <v>2.02</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK4">
         <v>1.9</v>
@@ -1120,68 +1120,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N5">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>5.5</v>
+        <v>5.85</v>
       </c>
       <c r="P5">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Q5">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="R5">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="S5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T5">
-        <v>3.92</v>
+        <v>4.5</v>
       </c>
       <c r="U5">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="V5">
         <v>1.83</v>
       </c>
       <c r="W5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z5">
-        <v>6.05</v>
+        <v>6.15</v>
       </c>
       <c r="AA5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AB5">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="AC5">
+        <v>1.84</v>
+      </c>
+      <c r="AD5">
         <v>1.83</v>
-      </c>
-      <c r="AD5">
-        <v>1.84</v>
       </c>
       <c r="AE5">
         <v>1.35</v>
       </c>
       <c r="AF5">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK5">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,28 +1287,28 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P6">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q6">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="R6">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S6">
         <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="V6">
         <v>1.36</v>
@@ -1317,34 +1317,34 @@
         <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
         <v>3.1</v>
       </c>
       <c r="AA6">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AB6">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC6">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD6">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
         <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q7">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="R7">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T7">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V7">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
         <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z7">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA7">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AB7">
+        <v>1.64</v>
+      </c>
+      <c r="AC7">
+        <v>4.1</v>
+      </c>
+      <c r="AD7">
+        <v>1.21</v>
+      </c>
+      <c r="AE7">
+        <v>1.07</v>
+      </c>
+      <c r="AF7">
+        <v>1.86</v>
+      </c>
+      <c r="AG7">
+        <v>1.87</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.19</v>
+      </c>
+      <c r="AK7">
         <v>1.65</v>
-      </c>
-      <c r="AC7">
-        <v>3.74</v>
-      </c>
-      <c r="AD7">
-        <v>1.19</v>
-      </c>
-      <c r="AE7">
-        <v>1.03</v>
-      </c>
-      <c r="AF7">
-        <v>1.85</v>
-      </c>
-      <c r="AG7">
-        <v>1.79</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.28</v>
-      </c>
-      <c r="AK7">
-        <v>1.57</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>4.75</v>
+        <v>1.98</v>
       </c>
       <c r="Q8">
-        <v>2.3</v>
+        <v>4.06</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T8">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="U8">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z8">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA8">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="AB8">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC8">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="AD8">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AG8">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="O9">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="Q9">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="T9">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="U9">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="AA9">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AB9">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AC9">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AD9">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE9">
         <v>1.03</v>
       </c>
       <c r="AF9">
+        <v>1.95</v>
+      </c>
+      <c r="AG9">
+        <v>1.71</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.3</v>
+      </c>
+      <c r="AK9">
         <v>1.91</v>
-      </c>
-      <c r="AG9">
-        <v>1.75</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.73</v>
-      </c>
-      <c r="AK9">
-        <v>1.22</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O10">
         <v>3.2</v>
@@ -1948,7 +1948,7 @@
         <v>2.37</v>
       </c>
       <c r="Q10">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="R10">
         <v>1.95</v>
@@ -1960,13 +1960,13 @@
         <v>2.62</v>
       </c>
       <c r="U10">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V10">
         <v>1.33</v>
       </c>
       <c r="W10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1.06</v>
@@ -1981,7 +1981,7 @@
         <v>2.1</v>
       </c>
       <c r="AB10">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC10">
         <v>3.95</v>
@@ -1993,10 +1993,10 @@
         <v>1.07</v>
       </c>
       <c r="AF10">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AG10">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="O11">
         <v>5.5</v>
       </c>
       <c r="P11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="S11">
         <v>1.3</v>
@@ -2123,7 +2123,7 @@
         <v>3.08</v>
       </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V11">
         <v>1.51</v>
@@ -2132,34 +2132,34 @@
         <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>4.33</v>
+        <v>3.88</v>
       </c>
       <c r="AA11">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB11">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC11">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
         <v>2.3</v>
       </c>
       <c r="AG11">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AK11">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O12">
         <v>2.85</v>
       </c>
       <c r="P12">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q12">
         <v>2.6</v>
       </c>
       <c r="R12">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="S12">
         <v>1.56</v>
@@ -2298,16 +2298,16 @@
         <v>1.07</v>
       </c>
       <c r="Y12">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="Z12">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="AA12">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AB12">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AC12">
         <v>5.25</v>
@@ -2316,13 +2316,13 @@
         <v>1.13</v>
       </c>
       <c r="AE12">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF12">
         <v>2.15</v>
       </c>
       <c r="AG12">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AK12">
         <v>1.7</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O13">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="P13">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q13">
-        <v>4.32</v>
+        <v>4.25</v>
       </c>
       <c r="R13">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="S13">
         <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.32</v>
+        <v>3.9</v>
       </c>
       <c r="U13">
         <v>2.07</v>
       </c>
       <c r="V13">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W13">
         <v>1.15</v>
@@ -2464,13 +2464,13 @@
         <v>1.11</v>
       </c>
       <c r="Z13">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AB13">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="AC13">
         <v>2.14</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
         <v>1.22</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="O14">
         <v>4.2</v>
@@ -2600,55 +2600,55 @@
         <v>5.7</v>
       </c>
       <c r="Q14">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="R14">
         <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
         <v>2.4</v>
       </c>
       <c r="V14">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="AA14">
+        <v>1.63</v>
+      </c>
+      <c r="AB14">
+        <v>2.12</v>
+      </c>
+      <c r="AC14">
+        <v>2.56</v>
+      </c>
+      <c r="AD14">
+        <v>1.42</v>
+      </c>
+      <c r="AE14">
+        <v>1.14</v>
+      </c>
+      <c r="AF14">
         <v>1.72</v>
       </c>
-      <c r="AB14">
-        <v>2.07</v>
-      </c>
-      <c r="AC14">
-        <v>2.66</v>
-      </c>
-      <c r="AD14">
-        <v>1.37</v>
-      </c>
-      <c r="AE14">
-        <v>1.16</v>
-      </c>
-      <c r="AF14">
-        <v>1.86</v>
-      </c>
       <c r="AG14">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK14">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O15">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q15">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
         <v>3.4</v>
       </c>
       <c r="U15">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V15">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W15">
         <v>1.11</v>
@@ -2787,7 +2787,7 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
         <v>5</v>
@@ -2799,7 +2799,7 @@
         <v>2.25</v>
       </c>
       <c r="AC15">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AD15">
         <v>1.5</v>
@@ -2827,7 +2827,7 @@
         <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="O16">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q16">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R16">
         <v>2.5</v>
@@ -2935,10 +2935,10 @@
         <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U16">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V16">
         <v>1.62</v>
@@ -2950,16 +2950,16 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z16">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA16">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB16">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC16">
         <v>2.29</v>
@@ -2968,13 +2968,13 @@
         <v>1.57</v>
       </c>
       <c r="AE16">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AG16">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P17">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="Q17">
-        <v>3.56</v>
+        <v>3.06</v>
       </c>
       <c r="R17">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T17">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="U17">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V17">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W17">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z17">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA17">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AB17">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AC17">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD17">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AE17">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF17">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AG17">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.44</v>
+        <v>2.11</v>
       </c>
       <c r="O18">
         <v>3.6</v>
       </c>
       <c r="P18">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q18">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="R18">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="S18">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
         <v>4.5</v>
@@ -3267,10 +3267,10 @@
         <v>1.78</v>
       </c>
       <c r="V18">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3279,25 +3279,25 @@
         <v>1.06</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>6.15</v>
       </c>
       <c r="AA18">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AB18">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="AC18">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AD18">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AE18">
         <v>1.33</v>
       </c>
       <c r="AF18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG18">
         <v>3</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.28</v>
+        <v>3.25</v>
       </c>
       <c r="O19">
-        <v>4.95</v>
+        <v>3.45</v>
       </c>
       <c r="P19">
-        <v>6.6</v>
+        <v>1.95</v>
       </c>
       <c r="Q19">
-        <v>1.73</v>
+        <v>3.74</v>
       </c>
       <c r="R19">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z19">
-        <v>5.84</v>
+        <v>4.55</v>
       </c>
       <c r="AA19">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AB19">
-        <v>2.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC19">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AD19">
-        <v>1.96</v>
+        <v>1.46</v>
       </c>
       <c r="AE19">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
-        <v>3.3</v>
+        <v>1.24</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,65 +3569,65 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="O20">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="U20">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="V20">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z20">
-        <v>5.1</v>
+        <v>4.35</v>
       </c>
       <c r="AA20">
+        <v>1.59</v>
+      </c>
+      <c r="AB20">
+        <v>2.35</v>
+      </c>
+      <c r="AC20">
+        <v>2.3</v>
+      </c>
+      <c r="AD20">
+        <v>1.49</v>
+      </c>
+      <c r="AE20">
+        <v>1.17</v>
+      </c>
+      <c r="AF20">
         <v>1.5</v>
       </c>
-      <c r="AB20">
+      <c r="AG20">
         <v>2.5</v>
       </c>
-      <c r="AC20">
-        <v>2.2</v>
-      </c>
-      <c r="AD20">
-        <v>1.48</v>
-      </c>
-      <c r="AE20">
-        <v>1.19</v>
-      </c>
-      <c r="AF20">
-        <v>1.44</v>
-      </c>
-      <c r="AG20">
-        <v>2.63</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="AK20">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.98</v>
+        <v>1.28</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="P21">
-        <v>2.05</v>
+        <v>7.8</v>
       </c>
       <c r="Q21">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="R21">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="S21">
+        <v>1.22</v>
+      </c>
+      <c r="T21">
+        <v>4</v>
+      </c>
+      <c r="U21">
+        <v>2</v>
+      </c>
+      <c r="V21">
+        <v>1.75</v>
+      </c>
+      <c r="W21">
         <v>1.2</v>
-      </c>
-      <c r="T21">
-        <v>2.75</v>
-      </c>
-      <c r="U21">
-        <v>2.22</v>
-      </c>
-      <c r="V21">
-        <v>1.57</v>
-      </c>
-      <c r="W21">
-        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>5.89</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AB21">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="AC21">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AD21">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AF21">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AG21">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK21">
-        <v>1.26</v>
+        <v>2.95</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="P22">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q22">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="R22">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
         <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U22">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
         <v>1.08</v>
@@ -3928,28 +3928,28 @@
         <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="AA22">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB22">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC22">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD22">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE22">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG22">
         <v>2</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="O23">
         <v>4</v>
       </c>
       <c r="P23">
-        <v>5.13</v>
+        <v>4.9</v>
       </c>
       <c r="Q23">
         <v>2.15</v>
@@ -4079,16 +4079,16 @@
         <v>3.22</v>
       </c>
       <c r="U23">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="V23">
         <v>1.46</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
         <v>1.19</v>
@@ -4097,25 +4097,25 @@
         <v>3.76</v>
       </c>
       <c r="AA23">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB23">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC23">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD23">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF23">
         <v>1.79</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,43 +4221,43 @@
         </is>
       </c>
       <c r="N24">
+        <v>2.6</v>
+      </c>
+      <c r="O24">
+        <v>2.7</v>
+      </c>
+      <c r="P24">
         <v>2.65</v>
       </c>
-      <c r="O24">
-        <v>2.85</v>
-      </c>
-      <c r="P24">
-        <v>2.85</v>
-      </c>
       <c r="Q24">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="R24">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="S24">
         <v>1.52</v>
       </c>
       <c r="T24">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U24">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="V24">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
         <v>1.45</v>
       </c>
       <c r="Z24">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="AA24">
         <v>2.5</v>
@@ -4266,19 +4266,19 @@
         <v>1.5</v>
       </c>
       <c r="AC24">
-        <v>4.85</v>
+        <v>5.2</v>
       </c>
       <c r="AD24">
         <v>1.11</v>
       </c>
       <c r="AE24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF24">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AG24">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="O25">
         <v>3.3</v>
       </c>
       <c r="P25">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="Q25">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R25">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S25">
         <v>1.45</v>
       </c>
       <c r="T25">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="U25">
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W25">
         <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z25">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AA25">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AB25">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC25">
         <v>3.55</v>
       </c>
       <c r="AD25">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE25">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF25">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG25">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK25">
         <v>1.91</v>
@@ -4547,22 +4547,22 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="O26">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="P26">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q26">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R26">
         <v>3.4</v>
       </c>
       <c r="S26">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="T26">
         <v>5</v>
@@ -4571,10 +4571,10 @@
         <v>1.7</v>
       </c>
       <c r="V26">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="W26">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4583,25 +4583,25 @@
         <v>1.08</v>
       </c>
       <c r="Z26">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="AA26">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AB26">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AC26">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AD26">
         <v>2.3</v>
       </c>
       <c r="AE26">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG26">
         <v>1.95</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK26">
         <v>6</v>
@@ -4710,28 +4710,28 @@
         </is>
       </c>
       <c r="N27">
+        <v>2.6</v>
+      </c>
+      <c r="O27">
+        <v>3.35</v>
+      </c>
+      <c r="P27">
         <v>2.55</v>
       </c>
-      <c r="O27">
-        <v>3.45</v>
-      </c>
-      <c r="P27">
-        <v>2.5</v>
-      </c>
       <c r="Q27">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="R27">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="S27">
         <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="U27">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="V27">
         <v>1.44</v>
@@ -4743,31 +4743,31 @@
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="AA27">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB27">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC27">
-        <v>2.59</v>
+        <v>3.11</v>
       </c>
       <c r="AD27">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE27">
         <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG27">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
         <v>1.43</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="O28">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="Q28">
-        <v>4.04</v>
+        <v>2.8</v>
       </c>
       <c r="R28">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="U28">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="V28">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z28">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="AA28">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AB28">
         <v>2.15</v>
       </c>
       <c r="AC28">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
         <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG28">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AK28">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.65</v>
+        <v>3.15</v>
       </c>
       <c r="O29">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>4.6</v>
+        <v>1.91</v>
       </c>
       <c r="Q29">
+        <v>3.5</v>
+      </c>
+      <c r="R29">
         <v>2.1</v>
-      </c>
-      <c r="R29">
-        <v>2.34</v>
       </c>
       <c r="S29">
         <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="U29">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W29">
+        <v>1.07</v>
+      </c>
+      <c r="X29">
+        <v>1.02</v>
+      </c>
+      <c r="Y29">
+        <v>1.17</v>
+      </c>
+      <c r="Z29">
+        <v>3.98</v>
+      </c>
+      <c r="AA29">
+        <v>1.52</v>
+      </c>
+      <c r="AB29">
+        <v>2.2</v>
+      </c>
+      <c r="AC29">
+        <v>2.64</v>
+      </c>
+      <c r="AD29">
+        <v>1.41</v>
+      </c>
+      <c r="AE29">
         <v>1.1</v>
       </c>
-      <c r="X29">
-        <v>1.04</v>
-      </c>
-      <c r="Y29">
-        <v>1.18</v>
-      </c>
-      <c r="Z29">
-        <v>2.8</v>
-      </c>
-      <c r="AA29">
-        <v>1.61</v>
-      </c>
-      <c r="AB29">
-        <v>1.93</v>
-      </c>
-      <c r="AC29">
-        <v>2.88</v>
-      </c>
-      <c r="AD29">
-        <v>1.25</v>
-      </c>
-      <c r="AE29">
-        <v>1.07</v>
-      </c>
       <c r="AF29">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AG29">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AK29">
-        <v>2.03</v>
+        <v>1.23</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.62</v>
+        <v>1.76</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
+        <v>3.7</v>
+      </c>
+      <c r="Q30">
+        <v>2.27</v>
+      </c>
+      <c r="R30">
         <v>2.3</v>
       </c>
-      <c r="Q30">
-        <v>3</v>
-      </c>
-      <c r="R30">
-        <v>2.05</v>
-      </c>
       <c r="S30">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="U30">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W30">
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z30">
-        <v>3.95</v>
+        <v>4.19</v>
       </c>
       <c r="AA30">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AB30">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AC30">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AD30">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>6.75</v>
+        <v>1.63</v>
       </c>
       <c r="O31">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>1.34</v>
+        <v>4.5</v>
       </c>
       <c r="Q31">
-        <v>6</v>
+        <v>2.16</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="S31">
+        <v>1.29</v>
+      </c>
+      <c r="T31">
+        <v>2.35</v>
+      </c>
+      <c r="U31">
+        <v>2.5</v>
+      </c>
+      <c r="V31">
+        <v>1.36</v>
+      </c>
+      <c r="W31">
+        <v>1.08</v>
+      </c>
+      <c r="X31">
+        <v>1.04</v>
+      </c>
+      <c r="Y31">
         <v>1.26</v>
       </c>
-      <c r="T31">
-        <v>3.24</v>
-      </c>
-      <c r="U31">
-        <v>2.04</v>
-      </c>
-      <c r="V31">
-        <v>1.48</v>
-      </c>
-      <c r="W31">
-        <v>1.09</v>
-      </c>
-      <c r="X31">
-        <v>1.03</v>
-      </c>
-      <c r="Y31">
-        <v>1.18</v>
-      </c>
       <c r="Z31">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA31">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AB31">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC31">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD31">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AG31">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>2.88</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>1.06</v>
+        <v>2.1</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="O32">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q32">
-        <v>2.23</v>
+        <v>3.38</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="U32">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V32">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W32">
         <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="AA32">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC32">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="AD32">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AG32">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AK32">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.37</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="P33">
-        <v>2.46</v>
+        <v>1.32</v>
       </c>
       <c r="Q33">
-        <v>2.84</v>
+        <v>6.95</v>
       </c>
       <c r="R33">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="V33">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W33">
         <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="Z33">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="AA33">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB33">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AC33">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AD33">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AE33">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF33">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.4</v>
+        <v>2.74</v>
       </c>
       <c r="AK33">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="O34">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P34">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="Q34">
-        <v>5.35</v>
+        <v>5.1</v>
       </c>
       <c r="R34">
         <v>2.25</v>
@@ -5869,47 +5869,47 @@
         <v>1.37</v>
       </c>
       <c r="T34">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U34">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
       <c r="AA34">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
+        <v>1.92</v>
+      </c>
+      <c r="AC34">
+        <v>3.08</v>
+      </c>
+      <c r="AD34">
+        <v>1.28</v>
+      </c>
+      <c r="AE34">
+        <v>1.06</v>
+      </c>
+      <c r="AF34">
+        <v>1.8</v>
+      </c>
+      <c r="AG34">
         <v>1.95</v>
       </c>
-      <c r="AC34">
-        <v>3.04</v>
-      </c>
-      <c r="AD34">
-        <v>1.29</v>
-      </c>
-      <c r="AE34">
-        <v>1.07</v>
-      </c>
-      <c r="AF34">
-        <v>1.83</v>
-      </c>
-      <c r="AG34">
-        <v>1.9</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK34">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q35">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U35">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="V35">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AA35">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC35">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AD35">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="O36">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P36">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="Q36">
         <v>2.05</v>
       </c>
       <c r="R36">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
         <v>1.29</v>
@@ -6198,10 +6198,10 @@
         <v>3.4</v>
       </c>
       <c r="U36">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="V36">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W36">
         <v>1.12</v>
@@ -6210,31 +6210,31 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="AA36">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB36">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AC36">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AD36">
         <v>1.44</v>
       </c>
       <c r="AE36">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF36">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG36">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK36">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="O37">
         <v>3.75</v>
       </c>
       <c r="P37">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="Q37">
         <v>2.25</v>
@@ -6358,13 +6358,13 @@
         <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
         <v>2.57</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W37">
         <v>1.08</v>
@@ -6376,28 +6376,28 @@
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB37">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC37">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD37">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
         <v>1.91</v>
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O38">
         <v>3.6</v>
       </c>
       <c r="P38">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="Q38">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="R38">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V38">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
         <v>1.08</v>
@@ -6536,16 +6536,16 @@
         <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA38">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB38">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AC38">
         <v>2.8</v>
@@ -6554,13 +6554,13 @@
         <v>1.43</v>
       </c>
       <c r="AE38">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AK38">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="O39">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P39">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="Q39">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R39">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S39">
         <v>1.23</v>
       </c>
       <c r="T39">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="U39">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="V39">
         <v>1.57</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z39">
         <v>5</v>
       </c>
       <c r="AA39">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB39">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="AC39">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AD39">
+        <v>1.61</v>
+      </c>
+      <c r="AE39">
+        <v>1.26</v>
+      </c>
+      <c r="AF39">
         <v>1.6</v>
       </c>
-      <c r="AE39">
-        <v>1.2</v>
-      </c>
-      <c r="AF39">
-        <v>1.59</v>
-      </c>
       <c r="AG39">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P40">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="Q40">
         <v>3.1</v>
       </c>
       <c r="R40">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="S40">
         <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U40">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V40">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W40">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z40">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="AA40">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB40">
         <v>2.6</v>
       </c>
       <c r="AC40">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AD40">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE40">
+        <v>1.22</v>
+      </c>
+      <c r="AF40">
+        <v>1.38</v>
+      </c>
+      <c r="AG40">
+        <v>2.77</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.25</v>
       </c>
-      <c r="AF40">
-        <v>1.36</v>
-      </c>
-      <c r="AG40">
-        <v>2.8</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.49</v>
-      </c>
       <c r="AK40">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="O41">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P41">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q41">
-        <v>2.81</v>
+        <v>3.68</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="T41">
-        <v>2.86</v>
+        <v>2.29</v>
       </c>
       <c r="U41">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="V41">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="Z41">
-        <v>3.9</v>
+        <v>2.61</v>
       </c>
       <c r="AA41">
-        <v>1.85</v>
+        <v>2.48</v>
       </c>
       <c r="AB41">
-        <v>1.98</v>
+        <v>1.49</v>
       </c>
       <c r="AC41">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="AD41">
+        <v>1.14</v>
+      </c>
+      <c r="AE41">
+        <v>1</v>
+      </c>
+      <c r="AF41">
+        <v>1.95</v>
+      </c>
+      <c r="AG41">
+        <v>1.75</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.44</v>
+      </c>
+      <c r="AK41">
         <v>1.36</v>
-      </c>
-      <c r="AE41">
-        <v>1.1</v>
-      </c>
-      <c r="AF41">
-        <v>1.58</v>
-      </c>
-      <c r="AG41">
-        <v>2.15</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.31</v>
-      </c>
-      <c r="AK41">
-        <v>1.5</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.7</v>
+        <v>2.03</v>
       </c>
       <c r="O42">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P42">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q42">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="R42">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="S42">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T42">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U42">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="V42">
         <v>1.25</v>
       </c>
       <c r="W42">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y42">
         <v>1.46</v>
       </c>
       <c r="Z42">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="AA42">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="AB42">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC42">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="AD42">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG42">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="Q43">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R43">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="U43">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="V43">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W43">
         <v>1.07</v>
       </c>
       <c r="X43">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z43">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="AA43">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AB43">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AC43">
-        <v>3.5</v>
+        <v>2.51</v>
       </c>
       <c r="AD43">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AE43">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG43">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
+        <v>1.77</v>
+      </c>
+      <c r="O44">
+        <v>3.35</v>
+      </c>
+      <c r="P44">
+        <v>4.1</v>
+      </c>
+      <c r="Q44">
         <v>2.45</v>
       </c>
-      <c r="O44">
-        <v>3.1</v>
-      </c>
-      <c r="P44">
-        <v>2.37</v>
-      </c>
-      <c r="Q44">
-        <v>3.3</v>
-      </c>
       <c r="R44">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T44">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U44">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="V44">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y44">
         <v>1.29</v>
       </c>
       <c r="Z44">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA44">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AB44">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC44">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD44">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE44">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,80 +7644,80 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="O45">
+        <v>3.2</v>
+      </c>
+      <c r="P45">
+        <v>2.5</v>
+      </c>
+      <c r="Q45">
+        <v>3.25</v>
+      </c>
+      <c r="R45">
+        <v>2.15</v>
+      </c>
+      <c r="S45">
+        <v>1.32</v>
+      </c>
+      <c r="T45">
         <v>2.9</v>
       </c>
-      <c r="P45">
-        <v>3.2</v>
-      </c>
-      <c r="Q45">
-        <v>2.8</v>
-      </c>
-      <c r="R45">
-        <v>1.95</v>
-      </c>
-      <c r="S45">
-        <v>1.49</v>
-      </c>
-      <c r="T45">
-        <v>2.32</v>
-      </c>
       <c r="U45">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="V45">
+        <v>1.4</v>
+      </c>
+      <c r="W45">
+        <v>1.09</v>
+      </c>
+      <c r="X45">
+        <v>1</v>
+      </c>
+      <c r="Y45">
+        <v>1.22</v>
+      </c>
+      <c r="Z45">
+        <v>3.48</v>
+      </c>
+      <c r="AA45">
+        <v>1.78</v>
+      </c>
+      <c r="AB45">
+        <v>1.89</v>
+      </c>
+      <c r="AC45">
+        <v>2.88</v>
+      </c>
+      <c r="AD45">
+        <v>1.32</v>
+      </c>
+      <c r="AE45">
+        <v>1.09</v>
+      </c>
+      <c r="AF45">
+        <v>1.62</v>
+      </c>
+      <c r="AG45">
+        <v>2.12</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
         <v>1.24</v>
       </c>
-      <c r="W45">
-        <v>1.04</v>
-      </c>
-      <c r="X45">
-        <v>1.04</v>
-      </c>
-      <c r="Y45">
-        <v>1.46</v>
-      </c>
-      <c r="Z45">
-        <v>2.47</v>
-      </c>
-      <c r="AA45">
-        <v>2.33</v>
-      </c>
-      <c r="AB45">
-        <v>1.51</v>
-      </c>
-      <c r="AC45">
-        <v>4.45</v>
-      </c>
-      <c r="AD45">
-        <v>1.14</v>
-      </c>
-      <c r="AE45">
-        <v>1.01</v>
-      </c>
-      <c r="AF45">
-        <v>2.05</v>
-      </c>
-      <c r="AG45">
-        <v>1.67</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.28</v>
-      </c>
       <c r="AK45">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,65 +7807,65 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="O46">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P46">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q46">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="R46">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S46">
+        <v>1.41</v>
+      </c>
+      <c r="T46">
+        <v>2.73</v>
+      </c>
+      <c r="U46">
+        <v>2.85</v>
+      </c>
+      <c r="V46">
         <v>1.36</v>
       </c>
-      <c r="T46">
-        <v>2.62</v>
-      </c>
-      <c r="U46">
-        <v>2.7</v>
-      </c>
-      <c r="V46">
-        <v>1.4</v>
-      </c>
       <c r="W46">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z46">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA46">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB46">
         <v>1.75</v>
       </c>
       <c r="AC46">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AD46">
         <v>1.25</v>
       </c>
       <c r="AE46">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF46">
+        <v>1.84</v>
+      </c>
+      <c r="AG46">
         <v>1.83</v>
       </c>
-      <c r="AG46">
-        <v>1.85</v>
-      </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK46">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O47">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="P47">
-        <v>4.21</v>
+        <v>3.75</v>
       </c>
       <c r="Q47">
         <v>2</v>
       </c>
       <c r="R47">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="S47">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T47">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="U47">
         <v>1.73</v>
       </c>
       <c r="V47">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="W47">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Z47">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA47">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AB47">
-        <v>3.98</v>
+        <v>4.5</v>
       </c>
       <c r="AC47">
         <v>1.6</v>
       </c>
       <c r="AD47">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="AE47">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AF47">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AG47">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AK47">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,58 +8133,58 @@
         </is>
       </c>
       <c r="N48">
-        <v>9.359999999999999</v>
+        <v>11</v>
       </c>
       <c r="O48">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="P48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Q48">
         <v>7.5</v>
       </c>
       <c r="R48">
-        <v>3.04</v>
+        <v>2.71</v>
       </c>
       <c r="S48">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T48">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U48">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V48">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="W48">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z48">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="AA48">
         <v>1.33</v>
       </c>
       <c r="AB48">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AC48">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AD48">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AE48">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF48">
         <v>1.57</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.13</v>
+        <v>3.21</v>
       </c>
       <c r="AK48">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="O49">
         <v>3.4</v>
       </c>
       <c r="P49">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q49">
         <v>2.8</v>
@@ -8311,49 +8311,49 @@
         <v>2.3</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T49">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
         <v>1.11</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z49">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AA49">
         <v>1.69</v>
       </c>
       <c r="AB49">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AC49">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AD49">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
         <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O50">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P50">
         <v>1.74</v>
@@ -8474,13 +8474,13 @@
         <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U50">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="V50">
         <v>1.61</v>
@@ -8498,25 +8498,25 @@
         <v>5.3</v>
       </c>
       <c r="AA50">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB50">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AC50">
         <v>2.2</v>
       </c>
       <c r="AD50">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE50">
         <v>1.22</v>
       </c>
       <c r="AF50">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
+        <v>1.89</v>
+      </c>
+      <c r="AK50">
         <v>1.17</v>
-      </c>
-      <c r="AK50">
-        <v>1.18</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.85</v>
+        <v>1.29</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>5.25</v>
       </c>
       <c r="P51">
-        <v>3.84</v>
+        <v>8.4</v>
       </c>
       <c r="Q51">
+        <v>1.72</v>
+      </c>
+      <c r="R51">
         <v>2.5</v>
       </c>
-      <c r="R51">
+      <c r="S51">
+        <v>1.3</v>
+      </c>
+      <c r="T51">
+        <v>3.26</v>
+      </c>
+      <c r="U51">
+        <v>2.35</v>
+      </c>
+      <c r="V51">
+        <v>1.51</v>
+      </c>
+      <c r="W51">
+        <v>1.12</v>
+      </c>
+      <c r="X51">
+        <v>1.02</v>
+      </c>
+      <c r="Y51">
+        <v>1.23</v>
+      </c>
+      <c r="Z51">
+        <v>3.92</v>
+      </c>
+      <c r="AA51">
+        <v>1.67</v>
+      </c>
+      <c r="AB51">
         <v>2.04</v>
       </c>
-      <c r="S51">
-        <v>1.4</v>
-      </c>
-      <c r="T51">
-        <v>2.93</v>
-      </c>
-      <c r="U51">
-        <v>2.81</v>
-      </c>
-      <c r="V51">
-        <v>1.36</v>
-      </c>
-      <c r="W51">
-        <v>1.04</v>
-      </c>
-      <c r="X51">
-        <v>1.01</v>
-      </c>
-      <c r="Y51">
-        <v>1.27</v>
-      </c>
-      <c r="Z51">
-        <v>3.14</v>
-      </c>
-      <c r="AA51">
-        <v>2.02</v>
-      </c>
-      <c r="AB51">
-        <v>1.8</v>
-      </c>
       <c r="AC51">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD51">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AG51">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK51">
-        <v>1.83</v>
+        <v>3.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="O52">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="P52">
-        <v>8.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q52">
-        <v>1.73</v>
+        <v>2.49</v>
       </c>
       <c r="R52">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T52">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="U52">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
+        <v>1.33</v>
+      </c>
+      <c r="Z52">
+        <v>3.2</v>
+      </c>
+      <c r="AA52">
+        <v>2.05</v>
+      </c>
+      <c r="AB52">
+        <v>1.75</v>
+      </c>
+      <c r="AC52">
+        <v>3.34</v>
+      </c>
+      <c r="AD52">
+        <v>1.24</v>
+      </c>
+      <c r="AE52">
+        <v>1.08</v>
+      </c>
+      <c r="AF52">
+        <v>1.83</v>
+      </c>
+      <c r="AG52">
+        <v>1.85</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.22</v>
       </c>
-      <c r="Z52">
-        <v>3.9</v>
-      </c>
-      <c r="AA52">
-        <v>1.7</v>
-      </c>
-      <c r="AB52">
-        <v>2.04</v>
-      </c>
-      <c r="AC52">
-        <v>2.88</v>
-      </c>
-      <c r="AD52">
-        <v>1.4</v>
-      </c>
-      <c r="AE52">
-        <v>1.12</v>
-      </c>
-      <c r="AF52">
-        <v>2.15</v>
-      </c>
-      <c r="AG52">
-        <v>1.62</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.05</v>
-      </c>
       <c r="AK52">
-        <v>3.6</v>
+        <v>1.83</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8944,23 +8944,23 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O53">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P53">
         <v>4.07</v>
       </c>
       <c r="Q53">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="R53">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="S53">
         <v>1.22</v>
@@ -8969,43 +8969,43 @@
         <v>3.9</v>
       </c>
       <c r="U53">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V53">
         <v>1.67</v>
       </c>
       <c r="W53">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X53">
         <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z53">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA53">
         <v>1.4</v>
       </c>
       <c r="AB53">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AC53">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AD53">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE53">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF53">
         <v>1.44</v>
       </c>
       <c r="AG53">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK53">
         <v>2.08</v>
@@ -9126,25 +9126,25 @@
         <v>2.08</v>
       </c>
       <c r="S54">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="U54">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="V54">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z54">
         <v>3.28</v>
@@ -9153,10 +9153,10 @@
         <v>1.83</v>
       </c>
       <c r="AB54">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC54">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD54">
         <v>1.3</v>
@@ -9168,7 +9168,7 @@
         <v>1.68</v>
       </c>
       <c r="AG54">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N60">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="O63">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P63">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="Q63">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="R63">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S63">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T63">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U63">
-        <v>2.52</v>
+        <v>2.71</v>
       </c>
       <c r="V63">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W63">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X63">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z63">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AA63">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB63">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC63">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD63">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE63">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF63">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG63">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AL63">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -635,52 +635,52 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="O2">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P2">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q2">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="R2">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="S2">
         <v>1.56</v>
       </c>
       <c r="T2">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U2">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="V2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
         <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y2">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z2">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AA2">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AB2">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC2">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="AD2">
         <v>1.13</v>
@@ -689,7 +689,7 @@
         <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AG2">
         <v>1.62</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK2">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O3">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="P3">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R3">
         <v>1.8</v>
@@ -816,46 +816,46 @@
         <v>1.63</v>
       </c>
       <c r="T3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
         <v>3.8</v>
       </c>
       <c r="V3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
         <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y3">
         <v>1.6</v>
       </c>
       <c r="Z3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AA3">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="AB3">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC3">
-        <v>6.31</v>
+        <v>6.5</v>
       </c>
       <c r="AD3">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AG3">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="O11">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q11">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R11">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T11">
         <v>3.08</v>
       </c>
       <c r="U11">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V11">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W11">
         <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z11">
-        <v>3.88</v>
+        <v>4.36</v>
       </c>
       <c r="AA11">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="AD11">
         <v>1.41</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF11">
         <v>2.3</v>
       </c>
       <c r="AG11">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.04</v>
       </c>
       <c r="AK11">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O12">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P12">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q12">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="R12">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="S12">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="T12">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="U12">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="V12">
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
+        <v>1.1</v>
+      </c>
+      <c r="Y12">
+        <v>1.65</v>
+      </c>
+      <c r="Z12">
+        <v>2.28</v>
+      </c>
+      <c r="AA12">
+        <v>3.06</v>
+      </c>
+      <c r="AB12">
+        <v>1.4</v>
+      </c>
+      <c r="AC12">
+        <v>7</v>
+      </c>
+      <c r="AD12">
         <v>1.07</v>
       </c>
-      <c r="Y12">
-        <v>1.47</v>
-      </c>
-      <c r="Z12">
-        <v>2.35</v>
-      </c>
-      <c r="AA12">
-        <v>2.43</v>
-      </c>
-      <c r="AB12">
-        <v>1.42</v>
-      </c>
-      <c r="AC12">
-        <v>5.25</v>
-      </c>
-      <c r="AD12">
-        <v>1.13</v>
-      </c>
       <c r="AE12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AG12">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK12">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="O17">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P17">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q17">
-        <v>3.06</v>
+        <v>3.74</v>
       </c>
       <c r="R17">
+        <v>2.15</v>
+      </c>
+      <c r="S17">
+        <v>1.25</v>
+      </c>
+      <c r="T17">
+        <v>3.5</v>
+      </c>
+      <c r="U17">
+        <v>2.25</v>
+      </c>
+      <c r="V17">
+        <v>1.57</v>
+      </c>
+      <c r="W17">
+        <v>1.15</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>1.13</v>
+      </c>
+      <c r="Z17">
+        <v>4.55</v>
+      </c>
+      <c r="AA17">
+        <v>1.46</v>
+      </c>
+      <c r="AB17">
+        <v>1.94</v>
+      </c>
+      <c r="AC17">
         <v>2.38</v>
       </c>
-      <c r="S17">
-        <v>1.18</v>
-      </c>
-      <c r="T17">
-        <v>3.8</v>
-      </c>
-      <c r="U17">
-        <v>2.1</v>
-      </c>
-      <c r="V17">
-        <v>1.51</v>
-      </c>
-      <c r="W17">
-        <v>1.18</v>
-      </c>
-      <c r="X17">
-        <v>1.02</v>
-      </c>
-      <c r="Y17">
-        <v>1.14</v>
-      </c>
-      <c r="Z17">
-        <v>5.5</v>
-      </c>
-      <c r="AA17">
-        <v>1.44</v>
-      </c>
-      <c r="AB17">
-        <v>2.55</v>
-      </c>
-      <c r="AC17">
-        <v>2.3</v>
-      </c>
       <c r="AD17">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AE17">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF17">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG17">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="O19">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="Q19">
-        <v>3.74</v>
+        <v>3.06</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>4.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA19">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB19">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="AC19">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD19">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF19">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4224,22 +4224,22 @@
         <v>2.6</v>
       </c>
       <c r="O24">
+        <v>2.8</v>
+      </c>
+      <c r="P24">
         <v>2.7</v>
       </c>
-      <c r="P24">
-        <v>2.65</v>
-      </c>
       <c r="Q24">
-        <v>3.46</v>
+        <v>3.66</v>
       </c>
       <c r="R24">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="S24">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="T24">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="U24">
         <v>3.35</v>
@@ -4251,10 +4251,10 @@
         <v>1.02</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y24">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Z24">
         <v>2.44</v>
@@ -4266,19 +4266,19 @@
         <v>1.5</v>
       </c>
       <c r="AC24">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="AD24">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE24">
         <v>1.01</v>
       </c>
       <c r="AF24">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AG24">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK24">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.35</v>
+        <v>3.15</v>
       </c>
       <c r="O28">
+        <v>3.4</v>
+      </c>
+      <c r="P28">
+        <v>1.91</v>
+      </c>
+      <c r="Q28">
         <v>3.5</v>
       </c>
-      <c r="P28">
-        <v>2.45</v>
-      </c>
-      <c r="Q28">
-        <v>2.8</v>
-      </c>
       <c r="R28">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="U28">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V28">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z28">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="AA28">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AB28">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC28">
-        <v>2.49</v>
+        <v>2.64</v>
       </c>
       <c r="AD28">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q29">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="U29">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V29">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z29">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="AA29">
+        <v>1.6</v>
+      </c>
+      <c r="AB29">
+        <v>2.15</v>
+      </c>
+      <c r="AC29">
+        <v>2.49</v>
+      </c>
+      <c r="AD29">
+        <v>1.42</v>
+      </c>
+      <c r="AE29">
+        <v>1.14</v>
+      </c>
+      <c r="AF29">
         <v>1.52</v>
       </c>
-      <c r="AB29">
-        <v>2.2</v>
-      </c>
-      <c r="AC29">
-        <v>2.64</v>
-      </c>
-      <c r="AD29">
+      <c r="AG29">
+        <v>2.38</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.41</v>
       </c>
-      <c r="AE29">
-        <v>1.1</v>
-      </c>
-      <c r="AF29">
-        <v>1.57</v>
-      </c>
-      <c r="AG29">
-        <v>2.21</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.21</v>
-      </c>
       <c r="AK29">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.8</v>
+        <v>2.03</v>
       </c>
       <c r="O41">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P41">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="Q41">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="S41">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="T41">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="U41">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="V41">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W41">
         <v>1.05</v>
@@ -7025,31 +7025,31 @@
         <v>1.06</v>
       </c>
       <c r="Y41">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z41">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="AA41">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="AB41">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AC41">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AD41">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE41">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF41">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG41">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="O42">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P42">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
       </c>
       <c r="R42">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="U42">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="V42">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="Z42">
-        <v>2.52</v>
+        <v>3.42</v>
       </c>
       <c r="AA42">
-        <v>2.31</v>
+        <v>1.88</v>
       </c>
       <c r="AB42">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="AC42">
-        <v>4.8</v>
+        <v>2.51</v>
       </c>
       <c r="AD42">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="AE42">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
+        <v>1.73</v>
+      </c>
+      <c r="AG42">
         <v>2.05</v>
-      </c>
-      <c r="AG42">
-        <v>1.67</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="O43">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P43">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Q43">
-        <v>2.88</v>
+        <v>3.68</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="T43">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="U43">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="V43">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y43">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="Z43">
-        <v>3.42</v>
+        <v>2.61</v>
       </c>
       <c r="AA43">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="AB43">
-        <v>1.93</v>
+        <v>1.49</v>
       </c>
       <c r="AC43">
-        <v>2.51</v>
+        <v>4.45</v>
       </c>
       <c r="AD43">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="AE43">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AF43">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AG43">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK43">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AL43">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -603,96 +603,96 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>1.85</v>
+        <v>4.4</v>
       </c>
       <c r="O2">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="P2">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>2.63</v>
+        <v>5.5</v>
       </c>
       <c r="R2">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="S2">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="T2">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y2">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="Z2">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AA2">
-        <v>2.55</v>
+        <v>2.96</v>
       </c>
       <c r="AB2">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AC2">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD2">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE2">
         <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AG2">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -701,41 +701,41 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "82"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK2">
-        <v>1.74</v>
+        <v>1.08</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -766,19 +766,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -790,72 +790,72 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
+        <v>1.85</v>
+      </c>
+      <c r="O3">
+        <v>2.9</v>
+      </c>
+      <c r="P3">
+        <v>4</v>
+      </c>
+      <c r="Q3">
+        <v>2.63</v>
+      </c>
+      <c r="R3">
+        <v>1.9</v>
+      </c>
+      <c r="S3">
+        <v>1.56</v>
+      </c>
+      <c r="T3">
+        <v>2.24</v>
+      </c>
+      <c r="U3">
+        <v>3.75</v>
+      </c>
+      <c r="V3">
+        <v>1.3</v>
+      </c>
+      <c r="W3">
+        <v>1.01</v>
+      </c>
+      <c r="X3">
+        <v>1.07</v>
+      </c>
+      <c r="Y3">
+        <v>1.46</v>
+      </c>
+      <c r="Z3">
+        <v>2.46</v>
+      </c>
+      <c r="AA3">
+        <v>2.55</v>
+      </c>
+      <c r="AB3">
+        <v>1.5</v>
+      </c>
+      <c r="AC3">
         <v>4.4</v>
       </c>
-      <c r="O3">
-        <v>2.84</v>
-      </c>
-      <c r="P3">
-        <v>1.8</v>
-      </c>
-      <c r="Q3">
-        <v>5.5</v>
-      </c>
-      <c r="R3">
-        <v>1.8</v>
-      </c>
-      <c r="S3">
-        <v>1.63</v>
-      </c>
-      <c r="T3">
-        <v>2.1</v>
-      </c>
-      <c r="U3">
-        <v>3.8</v>
-      </c>
-      <c r="V3">
-        <v>1.22</v>
-      </c>
-      <c r="W3">
-        <v>1.03</v>
-      </c>
-      <c r="X3">
-        <v>1.1</v>
-      </c>
-      <c r="Y3">
-        <v>1.6</v>
-      </c>
-      <c r="Z3">
-        <v>2.2</v>
-      </c>
-      <c r="AA3">
-        <v>2.96</v>
-      </c>
-      <c r="AB3">
-        <v>1.35</v>
-      </c>
-      <c r="AC3">
-        <v>6.5</v>
-      </c>
       <c r="AD3">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE3">
         <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AG3">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -864,41 +864,41 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["80", "90+4"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK3">
-        <v>1.08</v>
+        <v>1.74</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,130 +938,130 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="O4">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="P4">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="Q4">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="R4">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V4">
         <v>1.42</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.87</v>
+        <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC4">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD4">
         <v>1.33</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
         <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "90+6"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70", "87", "90+13"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1116,115 +1116,115 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>8</v>
+        <v>10.2</v>
       </c>
       <c r="O5">
-        <v>5.85</v>
+        <v>5.4</v>
       </c>
       <c r="P5">
         <v>1.21</v>
       </c>
       <c r="Q5">
-        <v>7.6</v>
+        <v>8.15</v>
       </c>
       <c r="R5">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="S5">
         <v>1.2</v>
       </c>
       <c r="T5">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="U5">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="W5">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
+        <v>1.1</v>
+      </c>
+      <c r="Z5">
+        <v>5.05</v>
+      </c>
+      <c r="AA5">
+        <v>1.44</v>
+      </c>
+      <c r="AB5">
+        <v>2.62</v>
+      </c>
+      <c r="AC5">
+        <v>2.08</v>
+      </c>
+      <c r="AD5">
+        <v>1.64</v>
+      </c>
+      <c r="AE5">
+        <v>1.25</v>
+      </c>
+      <c r="AF5">
+        <v>1.83</v>
+      </c>
+      <c r="AG5">
+        <v>1.84</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>["90+2"]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.07</v>
       </c>
-      <c r="Z5">
-        <v>6.15</v>
-      </c>
-      <c r="AA5">
-        <v>1.32</v>
-      </c>
-      <c r="AB5">
-        <v>2.56</v>
-      </c>
-      <c r="AC5">
-        <v>1.84</v>
-      </c>
-      <c r="AD5">
-        <v>1.83</v>
-      </c>
-      <c r="AE5">
-        <v>1.35</v>
-      </c>
-      <c r="AF5">
-        <v>1.8</v>
-      </c>
-      <c r="AG5">
-        <v>1.96</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.05</v>
-      </c>
       <c r="AK5">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,130 +1264,130 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="O6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>2.8</v>
+        <v>3.21</v>
       </c>
       <c r="Q6">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="R6">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U6">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AD6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
         <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "45", "75", "78", "90"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "68"]</t>
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK6">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1442,72 +1442,72 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O7">
         <v>3.1</v>
       </c>
       <c r="P7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q7">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S7">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="U7">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W7">
         <v>1.03</v>
       </c>
       <c r="X7">
+        <v>1.04</v>
+      </c>
+      <c r="Y7">
+        <v>1.33</v>
+      </c>
+      <c r="Z7">
+        <v>3</v>
+      </c>
+      <c r="AA7">
+        <v>2.15</v>
+      </c>
+      <c r="AB7">
+        <v>1.66</v>
+      </c>
+      <c r="AC7">
+        <v>4</v>
+      </c>
+      <c r="AD7">
+        <v>1.22</v>
+      </c>
+      <c r="AE7">
         <v>1.05</v>
       </c>
-      <c r="Y7">
-        <v>1.34</v>
-      </c>
-      <c r="Z7">
-        <v>2.78</v>
-      </c>
-      <c r="AA7">
-        <v>2.08</v>
-      </c>
-      <c r="AB7">
-        <v>1.64</v>
-      </c>
-      <c r="AC7">
-        <v>4.1</v>
-      </c>
-      <c r="AD7">
-        <v>1.21</v>
-      </c>
-      <c r="AE7">
-        <v>1.07</v>
-      </c>
       <c r="AF7">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AG7">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1516,41 +1516,41 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67", "89"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK7">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,54 +1590,54 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P8">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Q8">
-        <v>4.06</v>
+        <v>4.35</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S8">
         <v>1.5</v>
       </c>
       <c r="T8">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="U8">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="V8">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
         <v>1.02</v>
@@ -1646,74 +1646,74 @@
         <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z8">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AA8">
         <v>2.35</v>
       </c>
       <c r="AB8">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC8">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AD8">
         <v>1.16</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75", "87"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "33", "34", "57"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1765,118 +1765,118 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="Q9">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S9">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="U9">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W9">
         <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA9">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AB9">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
-        <v>4.1</v>
+        <v>3.48</v>
       </c>
       <c r="AD9">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AG9">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>["90+4"]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1928,118 +1928,118 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
         <v>2.75</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="R10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S10">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T10">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="U10">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="V10">
         <v>1.33</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z10">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA10">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB10">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC10">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="AD10">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG10">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+2", "90+2"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "77"]</t>
         </is>
       </c>
       <c r="AJ10">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AK10">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="O11">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>11</v>
       </c>
       <c r="Q11">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="R11">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="S11">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T11">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="U11">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="V11">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>4.36</v>
+        <v>4.15</v>
       </c>
       <c r="AA11">
         <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC11">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="AD11">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE11">
         <v>1.16</v>
       </c>
       <c r="AF11">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AG11">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AK11">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O12">
         <v>2.8</v>
@@ -2277,49 +2277,49 @@
         <v>2.78</v>
       </c>
       <c r="R12">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="S12">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T12">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="U12">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="V12">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y12">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z12">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AA12">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="AB12">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC12">
-        <v>7</v>
+        <v>5.45</v>
       </c>
       <c r="AD12">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AE12">
         <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AG12">
         <v>1.5</v>
@@ -2338,7 +2338,7 @@
         <v>1.34</v>
       </c>
       <c r="AK12">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2405,130 +2405,130 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="O13">
-        <v>3.76</v>
+        <v>3.87</v>
       </c>
       <c r="P13">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q13">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="R13">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="S13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U13">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="V13">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W13">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>5.5</v>
+        <v>6.58</v>
       </c>
       <c r="AA13">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AB13">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC13">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AD13">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AE13">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF13">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG13">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "49"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "63", "69", "82", "90+1"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,57 +2568,57 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="O14">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P14">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="Q14">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="R14">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S14">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U14">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1.02</v>
@@ -2630,68 +2630,68 @@
         <v>4.15</v>
       </c>
       <c r="AA14">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB14">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC14">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD14">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE14">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>["20", "23", "45", "90"]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ14">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,16 +2731,16 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -2750,111 +2750,111 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="O15">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="Q15">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="U15">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="V15">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z15">
+        <v>4.33</v>
+      </c>
+      <c r="AA15">
+        <v>1.66</v>
+      </c>
+      <c r="AB15">
+        <v>2.23</v>
+      </c>
+      <c r="AC15">
+        <v>2.41</v>
+      </c>
+      <c r="AD15">
+        <v>1.45</v>
+      </c>
+      <c r="AE15">
+        <v>1.15</v>
+      </c>
+      <c r="AF15">
+        <v>1.5</v>
+      </c>
+      <c r="AG15">
+        <v>2.42</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>["25"]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>["38"]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.25</v>
+      </c>
+      <c r="AK15">
+        <v>1.37</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
         <v>5</v>
       </c>
-      <c r="AA15">
-        <v>1.59</v>
-      </c>
-      <c r="AB15">
-        <v>2.25</v>
-      </c>
-      <c r="AC15">
-        <v>2.53</v>
-      </c>
-      <c r="AD15">
-        <v>1.5</v>
-      </c>
-      <c r="AE15">
-        <v>1.2</v>
-      </c>
-      <c r="AF15">
-        <v>1.42</v>
-      </c>
-      <c r="AG15">
-        <v>2.5</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
+      <c r="AN15">
+        <v>5</v>
+      </c>
+      <c r="AO15">
+        <v>11</v>
+      </c>
+      <c r="AP15">
+        <v>9</v>
+      </c>
+      <c r="AQ15">
+        <v>1.32</v>
+      </c>
+      <c r="AR15">
         <v>1.26</v>
       </c>
-      <c r="AK15">
-        <v>1.64</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>-1</v>
-      </c>
-      <c r="AN15">
-        <v>-1</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>-1</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
       <c r="AS15">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,54 +2894,54 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P16">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q16">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R16">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T16">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="U16">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="V16">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W16">
         <v>1.12</v>
@@ -2950,74 +2950,74 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z16">
+        <v>4.9</v>
+      </c>
+      <c r="AA16">
+        <v>1.53</v>
+      </c>
+      <c r="AB16">
+        <v>2.4</v>
+      </c>
+      <c r="AC16">
+        <v>2.33</v>
+      </c>
+      <c r="AD16">
+        <v>1.59</v>
+      </c>
+      <c r="AE16">
+        <v>1.19</v>
+      </c>
+      <c r="AF16">
+        <v>1.44</v>
+      </c>
+      <c r="AG16">
+        <v>2.53</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>["67"]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>["25", "72", "76"]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.26</v>
+      </c>
+      <c r="AK16">
+        <v>1.78</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>10</v>
+      </c>
+      <c r="AN16">
         <v>5</v>
       </c>
-      <c r="AA16">
-        <v>1.44</v>
-      </c>
-      <c r="AB16">
-        <v>2.55</v>
-      </c>
-      <c r="AC16">
-        <v>2.29</v>
-      </c>
-      <c r="AD16">
-        <v>1.57</v>
-      </c>
-      <c r="AE16">
-        <v>1.22</v>
-      </c>
-      <c r="AF16">
-        <v>1.41</v>
-      </c>
-      <c r="AG16">
-        <v>2.46</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.21</v>
-      </c>
-      <c r="AK16">
-        <v>1.84</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>-1</v>
-      </c>
-      <c r="AN16">
-        <v>-1</v>
-      </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3048,139 +3048,139 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="O17">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q17">
-        <v>3.74</v>
+        <v>3.32</v>
       </c>
       <c r="R17">
+        <v>2.41</v>
+      </c>
+      <c r="S17">
+        <v>1.19</v>
+      </c>
+      <c r="T17">
+        <v>3.78</v>
+      </c>
+      <c r="U17">
         <v>2.15</v>
       </c>
-      <c r="S17">
-        <v>1.25</v>
-      </c>
-      <c r="T17">
-        <v>3.5</v>
-      </c>
-      <c r="U17">
-        <v>2.25</v>
-      </c>
       <c r="V17">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z17">
-        <v>4.55</v>
+        <v>5.25</v>
       </c>
       <c r="AA17">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB17">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="AC17">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AD17">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AE17">
         <v>1.2</v>
       </c>
       <c r="AF17">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AG17">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "55", "90+2"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,130 +3220,130 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O18">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P18">
+        <v>2.7</v>
+      </c>
+      <c r="Q18">
+        <v>2.4</v>
+      </c>
+      <c r="R18">
         <v>2.6</v>
       </c>
-      <c r="Q18">
-        <v>2.64</v>
-      </c>
-      <c r="R18">
-        <v>2.44</v>
-      </c>
       <c r="S18">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="T18">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="U18">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="V18">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z18">
-        <v>6.15</v>
+        <v>6.46</v>
       </c>
       <c r="AA18">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB18">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="AC18">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AD18">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="AE18">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AF18">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AG18">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4"]</t>
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK18">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="O19">
-        <v>4</v>
+        <v>3.54</v>
       </c>
       <c r="P19">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q19">
-        <v>3.06</v>
+        <v>3.78</v>
       </c>
       <c r="R19">
+        <v>2.26</v>
+      </c>
+      <c r="S19">
+        <v>1.23</v>
+      </c>
+      <c r="T19">
+        <v>3.46</v>
+      </c>
+      <c r="U19">
+        <v>2.19</v>
+      </c>
+      <c r="V19">
+        <v>1.55</v>
+      </c>
+      <c r="W19">
+        <v>1.11</v>
+      </c>
+      <c r="X19">
+        <v>1.01</v>
+      </c>
+      <c r="Y19">
+        <v>1.13</v>
+      </c>
+      <c r="Z19">
+        <v>4.55</v>
+      </c>
+      <c r="AA19">
+        <v>1.6</v>
+      </c>
+      <c r="AB19">
+        <v>2.3</v>
+      </c>
+      <c r="AC19">
         <v>2.38</v>
       </c>
-      <c r="S19">
-        <v>1.18</v>
-      </c>
-      <c r="T19">
-        <v>3.8</v>
-      </c>
-      <c r="U19">
-        <v>2.1</v>
-      </c>
-      <c r="V19">
-        <v>1.51</v>
-      </c>
-      <c r="W19">
-        <v>1.18</v>
-      </c>
-      <c r="X19">
-        <v>1.02</v>
-      </c>
-      <c r="Y19">
-        <v>1.14</v>
-      </c>
-      <c r="Z19">
-        <v>5.5</v>
-      </c>
-      <c r="AA19">
-        <v>1.44</v>
-      </c>
-      <c r="AB19">
-        <v>2.55</v>
-      </c>
-      <c r="AC19">
-        <v>2.3</v>
-      </c>
       <c r="AD19">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AE19">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AF19">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AG19">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3546,45 +3546,45 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="R20">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T20">
         <v>3.18</v>
@@ -3602,74 +3602,74 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="AA20">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB20">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC20">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AD20">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AE20">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "80"]</t>
         </is>
       </c>
       <c r="AJ20">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,130 +3709,130 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
         <v>1.28</v>
       </c>
       <c r="O21">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="P21">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="R21">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="S21">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="U21">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V21">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W21">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>5.89</v>
+        <v>6.45</v>
       </c>
       <c r="AA21">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.59</v>
+        <v>2.87</v>
       </c>
       <c r="AC21">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AD21">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AE21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF21">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG21">
         <v>2.07</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["79", "90+4"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39"]</t>
         </is>
       </c>
       <c r="AJ21">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK21">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="O22">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="P22">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="Q22">
-        <v>2.45</v>
+        <v>2.99</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S22">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="U22">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V22">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
         <v>1.08</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z22">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="AA22">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB22">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC22">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AD22">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE22">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AK22">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4035,130 +4035,130 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="O23">
         <v>4</v>
       </c>
       <c r="P23">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q23">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="R23">
+        <v>2.28</v>
+      </c>
+      <c r="S23">
+        <v>1.24</v>
+      </c>
+      <c r="T23">
+        <v>3.55</v>
+      </c>
+      <c r="U23">
+        <v>2.26</v>
+      </c>
+      <c r="V23">
+        <v>1.55</v>
+      </c>
+      <c r="W23">
+        <v>1.11</v>
+      </c>
+      <c r="X23">
+        <v>1.03</v>
+      </c>
+      <c r="Y23">
+        <v>1.14</v>
+      </c>
+      <c r="Z23">
+        <v>4.45</v>
+      </c>
+      <c r="AA23">
+        <v>1.6</v>
+      </c>
+      <c r="AB23">
+        <v>2.3</v>
+      </c>
+      <c r="AC23">
         <v>2.43</v>
       </c>
-      <c r="S23">
-        <v>1.28</v>
-      </c>
-      <c r="T23">
-        <v>3.22</v>
-      </c>
-      <c r="U23">
-        <v>2.47</v>
-      </c>
-      <c r="V23">
-        <v>1.46</v>
-      </c>
-      <c r="W23">
-        <v>1.07</v>
-      </c>
-      <c r="X23">
-        <v>1.02</v>
-      </c>
-      <c r="Y23">
-        <v>1.19</v>
-      </c>
-      <c r="Z23">
-        <v>3.76</v>
-      </c>
-      <c r="AA23">
-        <v>1.76</v>
-      </c>
-      <c r="AB23">
-        <v>1.98</v>
-      </c>
-      <c r="AC23">
-        <v>3.1</v>
-      </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG23">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "28", "87"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AJ23">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -4210,14 +4210,14 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AJ24">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="P25">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="R25">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S25">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T25">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U25">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="V25">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
         <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z25">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA25">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="AB25">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AC25">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="AD25">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE25">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4524,57 +4524,57 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="O26">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q26">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="R26">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="S26">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="U26">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="V26">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="W26">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4583,71 +4583,71 @@
         <v>1.08</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AB26">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AC26">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AD26">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AE26">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AF26">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG26">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "45", "69", "74", "87"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AJ26">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AK26">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>32</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O27">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="P27">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="Q27">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="R27">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T27">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="U27">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="AA27">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AC27">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AD27">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AE27">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK27">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,34 +4873,34 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
         <v>1.91</v>
       </c>
       <c r="Q28">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T28">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U28">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
         <v>1.02</v>
@@ -4909,28 +4909,28 @@
         <v>1.17</v>
       </c>
       <c r="Z28">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AA28">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AB28">
         <v>2.2</v>
       </c>
       <c r="AC28">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="AD28">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AF28">
         <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="AK28">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q29">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="R29">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T29">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="U29">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="V29">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
+        <v>1.1</v>
+      </c>
+      <c r="X29">
+        <v>1.02</v>
+      </c>
+      <c r="Y29">
+        <v>1.18</v>
+      </c>
+      <c r="Z29">
+        <v>3.9</v>
+      </c>
+      <c r="AA29">
+        <v>1.65</v>
+      </c>
+      <c r="AB29">
+        <v>2.06</v>
+      </c>
+      <c r="AC29">
+        <v>2.62</v>
+      </c>
+      <c r="AD29">
+        <v>1.38</v>
+      </c>
+      <c r="AE29">
         <v>1.12</v>
       </c>
-      <c r="X29">
-        <v>1.01</v>
-      </c>
-      <c r="Y29">
-        <v>1.16</v>
-      </c>
-      <c r="Z29">
-        <v>4.15</v>
-      </c>
-      <c r="AA29">
-        <v>1.6</v>
-      </c>
-      <c r="AB29">
-        <v>2.15</v>
-      </c>
-      <c r="AC29">
-        <v>2.49</v>
-      </c>
-      <c r="AD29">
-        <v>1.42</v>
-      </c>
-      <c r="AE29">
-        <v>1.14</v>
-      </c>
       <c r="AF29">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AG29">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AK29">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="O30">
         <v>3.6</v>
       </c>
       <c r="P30">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q30">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T30">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="U30">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V30">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>4.19</v>
+        <v>3.98</v>
       </c>
       <c r="AA30">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB30">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AC30">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD30">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG30">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK30">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q31">
         <v>2.16</v>
@@ -5377,16 +5377,16 @@
         <v>2.22</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T31">
-        <v>2.35</v>
+        <v>3.12</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W31">
         <v>1.08</v>
@@ -5395,16 +5395,16 @@
         <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>2.8</v>
+        <v>3.79</v>
       </c>
       <c r="AA31">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AB31">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AC31">
         <v>2.88</v>
@@ -5416,10 +5416,10 @@
         <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
         <v>2.1</v>
@@ -5525,34 +5525,34 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O32">
         <v>3.4</v>
       </c>
       <c r="P32">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q32">
         <v>3.38</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T32">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="U32">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V32">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X32">
         <v>1.03</v>
@@ -5561,28 +5561,28 @@
         <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>2.9</v>
+        <v>3.94</v>
       </c>
       <c r="AA32">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB32">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD32">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
         <v>1.36</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O33">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P33">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Q33">
         <v>6.95</v>
       </c>
       <c r="R33">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T33">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="U33">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V33">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>4.07</v>
+        <v>3.92</v>
       </c>
       <c r="AA33">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB33">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AD33">
         <v>1.38</v>
       </c>
       <c r="AE33">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG33">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>2.74</v>
+        <v>1.12</v>
       </c>
       <c r="AK33">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,49 +5851,49 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="O34">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q34">
-        <v>5.1</v>
+        <v>5.16</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T34">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="U34">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="V34">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z34">
         <v>3.42</v>
       </c>
       <c r="AA34">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB34">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC34">
         <v>3.08</v>
@@ -5905,10 +5905,10 @@
         <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG34">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.19</v>
       </c>
       <c r="AK34">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="P35">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="Q35">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="R35">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S35">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T35">
-        <v>3.14</v>
+        <v>2.67</v>
       </c>
       <c r="U35">
-        <v>2.67</v>
+        <v>2.97</v>
       </c>
       <c r="V35">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W35">
+        <v>1.03</v>
+      </c>
+      <c r="X35">
+        <v>1.04</v>
+      </c>
+      <c r="Y35">
+        <v>1.33</v>
+      </c>
+      <c r="Z35">
+        <v>3.08</v>
+      </c>
+      <c r="AA35">
+        <v>1.99</v>
+      </c>
+      <c r="AB35">
+        <v>1.76</v>
+      </c>
+      <c r="AC35">
+        <v>3.57</v>
+      </c>
+      <c r="AD35">
+        <v>1.31</v>
+      </c>
+      <c r="AE35">
         <v>1.05</v>
       </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.25</v>
-      </c>
-      <c r="Z35">
-        <v>3.42</v>
-      </c>
-      <c r="AA35">
-        <v>1.85</v>
-      </c>
-      <c r="AB35">
-        <v>1.89</v>
-      </c>
-      <c r="AC35">
-        <v>2.97</v>
-      </c>
-      <c r="AD35">
-        <v>1.34</v>
-      </c>
-      <c r="AE35">
-        <v>1.08</v>
-      </c>
       <c r="AF35">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG35">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="O36">
         <v>4.5</v>
       </c>
       <c r="P36">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="Q36">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="T36">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U36">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V36">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W36">
+        <v>1.11</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
         <v>1.12</v>
       </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.14</v>
-      </c>
       <c r="Z36">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA36">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AB36">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AC36">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="AD36">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AE36">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF36">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK36">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.88</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>3.92</v>
+        <v>6.1</v>
       </c>
       <c r="Q37">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="R37">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="U37">
-        <v>2.57</v>
+        <v>2.18</v>
       </c>
       <c r="V37">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z37">
-        <v>4.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA37">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AB37">
-        <v>2.09</v>
+        <v>2.75</v>
       </c>
       <c r="AC37">
-        <v>2.59</v>
+        <v>2.19</v>
       </c>
       <c r="AD37">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AF37">
         <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK37">
-        <v>1.91</v>
+        <v>2.86</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.7</v>
+        <v>1.78</v>
       </c>
       <c r="O38">
         <v>3.6</v>
       </c>
       <c r="P38">
-        <v>1.84</v>
+        <v>3.5</v>
       </c>
       <c r="Q38">
-        <v>4.33</v>
+        <v>2.38</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T38">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U38">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="V38">
+        <v>1.51</v>
+      </c>
+      <c r="W38">
+        <v>1.1</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
+        <v>1.17</v>
+      </c>
+      <c r="Z38">
+        <v>3.95</v>
+      </c>
+      <c r="AA38">
+        <v>1.69</v>
+      </c>
+      <c r="AB38">
+        <v>2.09</v>
+      </c>
+      <c r="AC38">
+        <v>2.59</v>
+      </c>
+      <c r="AD38">
         <v>1.46</v>
-      </c>
-      <c r="W38">
-        <v>1.08</v>
-      </c>
-      <c r="X38">
-        <v>1.04</v>
-      </c>
-      <c r="Y38">
-        <v>1.2</v>
-      </c>
-      <c r="Z38">
-        <v>4.1</v>
-      </c>
-      <c r="AA38">
-        <v>1.7</v>
-      </c>
-      <c r="AB38">
-        <v>1.99</v>
-      </c>
-      <c r="AC38">
-        <v>2.8</v>
-      </c>
-      <c r="AD38">
-        <v>1.43</v>
       </c>
       <c r="AE38">
         <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.51</v>
+        <v>3.6</v>
       </c>
       <c r="O39">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="Q39">
-        <v>1.9</v>
+        <v>4.46</v>
       </c>
       <c r="R39">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="S39">
+        <v>1.32</v>
+      </c>
+      <c r="T39">
+        <v>3.3</v>
+      </c>
+      <c r="U39">
+        <v>2.39</v>
+      </c>
+      <c r="V39">
+        <v>1.46</v>
+      </c>
+      <c r="W39">
+        <v>1.08</v>
+      </c>
+      <c r="X39">
+        <v>1</v>
+      </c>
+      <c r="Y39">
+        <v>1.19</v>
+      </c>
+      <c r="Z39">
+        <v>3.82</v>
+      </c>
+      <c r="AA39">
+        <v>1.72</v>
+      </c>
+      <c r="AB39">
+        <v>2.1</v>
+      </c>
+      <c r="AC39">
+        <v>2.62</v>
+      </c>
+      <c r="AD39">
+        <v>1.38</v>
+      </c>
+      <c r="AE39">
+        <v>1.12</v>
+      </c>
+      <c r="AF39">
+        <v>1.63</v>
+      </c>
+      <c r="AG39">
+        <v>2.14</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.25</v>
+      </c>
+      <c r="AK39">
         <v>1.23</v>
-      </c>
-      <c r="T39">
-        <v>3.75</v>
-      </c>
-      <c r="U39">
-        <v>2.12</v>
-      </c>
-      <c r="V39">
-        <v>1.57</v>
-      </c>
-      <c r="W39">
-        <v>1.12</v>
-      </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.1</v>
-      </c>
-      <c r="Z39">
-        <v>5</v>
-      </c>
-      <c r="AA39">
-        <v>1.5</v>
-      </c>
-      <c r="AB39">
-        <v>2.63</v>
-      </c>
-      <c r="AC39">
-        <v>2.38</v>
-      </c>
-      <c r="AD39">
-        <v>1.61</v>
-      </c>
-      <c r="AE39">
-        <v>1.26</v>
-      </c>
-      <c r="AF39">
-        <v>1.6</v>
-      </c>
-      <c r="AG39">
-        <v>2.19</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.2</v>
-      </c>
-      <c r="AK39">
-        <v>2.5</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.03</v>
+        <v>2.6</v>
       </c>
       <c r="O41">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P41">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="Q41">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="R41">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S41">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T41">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U41">
-        <v>3.6</v>
+        <v>2.81</v>
       </c>
       <c r="V41">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="W41">
         <v>1.05</v>
       </c>
       <c r="X41">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="Z41">
-        <v>2.52</v>
+        <v>3.14</v>
       </c>
       <c r="AA41">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AB41">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AC41">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD41">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE41">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF41">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AG41">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK41">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O42">
+        <v>2.87</v>
+      </c>
+      <c r="P42">
         <v>3.1</v>
       </c>
-      <c r="P42">
-        <v>3</v>
-      </c>
       <c r="Q42">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="T42">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="U42">
-        <v>2.55</v>
+        <v>3.42</v>
       </c>
       <c r="V42">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="Z42">
-        <v>3.42</v>
+        <v>2.49</v>
       </c>
       <c r="AA42">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AB42">
-        <v>1.93</v>
+        <v>1.49</v>
       </c>
       <c r="AC42">
-        <v>2.51</v>
+        <v>4.6</v>
       </c>
       <c r="AD42">
-        <v>1.49</v>
+        <v>1.13</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AF42">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AG42">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
+        <v>2.2</v>
+      </c>
+      <c r="O43">
+        <v>3.4</v>
+      </c>
+      <c r="P43">
         <v>2.8</v>
       </c>
-      <c r="O43">
-        <v>3</v>
-      </c>
-      <c r="P43">
-        <v>2.55</v>
-      </c>
       <c r="Q43">
-        <v>3.68</v>
+        <v>2.82</v>
       </c>
       <c r="R43">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="S43">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="T43">
-        <v>2.29</v>
+        <v>3.12</v>
       </c>
       <c r="U43">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="V43">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="W43">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="Z43">
+        <v>4.4</v>
+      </c>
+      <c r="AA43">
+        <v>1.61</v>
+      </c>
+      <c r="AB43">
+        <v>2.24</v>
+      </c>
+      <c r="AC43">
         <v>2.61</v>
       </c>
-      <c r="AA43">
-        <v>2.48</v>
-      </c>
-      <c r="AB43">
-        <v>1.49</v>
-      </c>
-      <c r="AC43">
-        <v>4.45</v>
-      </c>
       <c r="AD43">
+        <v>1.46</v>
+      </c>
+      <c r="AE43">
         <v>1.14</v>
       </c>
-      <c r="AE43">
-        <v>1</v>
-      </c>
       <c r="AF43">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AG43">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="O44">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q44">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="R44">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S44">
+        <v>1.36</v>
+      </c>
+      <c r="T44">
+        <v>2.73</v>
+      </c>
+      <c r="U44">
+        <v>2.61</v>
+      </c>
+      <c r="V44">
         <v>1.39</v>
-      </c>
-      <c r="T44">
-        <v>2.8</v>
-      </c>
-      <c r="U44">
-        <v>2.84</v>
-      </c>
-      <c r="V44">
-        <v>1.36</v>
       </c>
       <c r="W44">
         <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z44">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA44">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AB44">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC44">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD44">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG44">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK44">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="O45">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P45">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q45">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="R45">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S45">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="U45">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W45">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z45">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AA45">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AB45">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC45">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD45">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE45">
         <v>1.09</v>
       </c>
       <c r="AF45">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG45">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="O46">
         <v>3.3</v>
@@ -7816,56 +7816,56 @@
         <v>4.2</v>
       </c>
       <c r="Q46">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="R46">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="S46">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T46">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U46">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="V46">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W46">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>1.3</v>
+      </c>
+      <c r="Z46">
+        <v>2.97</v>
+      </c>
+      <c r="AA46">
+        <v>2.04</v>
+      </c>
+      <c r="AB46">
+        <v>1.67</v>
+      </c>
+      <c r="AC46">
+        <v>3.58</v>
+      </c>
+      <c r="AD46">
+        <v>1.21</v>
+      </c>
+      <c r="AE46">
         <v>1.03</v>
       </c>
-      <c r="Y46">
-        <v>1.27</v>
-      </c>
-      <c r="Z46">
-        <v>3.14</v>
-      </c>
-      <c r="AA46">
-        <v>1.93</v>
-      </c>
-      <c r="AB46">
+      <c r="AF46">
+        <v>1.92</v>
+      </c>
+      <c r="AG46">
         <v>1.75</v>
       </c>
-      <c r="AC46">
-        <v>3.28</v>
-      </c>
-      <c r="AD46">
-        <v>1.25</v>
-      </c>
-      <c r="AE46">
-        <v>1.05</v>
-      </c>
-      <c r="AF46">
-        <v>1.84</v>
-      </c>
-      <c r="AG46">
-        <v>1.83</v>
-      </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,31 +8133,31 @@
         </is>
       </c>
       <c r="N48">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O48">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="P48">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Q48">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
       <c r="R48">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="S48">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T48">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U48">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="V48">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="W48">
         <v>1.25</v>
@@ -8166,31 +8166,31 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z48">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="AA48">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AB48">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AC48">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AD48">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AE48">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AG48">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>3.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK48">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O51">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="P51">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q51">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R51">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T51">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="U51">
         <v>2.35</v>
@@ -8649,37 +8649,37 @@
         <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="AA51">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC51">
         <v>2.88</v>
       </c>
       <c r="AD51">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE51">
         <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AG51">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AK51">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="O52">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="Q52">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="R52">
         <v>2.1</v>
       </c>
       <c r="S52">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T52">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U52">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V52">
         <v>1.36</v>
       </c>
       <c r="W52">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y52">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z52">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA52">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB52">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC52">
-        <v>3.34</v>
+        <v>3.63</v>
       </c>
       <c r="AD52">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE52">
         <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG52">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="O63">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P63">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q63">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R63">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="S63">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T63">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="U63">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="V63">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z63">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA63">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AB63">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AC63">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AD63">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE63">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF63">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG63">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AL63">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "90+3"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2257,11 +2257,11 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "90+5"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -3374,75 +3374,75 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O19">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>3.78</v>
+        <v>3.46</v>
       </c>
       <c r="R19">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="S19">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T19">
-        <v>3.46</v>
+        <v>3.18</v>
       </c>
       <c r="U19">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="AA19">
         <v>1.6</v>
@@ -3451,62 +3451,62 @@
         <v>2.3</v>
       </c>
       <c r="AC19">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AD19">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AE19">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF19">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG19">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "80"]</t>
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3537,31 +3537,31 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -3569,43 +3569,43 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P20">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q20">
+        <v>3.78</v>
+      </c>
+      <c r="R20">
+        <v>2.26</v>
+      </c>
+      <c r="S20">
+        <v>1.23</v>
+      </c>
+      <c r="T20">
         <v>3.46</v>
       </c>
-      <c r="R20">
-        <v>2.21</v>
-      </c>
-      <c r="S20">
-        <v>1.27</v>
-      </c>
-      <c r="T20">
-        <v>3.18</v>
-      </c>
       <c r="U20">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="V20">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W20">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z20">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="AA20">
         <v>1.6</v>
@@ -3614,62 +3614,62 @@
         <v>2.3</v>
       </c>
       <c r="AC20">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AD20">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE20">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF20">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AG20">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>["18"]</t>
+          <t>["41"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>["23", "80"]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO20">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AP20">
         <v>9</v>
       </c>
       <c r="AQ20">
-        <v>1.39</v>
+        <v>0.96</v>
       </c>
       <c r="AR20">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AS20">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="AT20">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3887,11 +3887,11 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "26"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -4376,11 +4376,11 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78"]</t>
         </is>
       </c>
       <c r="AJ25">
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4690,23 +4690,23 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "90+3"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4841,19 +4841,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -4862,118 +4862,118 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="Q28">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="R28">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T28">
-        <v>2.63</v>
+        <v>3.38</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V28">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA28">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB28">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AC28">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AD28">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG28">
         <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AJ28">
-        <v>1.7</v>
+        <v>1.19</v>
       </c>
       <c r="AK28">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5004,22 +5004,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -5028,27 +5028,27 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q29">
-        <v>2.79</v>
+        <v>2.37</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S29">
         <v>1.24</v>
@@ -5057,10 +5057,10 @@
         <v>3.38</v>
       </c>
       <c r="U29">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W29">
         <v>1.1</v>
@@ -5069,74 +5069,74 @@
         <v>1.02</v>
       </c>
       <c r="Y29">
+        <v>1.17</v>
+      </c>
+      <c r="Z29">
+        <v>3.98</v>
+      </c>
+      <c r="AA29">
+        <v>1.66</v>
+      </c>
+      <c r="AB29">
+        <v>2.11</v>
+      </c>
+      <c r="AC29">
+        <v>2.7</v>
+      </c>
+      <c r="AD29">
+        <v>1.36</v>
+      </c>
+      <c r="AE29">
+        <v>1.1</v>
+      </c>
+      <c r="AF29">
+        <v>1.61</v>
+      </c>
+      <c r="AG29">
+        <v>2.16</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>["3", "11", "25"]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>["69"]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.18</v>
       </c>
-      <c r="Z29">
-        <v>3.9</v>
-      </c>
-      <c r="AA29">
-        <v>1.65</v>
-      </c>
-      <c r="AB29">
-        <v>2.06</v>
-      </c>
-      <c r="AC29">
-        <v>2.62</v>
-      </c>
-      <c r="AD29">
-        <v>1.38</v>
-      </c>
-      <c r="AE29">
-        <v>1.12</v>
-      </c>
-      <c r="AF29">
-        <v>1.56</v>
-      </c>
-      <c r="AG29">
-        <v>2.25</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.19</v>
-      </c>
       <c r="AK29">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5167,22 +5167,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -5195,111 +5195,111 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q30">
-        <v>2.37</v>
+        <v>2.16</v>
       </c>
       <c r="R30">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S30">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="T30">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="U30">
-        <v>2.34</v>
+        <v>2.73</v>
       </c>
       <c r="V30">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
+        <v>1.2</v>
+      </c>
+      <c r="Z30">
+        <v>3.79</v>
+      </c>
+      <c r="AA30">
+        <v>1.72</v>
+      </c>
+      <c r="AB30">
+        <v>2.07</v>
+      </c>
+      <c r="AC30">
+        <v>2.88</v>
+      </c>
+      <c r="AD30">
+        <v>1.32</v>
+      </c>
+      <c r="AE30">
+        <v>1.08</v>
+      </c>
+      <c r="AF30">
+        <v>1.75</v>
+      </c>
+      <c r="AG30">
+        <v>1.95</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>["13", "38"]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.17</v>
       </c>
-      <c r="Z30">
-        <v>3.98</v>
-      </c>
-      <c r="AA30">
-        <v>1.66</v>
-      </c>
-      <c r="AB30">
-        <v>2.11</v>
-      </c>
-      <c r="AC30">
-        <v>2.7</v>
-      </c>
-      <c r="AD30">
-        <v>1.36</v>
-      </c>
-      <c r="AE30">
-        <v>1.1</v>
-      </c>
-      <c r="AF30">
-        <v>1.61</v>
-      </c>
-      <c r="AG30">
-        <v>2.16</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.18</v>
-      </c>
       <c r="AK30">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5330,16 +5330,16 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -5351,118 +5351,118 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>4.33</v>
+        <v>1.91</v>
       </c>
       <c r="Q31">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="R31">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S31">
         <v>1.28</v>
       </c>
       <c r="T31">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="U31">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z31">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="AA31">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AB31">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AF31">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG31">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
+          <t>["75", "87", "90+5"]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="AK31">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="AL31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -5514,14 +5514,14 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72", "90+4"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,26 +5665,26 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AJ33">
@@ -5767,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -5840,14 +5840,14 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
@@ -5930,28 +5930,28 @@
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -6006,11 +6006,11 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AJ35">
@@ -6093,28 +6093,28 @@
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6154,26 +6154,26 @@
         </is>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "61"]</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "36"]</t>
         </is>
       </c>
       <c r="AJ36">
@@ -6256,28 +6256,28 @@
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6320,13 +6320,13 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40"]</t>
         </is>
       </c>
       <c r="AJ37">
@@ -6419,28 +6419,28 @@
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6483,23 +6483,23 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "46", "76", "87"]</t>
         </is>
       </c>
       <c r="AJ38">
@@ -6582,28 +6582,28 @@
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6643,26 +6643,26 @@
         </is>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "68"]</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22"]</t>
         </is>
       </c>
       <c r="AJ39">
@@ -6745,28 +6745,28 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6809,127 +6809,127 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="O40">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="Q40">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="R40">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="S40">
+        <v>1.27</v>
+      </c>
+      <c r="T40">
+        <v>3.18</v>
+      </c>
+      <c r="U40">
+        <v>2.21</v>
+      </c>
+      <c r="V40">
+        <v>1.6</v>
+      </c>
+      <c r="W40">
+        <v>1.12</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.13</v>
+      </c>
+      <c r="Z40">
+        <v>4.6</v>
+      </c>
+      <c r="AA40">
+        <v>1.61</v>
+      </c>
+      <c r="AB40">
+        <v>2.25</v>
+      </c>
+      <c r="AC40">
+        <v>2.38</v>
+      </c>
+      <c r="AD40">
+        <v>1.51</v>
+      </c>
+      <c r="AE40">
+        <v>1.16</v>
+      </c>
+      <c r="AF40">
+        <v>1.5</v>
+      </c>
+      <c r="AG40">
+        <v>2.47</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>["37", "90+2"]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.22</v>
       </c>
-      <c r="T40">
-        <v>3.8</v>
-      </c>
-      <c r="U40">
-        <v>2.14</v>
-      </c>
-      <c r="V40">
-        <v>1.64</v>
-      </c>
-      <c r="W40">
-        <v>1.16</v>
-      </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.09</v>
-      </c>
-      <c r="Z40">
-        <v>5.35</v>
-      </c>
-      <c r="AA40">
-        <v>1.42</v>
-      </c>
-      <c r="AB40">
-        <v>2.6</v>
-      </c>
-      <c r="AC40">
-        <v>2.11</v>
-      </c>
-      <c r="AD40">
+      <c r="AK40">
+        <v>1.26</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>4</v>
+      </c>
+      <c r="AN40">
+        <v>6</v>
+      </c>
+      <c r="AO40">
+        <v>17</v>
+      </c>
+      <c r="AP40">
+        <v>16</v>
+      </c>
+      <c r="AQ40">
         <v>1.62</v>
       </c>
-      <c r="AE40">
-        <v>1.22</v>
-      </c>
-      <c r="AF40">
-        <v>1.38</v>
-      </c>
-      <c r="AG40">
-        <v>2.77</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.25</v>
-      </c>
-      <c r="AK40">
-        <v>1.45</v>
-      </c>
-      <c r="AL40">
-        <v>0</v>
-      </c>
-      <c r="AM40">
-        <v>-1</v>
-      </c>
-      <c r="AN40">
-        <v>-1</v>
-      </c>
-      <c r="AO40">
-        <v>-1</v>
-      </c>
-      <c r="AP40">
-        <v>-1</v>
-      </c>
-      <c r="AQ40">
-        <v>0</v>
-      </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6960,139 +6960,139 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O41">
+        <v>2.87</v>
+      </c>
+      <c r="P41">
         <v>3.1</v>
       </c>
-      <c r="P41">
-        <v>2.4</v>
-      </c>
       <c r="Q41">
-        <v>3.58</v>
+        <v>2.95</v>
       </c>
       <c r="R41">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="S41">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="T41">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="U41">
-        <v>2.81</v>
+        <v>3.42</v>
       </c>
       <c r="V41">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="W41">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="Z41">
-        <v>3.14</v>
+        <v>2.49</v>
       </c>
       <c r="AA41">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AB41">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AC41">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD41">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE41">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF41">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="AG41">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55", "90+1"]</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "36", "78"]</t>
         </is>
       </c>
       <c r="AJ41">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AL41">
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7123,22 +7123,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -7151,111 +7151,111 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
+        <v>2.2</v>
+      </c>
+      <c r="O42">
+        <v>3.4</v>
+      </c>
+      <c r="P42">
+        <v>2.8</v>
+      </c>
+      <c r="Q42">
+        <v>2.82</v>
+      </c>
+      <c r="R42">
+        <v>2.12</v>
+      </c>
+      <c r="S42">
+        <v>1.28</v>
+      </c>
+      <c r="T42">
+        <v>3.12</v>
+      </c>
+      <c r="U42">
         <v>2.25</v>
       </c>
-      <c r="O42">
-        <v>2.87</v>
-      </c>
-      <c r="P42">
-        <v>3.1</v>
-      </c>
-      <c r="Q42">
-        <v>2.95</v>
-      </c>
-      <c r="R42">
-        <v>1.83</v>
-      </c>
-      <c r="S42">
+      <c r="V42">
         <v>1.53</v>
       </c>
-      <c r="T42">
-        <v>2.29</v>
-      </c>
-      <c r="U42">
-        <v>3.42</v>
-      </c>
-      <c r="V42">
-        <v>1.23</v>
-      </c>
       <c r="W42">
+        <v>1.11</v>
+      </c>
+      <c r="X42">
         <v>1.02</v>
       </c>
-      <c r="X42">
-        <v>1.04</v>
-      </c>
       <c r="Y42">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>2.49</v>
+        <v>4.4</v>
       </c>
       <c r="AA42">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="AB42">
-        <v>1.49</v>
+        <v>2.24</v>
       </c>
       <c r="AC42">
-        <v>4.6</v>
+        <v>2.61</v>
       </c>
       <c r="AD42">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="AE42">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="AG42">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
+          <t>["44"]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL42">
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G43">
@@ -7314,68 +7314,68 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q43">
-        <v>2.82</v>
+        <v>3.58</v>
       </c>
       <c r="R43">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="S43">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="T43">
-        <v>3.12</v>
+        <v>2.48</v>
       </c>
       <c r="U43">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="V43">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z43">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA43">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AB43">
-        <v>2.24</v>
+        <v>1.66</v>
       </c>
       <c r="AC43">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="AD43">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AE43">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AG43">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,37 +7388,37 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK43">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL43">
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
@@ -7560,28 +7560,28 @@
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -7633,14 +7633,14 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AJ45">
@@ -7723,28 +7723,28 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -7796,14 +7796,14 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
@@ -7886,28 +7886,28 @@
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7947,100 +7947,100 @@
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="O47">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="P47">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R47">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S47">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="U47">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V47">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="W47">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Z47">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AA47">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AB47">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="AC47">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AD47">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="AE47">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AF47">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AG47">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49"]</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "45", "65"]</t>
         </is>
       </c>
       <c r="AJ47">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AK47">
         <v>1.98</v>
@@ -8049,28 +8049,28 @@
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8110,130 +8110,130 @@
         </is>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I48">
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N48">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="O48">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="P48">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Q48">
-        <v>7.53</v>
+        <v>9</v>
       </c>
       <c r="R48">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="S48">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T48">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="V48">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="W48">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z48">
-        <v>7.2</v>
+        <v>6.25</v>
       </c>
       <c r="AA48">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB48">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="AC48">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AD48">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AE48">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AF48">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71", "83"]</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "33", "90+1"]</t>
         </is>
       </c>
       <c r="AJ48">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK48">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AL48">
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN48">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO48">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP48">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ48">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS48">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -8299,31 +8299,31 @@
         <v>2.14</v>
       </c>
       <c r="O49">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P49">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S49">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U49">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X49">
         <v>1.03</v>
@@ -8332,22 +8332,22 @@
         <v>1.18</v>
       </c>
       <c r="Z49">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AA49">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB49">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AC49">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="AD49">
         <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
         <v>1.57</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,31 +8459,31 @@
         </is>
       </c>
       <c r="N50">
+        <v>3.75</v>
+      </c>
+      <c r="O50">
         <v>3.8</v>
       </c>
-      <c r="O50">
-        <v>4.1</v>
-      </c>
       <c r="P50">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="Q50">
-        <v>4.15</v>
+        <v>3.46</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="V50">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="W50">
         <v>1.17</v>
@@ -8492,31 +8492,31 @@
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z50">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA50">
         <v>1.42</v>
       </c>
       <c r="AB50">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AC50">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD50">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AE50">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF50">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG50">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AK50">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="O51">
-        <v>5.05</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>9.199999999999999</v>
+        <v>4.05</v>
       </c>
       <c r="Q51">
+        <v>2.45</v>
+      </c>
+      <c r="R51">
+        <v>2.1</v>
+      </c>
+      <c r="S51">
+        <v>1.4</v>
+      </c>
+      <c r="T51">
+        <v>2.63</v>
+      </c>
+      <c r="U51">
+        <v>2.9</v>
+      </c>
+      <c r="V51">
+        <v>1.36</v>
+      </c>
+      <c r="W51">
+        <v>1.06</v>
+      </c>
+      <c r="X51">
+        <v>1.06</v>
+      </c>
+      <c r="Y51">
+        <v>1.3</v>
+      </c>
+      <c r="Z51">
+        <v>3.1</v>
+      </c>
+      <c r="AA51">
+        <v>1.98</v>
+      </c>
+      <c r="AB51">
         <v>1.7</v>
       </c>
-      <c r="R51">
-        <v>2.47</v>
-      </c>
-      <c r="S51">
-        <v>1.27</v>
-      </c>
-      <c r="T51">
-        <v>3.32</v>
-      </c>
-      <c r="U51">
-        <v>2.35</v>
-      </c>
-      <c r="V51">
-        <v>1.51</v>
-      </c>
-      <c r="W51">
-        <v>1.1</v>
-      </c>
-      <c r="X51">
-        <v>1.03</v>
-      </c>
-      <c r="Y51">
-        <v>1.18</v>
-      </c>
-      <c r="Z51">
-        <v>3.88</v>
-      </c>
-      <c r="AA51">
-        <v>1.71</v>
-      </c>
-      <c r="AB51">
-        <v>2.1</v>
-      </c>
       <c r="AC51">
-        <v>2.88</v>
+        <v>3.63</v>
       </c>
       <c r="AD51">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AG51">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.77</v>
+        <v>1.28</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>5.05</v>
       </c>
       <c r="P52">
-        <v>4.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q52">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="R52">
+        <v>2.47</v>
+      </c>
+      <c r="S52">
+        <v>1.27</v>
+      </c>
+      <c r="T52">
+        <v>3.32</v>
+      </c>
+      <c r="U52">
+        <v>2.35</v>
+      </c>
+      <c r="V52">
+        <v>1.51</v>
+      </c>
+      <c r="W52">
+        <v>1.1</v>
+      </c>
+      <c r="X52">
+        <v>1.03</v>
+      </c>
+      <c r="Y52">
+        <v>1.18</v>
+      </c>
+      <c r="Z52">
+        <v>3.88</v>
+      </c>
+      <c r="AA52">
+        <v>1.71</v>
+      </c>
+      <c r="AB52">
         <v>2.1</v>
       </c>
-      <c r="S52">
-        <v>1.4</v>
-      </c>
-      <c r="T52">
-        <v>2.63</v>
-      </c>
-      <c r="U52">
-        <v>2.9</v>
-      </c>
-      <c r="V52">
-        <v>1.36</v>
-      </c>
-      <c r="W52">
-        <v>1.06</v>
-      </c>
-      <c r="X52">
-        <v>1.06</v>
-      </c>
-      <c r="Y52">
-        <v>1.3</v>
-      </c>
-      <c r="Z52">
-        <v>3.1</v>
-      </c>
-      <c r="AA52">
-        <v>1.98</v>
-      </c>
-      <c r="AB52">
-        <v>1.7</v>
-      </c>
       <c r="AC52">
-        <v>3.63</v>
+        <v>2.88</v>
       </c>
       <c r="AD52">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AG52">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK52">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,31 +8948,31 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="O53">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P53">
-        <v>4.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q53">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="R53">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="S53">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
         <v>3.9</v>
       </c>
       <c r="U53">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="V53">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="W53">
         <v>1.15</v>
@@ -8981,31 +8981,31 @@
         <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA53">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AB53">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="AC53">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="AD53">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AE53">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
         <v>1.44</v>
       </c>
       <c r="AG53">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK53">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O54">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P54">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="Q54">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="R54">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S54">
         <v>1.33</v>
       </c>
       <c r="T54">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="U54">
         <v>2.55</v>
       </c>
       <c r="V54">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z54">
         <v>3.28</v>
       </c>
       <c r="AA54">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB54">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC54">
         <v>3.4</v>
       </c>
       <c r="AD54">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE54">
         <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG54">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK54">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N58">
